--- a/research/traditional_assets/database/data/netherlands/netherlands_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_telecom_services.xlsx
@@ -650,10 +650,10 @@
         <v>0.2600405229120986</v>
       </c>
       <c r="X2">
-        <v>0.07763903132153564</v>
+        <v>0.07761856165522107</v>
       </c>
       <c r="Y2">
-        <v>0.1824014915905629</v>
+        <v>0.1824219612568775</v>
       </c>
       <c r="Z2">
         <v>0.7152350508140561</v>
@@ -662,10 +662,10 @@
         <v>0.139710635333767</v>
       </c>
       <c r="AB2">
-        <v>0.06588298540856662</v>
+        <v>0.06586944041636952</v>
       </c>
       <c r="AC2">
-        <v>0.07382764992520037</v>
+        <v>0.07384119491739746</v>
       </c>
       <c r="AD2">
         <v>7235.1</v>
@@ -787,10 +787,10 @@
         <v>0.2600405229120986</v>
       </c>
       <c r="X3">
-        <v>0.07763903132153564</v>
+        <v>0.07761856165522107</v>
       </c>
       <c r="Y3">
-        <v>0.1824014915905629</v>
+        <v>0.1824219612568775</v>
       </c>
       <c r="Z3">
         <v>0.7152350508140561</v>
@@ -799,10 +799,10 @@
         <v>0.139710635333767</v>
       </c>
       <c r="AB3">
-        <v>0.06588298540856662</v>
+        <v>0.06586944041636952</v>
       </c>
       <c r="AC3">
-        <v>0.07382764992520037</v>
+        <v>0.07384119491739746</v>
       </c>
       <c r="AD3">
         <v>7235.1</v>
@@ -1139,49 +1139,49 @@
         <v>3.73639509279648</v>
       </c>
       <c r="F2">
-        <v>3.0941908822876</v>
+        <v>3.04332468333499</v>
       </c>
       <c r="G2">
         <v>2.8527324343506</v>
       </c>
       <c r="H2">
-        <v>2.61417198959073</v>
+        <v>2.78282824698368</v>
       </c>
       <c r="I2">
         <v>0.338289545664951</v>
       </c>
       <c r="J2">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="K2">
         <v>14152.2</v>
       </c>
       <c r="L2">
-        <v>14604.516674687</v>
+        <v>14636.5412699434</v>
       </c>
       <c r="M2">
         <v>20891</v>
       </c>
       <c r="N2">
-        <v>20738.279674687</v>
+        <v>21198.0502699434</v>
       </c>
       <c r="O2">
         <v>7235.1</v>
       </c>
       <c r="P2">
-        <v>6630.063</v>
+        <v>7057.809</v>
       </c>
       <c r="Q2">
-        <v>0.0658829854085666</v>
+        <v>0.0658694404163695</v>
       </c>
       <c r="R2">
-        <v>0.0661568528315121</v>
+        <v>0.0653307685318049</v>
       </c>
       <c r="S2">
         <v>0.0428876</v>
       </c>
       <c r="T2">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.0776390313215356</v>
+        <v>0.0776185616552211</v>
       </c>
       <c r="X2">
-        <v>0.0765778185963944</v>
+        <v>0.0772985231817984</v>
       </c>
       <c r="Y2">
         <v>0.734839761090556</v>
       </c>
       <c r="Z2">
-        <v>0.7103471407738819</v>
+        <v>0.727448572327908</v>
       </c>
       <c r="AA2">
         <v>7235.1</v>
@@ -1236,7 +1236,7 @@
         <v>14152.2</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.04329999999999999</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.0688828621459448</v>
+        <v>0.06886802191789448</v>
       </c>
       <c r="C2">
-        <v>19827.9085756532</v>
+        <v>19828.51329561332</v>
       </c>
       <c r="D2">
-        <v>19331.6085756532</v>
+        <v>19332.21329561332</v>
       </c>
       <c r="E2">
         <v>-7235.1</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.0688828621459448</v>
+        <v>0.06886802191789448</v>
       </c>
       <c r="T2">
         <v>0.532748774085323</v>
       </c>
       <c r="U2">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.258</v>
       </c>
       <c r="W2">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.06874892236160826</v>
+        <v>0.06872373242134631</v>
       </c>
       <c r="C3">
-        <v>19678.67833710189</v>
+        <v>19684.30134491922</v>
       </c>
       <c r="D3">
-        <v>19396.25133710189</v>
+        <v>19401.87434491922</v>
       </c>
       <c r="E3">
         <v>-7021.227000000001</v>
@@ -1539,37 +1539,37 @@
         <v>1187.8</v>
       </c>
       <c r="M3">
-        <v>11.0572341</v>
+        <v>10.7578119</v>
       </c>
       <c r="N3">
-        <v>1176.7427659</v>
+        <v>1177.0421881</v>
       </c>
       <c r="O3">
-        <v>303.5996336022</v>
+        <v>303.6768845298</v>
       </c>
       <c r="P3">
-        <v>873.1431322977999</v>
+        <v>873.3653035701998</v>
       </c>
       <c r="Q3">
-        <v>2221.5431322978</v>
+        <v>2221.7653035702</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.06905586703192754</v>
+        <v>0.06904091557711749</v>
       </c>
       <c r="T3">
         <v>0.5367416992405887</v>
       </c>
       <c r="U3">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.258</v>
       </c>
       <c r="W3">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>107.4228861628243</v>
+        <v>110.4127875669586</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.06861498257727171</v>
+        <v>0.06857944292479813</v>
       </c>
       <c r="C4">
-        <v>19529.88186551191</v>
+        <v>19540.59323833968</v>
       </c>
       <c r="D4">
-        <v>19461.32786551191</v>
+        <v>19472.03923833968</v>
       </c>
       <c r="E4">
         <v>-6807.354</v>
@@ -1621,37 +1621,37 @@
         <v>1187.8</v>
       </c>
       <c r="M4">
-        <v>22.11446820000001</v>
+        <v>21.51562380000001</v>
       </c>
       <c r="N4">
-        <v>1165.6855318</v>
+        <v>1166.2843762</v>
       </c>
       <c r="O4">
-        <v>300.7468672044</v>
+        <v>300.9013690596</v>
       </c>
       <c r="P4">
-        <v>864.9386645955999</v>
+        <v>865.3830071403997</v>
       </c>
       <c r="Q4">
-        <v>2213.3386645956</v>
+        <v>2213.7830071404</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.0692324026298691</v>
+        <v>0.06921733767836545</v>
       </c>
       <c r="T4">
         <v>0.5408161126643293</v>
       </c>
       <c r="U4">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.258</v>
       </c>
       <c r="W4">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>53.71144308141217</v>
+        <v>55.20639378347931</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.06848104279293517</v>
+        <v>0.06843515342824996</v>
       </c>
       <c r="C5">
-        <v>19381.52354158671</v>
+        <v>19397.39446201685</v>
       </c>
       <c r="D5">
-        <v>19526.84254158671</v>
+        <v>19542.71346201685</v>
       </c>
       <c r="E5">
         <v>-6593.481000000001</v>
@@ -1703,37 +1703,37 @@
         <v>1187.8</v>
       </c>
       <c r="M5">
-        <v>33.17170230000001</v>
+        <v>32.27343570000001</v>
       </c>
       <c r="N5">
-        <v>1154.6282977</v>
+        <v>1155.5265643</v>
       </c>
       <c r="O5">
-        <v>297.8941008065999</v>
+        <v>298.1258535894</v>
       </c>
       <c r="P5">
-        <v>856.7341968933997</v>
+        <v>857.4007107105998</v>
       </c>
       <c r="Q5">
-        <v>2205.1341968934</v>
+        <v>2205.8007107106</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.06941257813704657</v>
+        <v>0.06939739734871131</v>
       </c>
       <c r="T5">
         <v>0.5449745346122706</v>
       </c>
       <c r="U5">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.258</v>
       </c>
       <c r="W5">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>35.80762872094144</v>
+        <v>36.80426252231954</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.06834710300859864</v>
+        <v>0.06829086393170181</v>
       </c>
       <c r="C6">
-        <v>19233.60780521782</v>
+        <v>19254.7105820313</v>
       </c>
       <c r="D6">
-        <v>19592.79980521782</v>
+        <v>19613.9025820313</v>
       </c>
       <c r="E6">
         <v>-6379.608</v>
@@ -1785,37 +1785,37 @@
         <v>1187.8</v>
       </c>
       <c r="M6">
-        <v>44.22893640000002</v>
+        <v>43.03124760000001</v>
       </c>
       <c r="N6">
-        <v>1143.5710636</v>
+        <v>1144.7687524</v>
       </c>
       <c r="O6">
-        <v>295.0413344087999</v>
+        <v>295.3503381191999</v>
       </c>
       <c r="P6">
-        <v>848.5297291911997</v>
+        <v>849.4184142807999</v>
       </c>
       <c r="Q6">
-        <v>2196.9297291912</v>
+        <v>2197.8184142808</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.06959650730062358</v>
+        <v>0.06958120826218939</v>
       </c>
       <c r="T6">
         <v>0.5492195903507942</v>
       </c>
       <c r="U6">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.258</v>
       </c>
       <c r="W6">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>26.85572154070608</v>
+        <v>27.60319689173965</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.0682131632242621</v>
+        <v>0.06814657443515362</v>
       </c>
       <c r="C7">
-        <v>19086.13915648792</v>
+        <v>19112.54724586345</v>
       </c>
       <c r="D7">
-        <v>19659.20415648792</v>
+        <v>19685.61224586345</v>
       </c>
       <c r="E7">
         <v>-6165.735000000001</v>
@@ -1867,37 +1867,37 @@
         <v>1187.8</v>
       </c>
       <c r="M7">
-        <v>55.28617050000003</v>
+        <v>53.78905950000001</v>
       </c>
       <c r="N7">
-        <v>1132.5138295</v>
+        <v>1134.0109405</v>
       </c>
       <c r="O7">
-        <v>292.1885680109999</v>
+        <v>292.5748226489999</v>
       </c>
       <c r="P7">
-        <v>840.3252614889998</v>
+        <v>841.4361178509997</v>
       </c>
       <c r="Q7">
-        <v>2188.725261489</v>
+        <v>2189.836117851</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.06978430865711802</v>
+        <v>0.06976888887910909</v>
       </c>
       <c r="T7">
         <v>0.553554015683813</v>
       </c>
       <c r="U7">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.258</v>
       </c>
       <c r="W7">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>21.48457723256486</v>
+        <v>22.08255751339172</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.06807922343992556</v>
+        <v>0.06800228493860548</v>
       </c>
       <c r="C8">
-        <v>18939.12215669425</v>
+        <v>18970.91018388685</v>
       </c>
       <c r="D8">
-        <v>19726.06015669425</v>
+        <v>19757.84818388685</v>
       </c>
       <c r="E8">
         <v>-5951.862</v>
@@ -1949,37 +1949,37 @@
         <v>1187.8</v>
       </c>
       <c r="M8">
-        <v>66.34340460000001</v>
+        <v>64.54687140000001</v>
       </c>
       <c r="N8">
-        <v>1121.4565954</v>
+        <v>1123.2531286</v>
       </c>
       <c r="O8">
-        <v>289.3358016131999</v>
+        <v>289.7993071787999</v>
       </c>
       <c r="P8">
-        <v>832.1207937867998</v>
+        <v>833.4538214211998</v>
       </c>
       <c r="Q8">
-        <v>2180.5207937868</v>
+        <v>2181.8538214212</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.06997610578715487</v>
+        <v>0.06996056270064413</v>
       </c>
       <c r="T8">
         <v>0.5579806628324279</v>
       </c>
       <c r="U8">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.258</v>
       </c>
       <c r="W8">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>17.90381436047073</v>
+        <v>18.40213126115977</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.06794528365558902</v>
+        <v>0.0678579954420573</v>
       </c>
       <c r="C9">
-        <v>18792.56142939308</v>
+        <v>18829.80521089487</v>
       </c>
       <c r="D9">
-        <v>19793.37242939308</v>
+        <v>19830.61621089487</v>
       </c>
       <c r="E9">
         <v>-5737.989</v>
@@ -2031,37 +2031,37 @@
         <v>1187.8</v>
       </c>
       <c r="M9">
-        <v>77.40063870000003</v>
+        <v>75.30468330000002</v>
       </c>
       <c r="N9">
-        <v>1110.3993613</v>
+        <v>1112.4953167</v>
       </c>
       <c r="O9">
-        <v>286.4830352154</v>
+        <v>287.0237917085999</v>
       </c>
       <c r="P9">
-        <v>823.9163260845999</v>
+        <v>825.4715249913997</v>
       </c>
       <c r="Q9">
-        <v>2172.3163260846</v>
+        <v>2173.8715249914</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.07017202758665486</v>
+        <v>0.07015635853984656</v>
       </c>
       <c r="T9">
         <v>0.5625025066939161</v>
       </c>
       <c r="U9">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.258</v>
       </c>
       <c r="W9">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>15.34612659468919</v>
+        <v>15.77325536670837</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.06781134387125251</v>
+        <v>0.06771370594550914</v>
       </c>
       <c r="C10">
-        <v>18646.46166146557</v>
+        <v>18689.23822766086</v>
       </c>
       <c r="D10">
-        <v>19861.14566146557</v>
+        <v>19903.92222766086</v>
       </c>
       <c r="E10">
         <v>-5524.116</v>
@@ -2113,37 +2113,37 @@
         <v>1187.8</v>
       </c>
       <c r="M10">
-        <v>88.45787280000003</v>
+        <v>86.06249520000003</v>
       </c>
       <c r="N10">
-        <v>1099.3421272</v>
+        <v>1101.7375048</v>
       </c>
       <c r="O10">
-        <v>283.6302688175999</v>
+        <v>284.2482762383999</v>
       </c>
       <c r="P10">
-        <v>815.7118583823997</v>
+        <v>817.4892285615997</v>
       </c>
       <c r="Q10">
-        <v>2164.1118583824</v>
+        <v>2165.8892285616</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.07037220855570923</v>
+        <v>0.07035641081033601</v>
       </c>
       <c r="T10">
         <v>0.5671226515089151</v>
       </c>
       <c r="U10">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.258</v>
       </c>
       <c r="W10">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>13.42786077035304</v>
+        <v>13.80159844586982</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.06767740408691596</v>
+        <v>0.06756941644896097</v>
       </c>
       <c r="C11">
-        <v>18500.82760420569</v>
+        <v>18549.21522253331</v>
       </c>
       <c r="D11">
-        <v>19929.38460420569</v>
+        <v>19977.77222253331</v>
       </c>
       <c r="E11">
         <v>-5310.243</v>
@@ -2195,37 +2195,37 @@
         <v>1187.8</v>
       </c>
       <c r="M11">
-        <v>99.51510690000003</v>
+        <v>96.82030710000002</v>
       </c>
       <c r="N11">
-        <v>1088.2848931</v>
+        <v>1090.9796929</v>
       </c>
       <c r="O11">
-        <v>280.7775024197999</v>
+        <v>281.4727607681999</v>
       </c>
       <c r="P11">
-        <v>807.5073906801997</v>
+        <v>809.5069321317998</v>
       </c>
       <c r="Q11">
-        <v>2155.9073906802</v>
+        <v>2157.9069321318</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.07057678910650106</v>
+        <v>0.07056085983402305</v>
       </c>
       <c r="T11">
         <v>0.5718443379681998</v>
       </c>
       <c r="U11">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.258</v>
       </c>
       <c r="W11">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.93587624031381</v>
+        <v>12.26808750743985</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.06754346430257942</v>
+        <v>0.0674251269524128</v>
       </c>
       <c r="C12">
-        <v>18355.66407443046</v>
+        <v>18409.74227306654</v>
       </c>
       <c r="D12">
-        <v>19998.09407443046</v>
+        <v>20052.17227306654</v>
       </c>
       <c r="E12">
         <v>-5096.37</v>
@@ -2277,37 +2277,37 @@
         <v>1187.8</v>
       </c>
       <c r="M12">
-        <v>110.5723410000001</v>
+        <v>107.578119</v>
       </c>
       <c r="N12">
-        <v>1077.227659</v>
+        <v>1080.221881</v>
       </c>
       <c r="O12">
-        <v>277.9247360219999</v>
+        <v>278.6972452979999</v>
       </c>
       <c r="P12">
-        <v>799.3029229779997</v>
+        <v>801.5246357019998</v>
       </c>
       <c r="Q12">
-        <v>2147.702922978</v>
+        <v>2149.924635702</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.07078591589175491</v>
+        <v>0.07076985216934756</v>
       </c>
       <c r="T12">
         <v>0.5766709507932463</v>
       </c>
       <c r="U12">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.258</v>
       </c>
       <c r="W12">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>10.74228861628243</v>
+        <v>11.04127875669586</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.06740952451824288</v>
+        <v>0.06728083745586465</v>
       </c>
       <c r="C13">
-        <v>18210.97595561349</v>
+        <v>18270.82554768797</v>
       </c>
       <c r="D13">
-        <v>20067.27895561349</v>
+        <v>20127.12854768797</v>
       </c>
       <c r="E13">
         <v>-4882.496999999999</v>
@@ -2359,37 +2359,37 @@
         <v>1187.8</v>
       </c>
       <c r="M13">
-        <v>121.6295751000001</v>
+        <v>118.3359309</v>
       </c>
       <c r="N13">
-        <v>1066.1704249</v>
+        <v>1069.4640691</v>
       </c>
       <c r="O13">
-        <v>275.0719696241999</v>
+        <v>275.9217298277999</v>
       </c>
       <c r="P13">
-        <v>791.0984552757998</v>
+        <v>793.5423392721998</v>
       </c>
       <c r="Q13">
-        <v>2139.4984552758</v>
+        <v>2141.9423392722</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.07099974215532907</v>
+        <v>0.07098354096164566</v>
       </c>
       <c r="T13">
         <v>0.5816060268278443</v>
       </c>
       <c r="U13">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.258</v>
       </c>
       <c r="W13">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>9.76571692389312</v>
+        <v>10.03752614245078</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.06727558473390634</v>
+        <v>0.06713654795931646</v>
       </c>
       <c r="C14">
-        <v>18066.76819904193</v>
+        <v>18132.471307403</v>
       </c>
       <c r="D14">
-        <v>20136.94419904193</v>
+        <v>20202.647307403</v>
       </c>
       <c r="E14">
         <v>-4668.624</v>
@@ -2441,37 +2441,37 @@
         <v>1187.8</v>
       </c>
       <c r="M14">
-        <v>132.6868092</v>
+        <v>129.0937428</v>
       </c>
       <c r="N14">
-        <v>1055.1131908</v>
+        <v>1058.7062572</v>
       </c>
       <c r="O14">
-        <v>272.2192032263999</v>
+        <v>273.1462143575999</v>
       </c>
       <c r="P14">
-        <v>782.8939875735998</v>
+        <v>785.5600428423998</v>
       </c>
       <c r="Q14">
-        <v>2131.2939875736</v>
+        <v>2133.9600428424</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.07121842810671175</v>
+        <v>0.07120208631740507</v>
       </c>
       <c r="T14">
         <v>0.5866532636814107</v>
       </c>
       <c r="U14">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V14">
         <v>0.258</v>
       </c>
       <c r="W14">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.951907180235363</v>
+        <v>9.201065630579885</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.06724775094956981</v>
+        <v>0.0671369484627683</v>
       </c>
       <c r="C15">
-        <v>17867.4329533088</v>
+        <v>17918.38790614465</v>
       </c>
       <c r="D15">
-        <v>20151.4819533088</v>
+        <v>20202.43690614466</v>
       </c>
       <c r="E15">
         <v>-4454.751</v>
@@ -2523,37 +2523,37 @@
         <v>1187.8</v>
       </c>
       <c r="M15">
-        <v>146.8024272</v>
+        <v>144.0220782</v>
       </c>
       <c r="N15">
-        <v>1040.9975728</v>
+        <v>1043.7779218</v>
       </c>
       <c r="O15">
-        <v>268.5773737823999</v>
+        <v>269.2947038243999</v>
       </c>
       <c r="P15">
-        <v>772.4201990175998</v>
+        <v>774.4832179755997</v>
       </c>
       <c r="Q15">
-        <v>2120.8201990176</v>
+        <v>2122.8832179756</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.0714421413213446</v>
+        <v>0.07142565570433138</v>
       </c>
       <c r="T15">
         <v>0.5918165289683922</v>
       </c>
       <c r="U15">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V15">
         <v>0.258</v>
       </c>
       <c r="W15">
-        <v>0.03917760000000001</v>
+        <v>0.03843560000000001</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.091146874443499</v>
+        <v>8.247346621054376</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.06712197316523327</v>
+        <v>0.06700378896622013</v>
       </c>
       <c r="C16">
-        <v>17719.51705779748</v>
+        <v>17774.7115099576</v>
       </c>
       <c r="D16">
-        <v>20217.43905779748</v>
+        <v>20272.6335099576</v>
       </c>
       <c r="E16">
         <v>-4240.878</v>
@@ -2605,37 +2605,37 @@
         <v>1187.8</v>
       </c>
       <c r="M16">
-        <v>158.0949216</v>
+        <v>155.1006996</v>
       </c>
       <c r="N16">
-        <v>1029.7050784</v>
+        <v>1032.6993004</v>
       </c>
       <c r="O16">
-        <v>265.6639102271999</v>
+        <v>266.4364195031999</v>
       </c>
       <c r="P16">
-        <v>764.0411681727996</v>
+        <v>766.2628808967997</v>
       </c>
       <c r="Q16">
-        <v>2112.4411681728</v>
+        <v>2114.6628808968</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.0716710571688759</v>
+        <v>0.07165442437932573</v>
       </c>
       <c r="T16">
         <v>0.5970998701922804</v>
       </c>
       <c r="U16">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V16">
         <v>0.258</v>
       </c>
       <c r="W16">
-        <v>0.03917760000000001</v>
+        <v>0.03843560000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.513207811983249</v>
+        <v>7.658250433836208</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.06699619538089673</v>
+        <v>0.06687062946967195</v>
       </c>
       <c r="C17">
-        <v>17572.03434385999</v>
+        <v>17631.52463337819</v>
       </c>
       <c r="D17">
-        <v>20283.82934385999</v>
+        <v>20343.31963337819</v>
       </c>
       <c r="E17">
         <v>-4027.005</v>
@@ -2687,37 +2687,37 @@
         <v>1187.8</v>
       </c>
       <c r="M17">
-        <v>169.387416</v>
+        <v>166.179321</v>
       </c>
       <c r="N17">
-        <v>1018.412584</v>
+        <v>1021.620679</v>
       </c>
       <c r="O17">
-        <v>262.750446672</v>
+        <v>263.5781351819999</v>
       </c>
       <c r="P17">
-        <v>755.6621373279997</v>
+        <v>758.0425438179998</v>
       </c>
       <c r="Q17">
-        <v>2104.062137328</v>
+        <v>2106.442543818</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.07190535927164321</v>
+        <v>0.07188857584667289</v>
       </c>
       <c r="T17">
         <v>0.6025075253273188</v>
       </c>
       <c r="U17">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V17">
         <v>0.258</v>
       </c>
       <c r="W17">
-        <v>0.03917760000000001</v>
+        <v>0.03843560000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.012327291184367</v>
+        <v>7.147700404913794</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.06713160159656019</v>
+        <v>0.06693929397312379</v>
       </c>
       <c r="C18">
-        <v>17286.70670992445</v>
+        <v>17381.14045858625</v>
       </c>
       <c r="D18">
-        <v>20212.37470992445</v>
+        <v>20306.80845858626</v>
       </c>
       <c r="E18">
         <v>-3813.132</v>
@@ -2769,37 +2769,37 @@
         <v>1187.8</v>
       </c>
       <c r="M18">
-        <v>188.2082400000001</v>
+        <v>183.0752880000001</v>
       </c>
       <c r="N18">
-        <v>999.5917599999997</v>
+        <v>1004.724712</v>
       </c>
       <c r="O18">
-        <v>257.8946740799999</v>
+        <v>259.2189756959999</v>
       </c>
       <c r="P18">
-        <v>741.6970859199998</v>
+        <v>745.5057363039998</v>
       </c>
       <c r="Q18">
-        <v>2090.09708592</v>
+        <v>2093.905736304</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.072145239995905</v>
+        <v>0.0721283023489569</v>
       </c>
       <c r="T18">
         <v>0.6080439341560486</v>
       </c>
       <c r="U18">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V18">
         <v>0.258</v>
       </c>
       <c r="W18">
-        <v>0.04081000000000001</v>
+        <v>0.039697</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.31109456206593</v>
+        <v>6.488041138572451</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.06702214781222365</v>
+        <v>0.06681874847657562</v>
       </c>
       <c r="C19">
-        <v>17130.55398813533</v>
+        <v>17231.45265941477</v>
       </c>
       <c r="D19">
-        <v>20270.09498813533</v>
+        <v>20370.99365941477</v>
       </c>
       <c r="E19">
         <v>-3599.259</v>
@@ -2851,37 +2851,37 @@
         <v>1187.8</v>
       </c>
       <c r="M19">
-        <v>199.9712550000001</v>
+        <v>194.5174935000001</v>
       </c>
       <c r="N19">
-        <v>987.8287449999997</v>
+        <v>993.2825064999997</v>
       </c>
       <c r="O19">
-        <v>254.8598162099999</v>
+        <v>256.2668866769999</v>
       </c>
       <c r="P19">
-        <v>732.9689287899997</v>
+        <v>737.0156198229997</v>
       </c>
       <c r="Q19">
-        <v>2081.36892879</v>
+        <v>2085.415619823</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.07239090097858272</v>
+        <v>0.07237380539346461</v>
       </c>
       <c r="T19">
         <v>0.6137137504264346</v>
       </c>
       <c r="U19">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V19">
         <v>0.258</v>
       </c>
       <c r="W19">
-        <v>0.04081000000000001</v>
+        <v>0.039697</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.939853705473816</v>
+        <v>6.106391659832895</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.06711303402788713</v>
+        <v>0.06669820298002746</v>
       </c>
       <c r="C20">
-        <v>16868.72912418039</v>
+        <v>17082.17189642164</v>
       </c>
       <c r="D20">
-        <v>20222.14312418039</v>
+        <v>20435.58589642164</v>
       </c>
       <c r="E20">
         <v>-3385.386</v>
@@ -2933,45 +2933,45 @@
         <v>1187.8</v>
       </c>
       <c r="M20">
-        <v>217.508841</v>
+        <v>205.9596990000001</v>
       </c>
       <c r="N20">
-        <v>970.2911589999997</v>
+        <v>981.8403009999997</v>
       </c>
       <c r="O20">
-        <v>250.3351190219999</v>
+        <v>253.3147976579999</v>
       </c>
       <c r="P20">
-        <v>719.9560399779997</v>
+        <v>728.5255033419998</v>
       </c>
       <c r="Q20">
-        <v>2068.356039978</v>
+        <v>2076.925503342</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.07264255369254527</v>
+        <v>0.07262529631710665</v>
       </c>
       <c r="T20">
         <v>0.6195218548985372</v>
       </c>
       <c r="U20">
-        <v>0.05650000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V20">
         <v>0.258</v>
       </c>
       <c r="W20">
-        <v>0.04192300000000001</v>
+        <v>0.039697</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>5.460927448001985</v>
+        <v>5.767147678731068</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.06701471024355059</v>
+        <v>0.0666904414834793</v>
       </c>
       <c r="C21">
-        <v>16706.74214206371</v>
+        <v>16872.47180007003</v>
       </c>
       <c r="D21">
-        <v>20274.02914206371</v>
+        <v>20439.75880007003</v>
       </c>
       <c r="E21">
         <v>-3171.513</v>
@@ -3015,37 +3015,37 @@
         <v>1187.8</v>
       </c>
       <c r="M21">
-        <v>229.5926655000001</v>
+        <v>220.6527741</v>
       </c>
       <c r="N21">
-        <v>958.2073344999997</v>
+        <v>967.1472258999997</v>
       </c>
       <c r="O21">
-        <v>247.2174923009999</v>
+        <v>249.5239842821999</v>
       </c>
       <c r="P21">
-        <v>710.9898421989998</v>
+        <v>717.6232416177997</v>
       </c>
       <c r="Q21">
-        <v>2059.389842199</v>
+        <v>2066.0232416178</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.07290042005376615</v>
+        <v>0.07288299689318431</v>
       </c>
       <c r="T21">
         <v>0.6254733693576054</v>
       </c>
       <c r="U21">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V21">
         <v>0.258</v>
       </c>
       <c r="W21">
-        <v>0.04192300000000001</v>
+        <v>0.0402906</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.173510213896617</v>
+        <v>5.383118362525947</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.06691638645921405</v>
+        <v>0.06657583198693112</v>
       </c>
       <c r="C22">
-        <v>16545.02210338138</v>
+        <v>16720.41661643094</v>
       </c>
       <c r="D22">
-        <v>20326.18210338138</v>
+        <v>20501.57661643094</v>
       </c>
       <c r="E22">
         <v>-2957.639999999999</v>
@@ -3097,37 +3097,37 @@
         <v>1187.8</v>
       </c>
       <c r="M22">
-        <v>241.6764900000001</v>
+        <v>232.2660780000001</v>
       </c>
       <c r="N22">
-        <v>946.1235099999997</v>
+        <v>955.5339219999996</v>
       </c>
       <c r="O22">
-        <v>244.0998655799999</v>
+        <v>246.5277518759999</v>
       </c>
       <c r="P22">
-        <v>702.0236444199998</v>
+        <v>709.0061701239997</v>
       </c>
       <c r="Q22">
-        <v>2050.42364442</v>
+        <v>2057.406170124</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.07316473307401755</v>
+        <v>0.0731471399836639</v>
       </c>
       <c r="T22">
         <v>0.6315736716781504</v>
       </c>
       <c r="U22">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V22">
         <v>0.258</v>
       </c>
       <c r="W22">
-        <v>0.04192300000000001</v>
+        <v>0.0402906</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.914834703201786</v>
+        <v>5.113962444399648</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.06681806267487751</v>
+        <v>0.06646122249038296</v>
       </c>
       <c r="C23">
-        <v>16383.57107350415</v>
+        <v>16568.73648956747</v>
       </c>
       <c r="D23">
-        <v>20378.60407350415</v>
+        <v>20563.76948956747</v>
       </c>
       <c r="E23">
         <v>-2743.767</v>
@@ -3179,37 +3179,37 @@
         <v>1187.8</v>
       </c>
       <c r="M23">
-        <v>253.7603145000001</v>
+        <v>243.8793819000001</v>
       </c>
       <c r="N23">
-        <v>934.0396854999997</v>
+        <v>943.9206180999997</v>
       </c>
       <c r="O23">
-        <v>240.9822388589999</v>
+        <v>243.5315194697999</v>
       </c>
       <c r="P23">
-        <v>693.0574466409997</v>
+        <v>700.3890986301998</v>
       </c>
       <c r="Q23">
-        <v>2041.457446641</v>
+        <v>2048.7890986302</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.07343573756313608</v>
+        <v>0.07341797024099109</v>
       </c>
       <c r="T23">
         <v>0.6378284120321267</v>
       </c>
       <c r="U23">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V23">
         <v>0.258</v>
       </c>
       <c r="W23">
-        <v>0.04192300000000001</v>
+        <v>0.0402906</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.680794955430272</v>
+        <v>4.870440423237761</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.06671973889054097</v>
+        <v>0.06634661299383479</v>
       </c>
       <c r="C24">
-        <v>16222.39113916455</v>
+        <v>16417.43484314328</v>
       </c>
       <c r="D24">
-        <v>20431.29713916456</v>
+        <v>20626.34084314329</v>
       </c>
       <c r="E24">
         <v>-2529.893999999999</v>
@@ -3261,37 +3261,37 @@
         <v>1187.8</v>
       </c>
       <c r="M24">
-        <v>265.8441390000001</v>
+        <v>255.4926858000001</v>
       </c>
       <c r="N24">
-        <v>921.9558609999997</v>
+        <v>932.3073141999996</v>
       </c>
       <c r="O24">
-        <v>237.8646121379999</v>
+        <v>240.5352870635999</v>
       </c>
       <c r="P24">
-        <v>684.0912488619997</v>
+        <v>691.7720271363997</v>
       </c>
       <c r="Q24">
-        <v>2032.491248862</v>
+        <v>2040.1720271364</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.07371369088530894</v>
+        <v>0.07369574486389076</v>
       </c>
       <c r="T24">
         <v>0.6442435303438975</v>
       </c>
       <c r="U24">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V24">
         <v>0.258</v>
       </c>
       <c r="W24">
-        <v>0.04192300000000001</v>
+        <v>0.0402906</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.46803154836526</v>
+        <v>4.649056767636043</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.06662141510620442</v>
+        <v>0.06623200349728663</v>
       </c>
       <c r="C25">
-        <v>16061.48440873377</v>
+        <v>16266.51514261928</v>
       </c>
       <c r="D25">
-        <v>20484.26340873377</v>
+        <v>20689.29414261928</v>
       </c>
       <c r="E25">
         <v>-2316.021</v>
@@ -3343,37 +3343,37 @@
         <v>1187.8</v>
       </c>
       <c r="M25">
-        <v>277.9279635000001</v>
+        <v>267.1059897000001</v>
       </c>
       <c r="N25">
-        <v>909.8720364999997</v>
+        <v>920.6940102999997</v>
       </c>
       <c r="O25">
-        <v>234.7469854169999</v>
+        <v>237.5390546573999</v>
       </c>
       <c r="P25">
-        <v>675.1250510829998</v>
+        <v>683.1549556425998</v>
       </c>
       <c r="Q25">
-        <v>2023.525051083</v>
+        <v>2031.5549556426</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.07399886377429146</v>
+        <v>0.07398073441206054</v>
       </c>
       <c r="T25">
         <v>0.6508252751053245</v>
       </c>
       <c r="U25">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V25">
         <v>0.258</v>
       </c>
       <c r="W25">
-        <v>0.04192300000000001</v>
+        <v>0.0402906</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.273769307131988</v>
+        <v>4.446923864695346</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.06677240332186789</v>
+        <v>0.06611739400073846</v>
       </c>
       <c r="C26">
-        <v>15766.38770510141</v>
+        <v>16115.98089589333</v>
       </c>
       <c r="D26">
-        <v>20403.03970510141</v>
+        <v>20752.63289589333</v>
       </c>
       <c r="E26">
         <v>-2102.148</v>
@@ -3425,45 +3425,45 @@
         <v>1187.8</v>
       </c>
       <c r="M26">
-        <v>297.1979208000001</v>
+        <v>278.7192936000001</v>
       </c>
       <c r="N26">
-        <v>890.6020791999997</v>
+        <v>909.0807063999996</v>
       </c>
       <c r="O26">
-        <v>229.7753364335999</v>
+        <v>234.5428222511999</v>
       </c>
       <c r="P26">
-        <v>660.8267427663998</v>
+        <v>674.5378841487997</v>
       </c>
       <c r="Q26">
-        <v>2009.2267427664</v>
+        <v>2022.9378841488</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.07429154121298406</v>
+        <v>0.07427322368518217</v>
       </c>
       <c r="T26">
         <v>0.6575802236762629</v>
       </c>
       <c r="U26">
-        <v>0.05790000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V26">
         <v>0.258</v>
       </c>
       <c r="W26">
-        <v>0.0429618</v>
+        <v>0.0402906</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>3.996663222954821</v>
+        <v>4.261635370333041</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.06668446753753136</v>
+        <v>0.0661882845041903</v>
       </c>
       <c r="C27">
-        <v>15599.74101222523</v>
+        <v>15862.88470803122</v>
       </c>
       <c r="D27">
-        <v>20450.26601222523</v>
+        <v>20713.40970803122</v>
       </c>
       <c r="E27">
         <v>-1888.275</v>
@@ -3507,37 +3507,37 @@
         <v>1187.8</v>
       </c>
       <c r="M27">
-        <v>309.5811675000001</v>
+        <v>295.6794225000001</v>
       </c>
       <c r="N27">
-        <v>878.2188324999996</v>
+        <v>892.1205774999996</v>
       </c>
       <c r="O27">
-        <v>226.5804587849999</v>
+        <v>230.1671089949999</v>
       </c>
       <c r="P27">
-        <v>651.6383737149997</v>
+        <v>661.9534685049997</v>
       </c>
       <c r="Q27">
-        <v>2000.038373715</v>
+        <v>2010.353468505</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.07459202338337514</v>
+        <v>0.07457351267225372</v>
       </c>
       <c r="T27">
         <v>0.6645153042090929</v>
       </c>
       <c r="U27">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V27">
         <v>0.258</v>
       </c>
       <c r="W27">
-        <v>0.0429618</v>
+        <v>0.04103260000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.836796694036627</v>
+        <v>4.017188582002182</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.06659653175319483</v>
+        <v>0.06608109500764212</v>
       </c>
       <c r="C28">
-        <v>15433.31345321917</v>
+        <v>15708.37641928318</v>
       </c>
       <c r="D28">
-        <v>20497.71145321917</v>
+        <v>20772.77441928318</v>
       </c>
       <c r="E28">
         <v>-1674.401999999999</v>
@@ -3589,37 +3589,37 @@
         <v>1187.8</v>
       </c>
       <c r="M28">
-        <v>321.9644142000001</v>
+        <v>307.5065994000001</v>
       </c>
       <c r="N28">
-        <v>865.8355857999995</v>
+        <v>880.2934005999996</v>
       </c>
       <c r="O28">
-        <v>223.3855811363999</v>
+        <v>227.1156973547999</v>
       </c>
       <c r="P28">
-        <v>642.4500046635997</v>
+        <v>653.1777032451997</v>
       </c>
       <c r="Q28">
-        <v>1990.8500046636</v>
+        <v>2001.5777032452</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.07490062669350651</v>
+        <v>0.07488191757789475</v>
       </c>
       <c r="T28">
         <v>0.6716378193509183</v>
       </c>
       <c r="U28">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V28">
         <v>0.258</v>
       </c>
       <c r="W28">
-        <v>0.0429618</v>
+        <v>0.04103260000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.689227590419833</v>
+        <v>3.862681328848252</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.06650859596885828</v>
+        <v>0.06597390551109396</v>
       </c>
       <c r="C29">
-        <v>15267.10655682819</v>
+        <v>15554.20938755694</v>
       </c>
       <c r="D29">
-        <v>20545.37755682819</v>
+        <v>20832.48038755695</v>
       </c>
       <c r="E29">
         <v>-1460.529</v>
@@ -3671,37 +3671,37 @@
         <v>1187.8</v>
       </c>
       <c r="M29">
-        <v>334.3476609000001</v>
+        <v>319.3337763000001</v>
       </c>
       <c r="N29">
-        <v>853.4523390999996</v>
+        <v>868.4662236999995</v>
       </c>
       <c r="O29">
-        <v>220.1907034877999</v>
+        <v>224.0642857145999</v>
       </c>
       <c r="P29">
-        <v>633.2616356121997</v>
+        <v>644.4019379853996</v>
       </c>
       <c r="Q29">
-        <v>1981.6616356122</v>
+        <v>1992.8019379854</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.07521768488884696</v>
+        <v>0.07519877193300542</v>
       </c>
       <c r="T29">
         <v>0.6789554718938896</v>
       </c>
       <c r="U29">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V29">
         <v>0.258</v>
       </c>
       <c r="W29">
-        <v>0.0429618</v>
+        <v>0.04103260000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.552589531515395</v>
+        <v>3.719619057409428</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.06642066018452175</v>
+        <v>0.06586671601454579</v>
       </c>
       <c r="C30">
-        <v>15101.12186605038</v>
+        <v>15400.38656389973</v>
       </c>
       <c r="D30">
-        <v>20593.26586605038</v>
+        <v>20892.53056389973</v>
       </c>
       <c r="E30">
         <v>-1246.655999999999</v>
@@ -3753,37 +3753,37 @@
         <v>1187.8</v>
       </c>
       <c r="M30">
-        <v>346.7309076000001</v>
+        <v>331.1609532000001</v>
       </c>
       <c r="N30">
-        <v>841.0690923999996</v>
+        <v>856.6390467999996</v>
       </c>
       <c r="O30">
-        <v>216.9958258391999</v>
+        <v>221.0128740743999</v>
       </c>
       <c r="P30">
-        <v>624.0732665607997</v>
+        <v>635.6261727255996</v>
       </c>
       <c r="Q30">
-        <v>1972.4732665608</v>
+        <v>1984.0261727256</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.07554355025628021</v>
+        <v>0.07552442779798026</v>
       </c>
       <c r="T30">
         <v>0.6864763925630546</v>
       </c>
       <c r="U30">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V30">
         <v>0.258</v>
       </c>
       <c r="W30">
-        <v>0.0429618</v>
+        <v>0.04103260000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.425711333961274</v>
+        <v>3.586775519644806</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.0663327244001852</v>
+        <v>0.06575952651799762</v>
       </c>
       <c r="C31">
-        <v>14935.36093830351</v>
+        <v>15246.910933483</v>
       </c>
       <c r="D31">
-        <v>20641.37793830351</v>
+        <v>20952.927933483</v>
       </c>
       <c r="E31">
         <v>-1032.783</v>
@@ -3835,37 +3835,37 @@
         <v>1187.8</v>
       </c>
       <c r="M31">
-        <v>359.1141543000001</v>
+        <v>342.9881301</v>
       </c>
       <c r="N31">
-        <v>828.6858456999996</v>
+        <v>844.8118698999997</v>
       </c>
       <c r="O31">
-        <v>213.8009481905999</v>
+        <v>217.9614624341999</v>
       </c>
       <c r="P31">
-        <v>614.8848975093997</v>
+        <v>626.8504074657998</v>
       </c>
       <c r="Q31">
-        <v>1963.2848975094</v>
+        <v>1975.2504074658</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.07587859492983831</v>
+        <v>0.07585925706760227</v>
       </c>
       <c r="T31">
         <v>0.6942091701524775</v>
       </c>
       <c r="U31">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V31">
         <v>0.258</v>
       </c>
       <c r="W31">
-        <v>0.0429618</v>
+        <v>0.04103260000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.307583356928127</v>
+        <v>3.463093605174296</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.06624478861584866</v>
+        <v>0.06565233702144944</v>
       </c>
       <c r="C32">
-        <v>14769.82534559376</v>
+        <v>15093.78551609712</v>
       </c>
       <c r="D32">
-        <v>20689.71534559376</v>
+        <v>21013.67551609712</v>
       </c>
       <c r="E32">
         <v>-818.9099999999999</v>
@@ -3917,37 +3917,37 @@
         <v>1187.8</v>
       </c>
       <c r="M32">
-        <v>371.4974010000001</v>
+        <v>354.8153070000001</v>
       </c>
       <c r="N32">
-        <v>816.3025989999996</v>
+        <v>832.9846929999997</v>
       </c>
       <c r="O32">
-        <v>210.6060705419999</v>
+        <v>214.9100507939999</v>
       </c>
       <c r="P32">
-        <v>605.6965284579998</v>
+        <v>618.0746422059997</v>
       </c>
       <c r="Q32">
-        <v>1954.096528458</v>
+        <v>1966.474642206</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.07622321230835524</v>
+        <v>0.07620365288778493</v>
       </c>
       <c r="T32">
         <v>0.7021628842444557</v>
       </c>
       <c r="U32">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V32">
         <v>0.258</v>
       </c>
       <c r="W32">
-        <v>0.0429618</v>
+        <v>0.04103260000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.197330578363856</v>
+        <v>3.347657151668486</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.06615685283151213</v>
+        <v>0.06554514752490129</v>
       </c>
       <c r="C33">
-        <v>14604.51667468703</v>
+        <v>14941.01336665469</v>
       </c>
       <c r="D33">
-        <v>20738.27967468703</v>
+        <v>21074.7763666547</v>
       </c>
       <c r="E33">
         <v>-605.0369999999994</v>
@@ -3999,37 +3999,37 @@
         <v>1187.8</v>
       </c>
       <c r="M33">
-        <v>383.8806477000001</v>
+        <v>366.6424839000001</v>
       </c>
       <c r="N33">
-        <v>803.9193522999997</v>
+        <v>821.1575160999996</v>
       </c>
       <c r="O33">
-        <v>207.4111928933999</v>
+        <v>211.8586391537999</v>
       </c>
       <c r="P33">
-        <v>596.5081594065998</v>
+        <v>609.2988769461997</v>
       </c>
       <c r="Q33">
-        <v>1944.9081594066</v>
+        <v>1957.6988769462</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.0765778185963944</v>
+        <v>0.07655803119550911</v>
       </c>
       <c r="T33">
         <v>0.7103471407738824</v>
       </c>
       <c r="U33">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V33">
         <v>0.258</v>
       </c>
       <c r="W33">
-        <v>0.0429618</v>
+        <v>0.04103260000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.094190882287603</v>
+        <v>3.239668211292083</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.06668626104717558</v>
+        <v>0.06543795802835312</v>
       </c>
       <c r="C34">
-        <v>14101.66461588859</v>
+        <v>14788.59757570266</v>
       </c>
       <c r="D34">
-        <v>20449.30061588859</v>
+        <v>21136.23357570267</v>
       </c>
       <c r="E34">
         <v>-391.1639999999989</v>
@@ -4081,45 +4081,45 @@
         <v>1187.8</v>
       </c>
       <c r="M34">
-        <v>414.0581280000001</v>
+        <v>378.4696608000002</v>
       </c>
       <c r="N34">
-        <v>773.7418719999996</v>
+        <v>809.3303391999996</v>
       </c>
       <c r="O34">
-        <v>199.6254029759999</v>
+        <v>208.8072275135999</v>
       </c>
       <c r="P34">
-        <v>574.1164690239997</v>
+        <v>600.5231116863997</v>
       </c>
       <c r="Q34">
-        <v>1922.516469024</v>
+        <v>1948.9231116864</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.07694285448114058</v>
+        <v>0.07692283239463693</v>
       </c>
       <c r="T34">
         <v>0.7187721107306452</v>
       </c>
       <c r="U34">
-        <v>0.06050000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V34">
         <v>0.258</v>
       </c>
       <c r="W34">
-        <v>0.044891</v>
+        <v>0.04103260000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y34">
-        <v>2.868679346393605</v>
+        <v>3.138428579689205</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.06661761726283905</v>
+        <v>0.06533076853180493</v>
       </c>
       <c r="C35">
-        <v>13924.80578700889</v>
+        <v>14636.54126994341</v>
       </c>
       <c r="D35">
-        <v>20486.31478700889</v>
+        <v>21198.05026994341</v>
       </c>
       <c r="E35">
         <v>-177.2909999999993</v>
@@ -4163,45 +4163,45 @@
         <v>1187.8</v>
       </c>
       <c r="M35">
-        <v>426.9974445000001</v>
+        <v>390.2968377000001</v>
       </c>
       <c r="N35">
-        <v>760.8025554999997</v>
+        <v>797.5031622999995</v>
       </c>
       <c r="O35">
-        <v>196.2870593189999</v>
+        <v>205.7558158733999</v>
       </c>
       <c r="P35">
-        <v>564.5154961809998</v>
+        <v>591.7473464265996</v>
       </c>
       <c r="Q35">
-        <v>1912.915496181</v>
+        <v>1940.1473464266</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.07731878695946127</v>
+        <v>0.07729852318179842</v>
       </c>
       <c r="T35">
         <v>0.7274485723279083</v>
       </c>
       <c r="U35">
-        <v>0.06050000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V35">
         <v>0.258</v>
       </c>
       <c r="W35">
-        <v>0.044891</v>
+        <v>0.04103260000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>2.781749669230162</v>
+        <v>3.043324683334987</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.06654897347850251</v>
+        <v>0.06585427903525677</v>
       </c>
       <c r="C36">
-        <v>13748.08119579702</v>
+        <v>14124.13848554221</v>
       </c>
       <c r="D36">
-        <v>20523.46319579702</v>
+        <v>20899.52048554221</v>
       </c>
       <c r="E36">
         <v>36.58200000000124</v>
@@ -4245,37 +4245,37 @@
         <v>1187.8</v>
       </c>
       <c r="M36">
-        <v>439.9367610000002</v>
+        <v>420.3032196000001</v>
       </c>
       <c r="N36">
-        <v>747.8632389999996</v>
+        <v>767.4967803999996</v>
       </c>
       <c r="O36">
-        <v>192.9487156619999</v>
+        <v>198.0141693431999</v>
       </c>
       <c r="P36">
-        <v>554.9145233379996</v>
+        <v>569.4826110567997</v>
       </c>
       <c r="Q36">
-        <v>1903.314523338</v>
+        <v>1917.8826110568</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.07770611133106442</v>
+        <v>0.07768559853826784</v>
       </c>
       <c r="T36">
         <v>0.7363879570038764</v>
       </c>
       <c r="U36">
-        <v>0.06050000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V36">
         <v>0.258</v>
       </c>
       <c r="W36">
-        <v>0.044891</v>
+        <v>0.0428876</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.699933502488098</v>
+        <v>2.826054963676988</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.06648032969416598</v>
+        <v>0.06576563953870861</v>
       </c>
       <c r="C37">
-        <v>13571.49157383034</v>
+        <v>13960.21908135855</v>
       </c>
       <c r="D37">
-        <v>20560.74657383035</v>
+        <v>20949.47408135855</v>
       </c>
       <c r="E37">
         <v>250.4550000000017</v>
@@ -4327,37 +4327,37 @@
         <v>1187.8</v>
       </c>
       <c r="M37">
-        <v>452.8760775000002</v>
+        <v>432.6650790000002</v>
       </c>
       <c r="N37">
-        <v>734.9239224999995</v>
+        <v>755.1349209999996</v>
       </c>
       <c r="O37">
-        <v>189.6103720049999</v>
+        <v>194.8248096179999</v>
       </c>
       <c r="P37">
-        <v>545.3135504949996</v>
+        <v>560.3101113819997</v>
       </c>
       <c r="Q37">
-        <v>1893.713550495</v>
+        <v>1908.710111382</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.07810535337563997</v>
+        <v>0.07808458390570555</v>
       </c>
       <c r="T37">
         <v>0.7456023996698743</v>
       </c>
       <c r="U37">
-        <v>0.06050000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V37">
         <v>0.258</v>
       </c>
       <c r="W37">
-        <v>0.044891</v>
+        <v>0.0428876</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.622792545274153</v>
+        <v>2.74531053614336</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.06641168590982945</v>
+        <v>0.06567700004216044</v>
       </c>
       <c r="C38">
-        <v>13395.03765801191</v>
+        <v>13796.53904538316</v>
       </c>
       <c r="D38">
-        <v>20598.16565801191</v>
+        <v>20999.66704538316</v>
       </c>
       <c r="E38">
         <v>464.3280000000004</v>
@@ -4409,37 +4409,37 @@
         <v>1187.8</v>
       </c>
       <c r="M38">
-        <v>465.8153940000001</v>
+        <v>445.0269384000001</v>
       </c>
       <c r="N38">
-        <v>721.9846059999996</v>
+        <v>742.7730615999997</v>
       </c>
       <c r="O38">
-        <v>186.2720283479999</v>
+        <v>191.6354498927999</v>
       </c>
       <c r="P38">
-        <v>535.7125776519997</v>
+        <v>551.1376117071998</v>
       </c>
       <c r="Q38">
-        <v>1884.112577652</v>
+        <v>1899.5376117072</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.0785170717341085</v>
+        <v>0.07849603756587568</v>
       </c>
       <c r="T38">
         <v>0.7551047936691846</v>
       </c>
       <c r="U38">
-        <v>0.06050000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V38">
         <v>0.258</v>
       </c>
       <c r="W38">
-        <v>0.044891</v>
+        <v>0.0428876</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.549937196794315</v>
+        <v>2.669051910139379</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.06708430012549291</v>
+        <v>0.06558836054561228</v>
       </c>
       <c r="C39">
-        <v>12820.27768137295</v>
+        <v>13633.1001022591</v>
       </c>
       <c r="D39">
-        <v>20237.27868137295</v>
+        <v>21050.1011022591</v>
       </c>
       <c r="E39">
         <v>678.2010000000009</v>
@@ -4491,45 +4491,45 @@
         <v>1187.8</v>
       </c>
       <c r="M39">
-        <v>500.1206232000001</v>
+        <v>457.3887978000001</v>
       </c>
       <c r="N39">
-        <v>687.6793767999995</v>
+        <v>730.4112021999996</v>
       </c>
       <c r="O39">
-        <v>177.4212792143999</v>
+        <v>188.4460901675999</v>
       </c>
       <c r="P39">
-        <v>510.2580975855997</v>
+        <v>541.9651120323997</v>
       </c>
       <c r="Q39">
-        <v>1858.6580975856</v>
+        <v>1890.3651120324</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.0789418605166554</v>
+        <v>0.07892055324700362</v>
       </c>
       <c r="T39">
         <v>0.7649088509700603</v>
       </c>
       <c r="U39">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V39">
         <v>0.258</v>
       </c>
       <c r="W39">
-        <v>0.0468944</v>
+        <v>0.0428876</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.375027033278318</v>
+        <v>2.596915372027503</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.06703569034115636</v>
+        <v>0.06549972104906411</v>
       </c>
       <c r="C40">
-        <v>12632.06149252716</v>
+        <v>13469.90399323731</v>
       </c>
       <c r="D40">
-        <v>20262.93549252717</v>
+        <v>21100.77799323731</v>
       </c>
       <c r="E40">
         <v>892.0740000000005</v>
@@ -4573,45 +4573,45 @@
         <v>1187.8</v>
       </c>
       <c r="M40">
-        <v>513.6373968000001</v>
+        <v>469.7506572000001</v>
       </c>
       <c r="N40">
-        <v>674.1626031999996</v>
+        <v>718.0493427999996</v>
       </c>
       <c r="O40">
-        <v>173.9339516255999</v>
+        <v>185.2567304423999</v>
       </c>
       <c r="P40">
-        <v>500.2286515743997</v>
+        <v>532.7926123575998</v>
       </c>
       <c r="Q40">
-        <v>1848.6286515744</v>
+        <v>1881.1926123576</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.07938035216315542</v>
+        <v>0.07935876298236147</v>
       </c>
       <c r="T40">
         <v>0.7750291681838676</v>
       </c>
       <c r="U40">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V40">
         <v>0.258</v>
       </c>
       <c r="W40">
-        <v>0.0468944</v>
+        <v>0.0428876</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.312526321876256</v>
+        <v>2.528575493816253</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.06698708055681983</v>
+        <v>0.06642391155251594</v>
       </c>
       <c r="C41">
-        <v>12443.91044164633</v>
+        <v>12739.35077532824</v>
       </c>
       <c r="D41">
-        <v>20288.65744164633</v>
+        <v>20584.09777532825</v>
       </c>
       <c r="E41">
         <v>1105.947000000002</v>
@@ -4655,37 +4655,37 @@
         <v>1187.8</v>
       </c>
       <c r="M41">
-        <v>527.1541704000002</v>
+        <v>511.3061811000002</v>
       </c>
       <c r="N41">
-        <v>660.6458295999995</v>
+        <v>676.4938188999995</v>
       </c>
       <c r="O41">
-        <v>170.4466240367999</v>
+        <v>174.5354052761999</v>
       </c>
       <c r="P41">
-        <v>490.1992055631996</v>
+        <v>501.9584136237996</v>
       </c>
       <c r="Q41">
-        <v>1838.5992055632</v>
+        <v>1850.3584136238</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.07983322058495054</v>
+        <v>0.07981134025002612</v>
       </c>
       <c r="T41">
         <v>0.785481299076816</v>
       </c>
       <c r="U41">
-        <v>0.06320000000000001</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V41">
         <v>0.258</v>
       </c>
       <c r="W41">
-        <v>0.0468944</v>
+        <v>0.04548460000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.253230775161481</v>
+        <v>2.323069901960939</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.0683334307724833</v>
+        <v>0.06636124205596777</v>
       </c>
       <c r="C42">
-        <v>11540.93762847811</v>
+        <v>12559.71287660862</v>
       </c>
       <c r="D42">
-        <v>19599.55762847812</v>
+        <v>20618.33287660863</v>
       </c>
       <c r="E42">
         <v>1319.820000000002</v>
@@ -4737,45 +4737,45 @@
         <v>1187.8</v>
       </c>
       <c r="M42">
-        <v>580.8790680000003</v>
+        <v>524.4165960000001</v>
       </c>
       <c r="N42">
-        <v>606.9209319999994</v>
+        <v>663.3834039999996</v>
       </c>
       <c r="O42">
-        <v>156.5856004559999</v>
+        <v>171.1529182319999</v>
       </c>
       <c r="P42">
-        <v>450.3353315439996</v>
+        <v>492.2304857679997</v>
       </c>
       <c r="Q42">
-        <v>1798.735331544</v>
+        <v>1840.630485768</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.08030118462080549</v>
+        <v>0.08027900342661295</v>
       </c>
       <c r="T42">
         <v>0.7962818343328628</v>
       </c>
       <c r="U42">
-        <v>0.06790000000000002</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V42">
         <v>0.258</v>
       </c>
       <c r="W42">
-        <v>0.05038180000000001</v>
+        <v>0.04548460000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.044831816869667</v>
+        <v>2.264993154411916</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.07114894098814675</v>
+        <v>0.0671503885594196</v>
       </c>
       <c r="C43">
-        <v>10027.27387514762</v>
+        <v>11922.88580004275</v>
       </c>
       <c r="D43">
-        <v>18299.76687514762</v>
+        <v>20195.37880004275</v>
       </c>
       <c r="E43">
         <v>1533.693000000001</v>
@@ -4819,45 +4819,45 @@
         <v>1187.8</v>
       </c>
       <c r="M43">
-        <v>676.9508196000002</v>
+        <v>562.0796313000002</v>
       </c>
       <c r="N43">
-        <v>510.8491803999996</v>
+        <v>625.7203686999995</v>
       </c>
       <c r="O43">
-        <v>131.7990885431999</v>
+        <v>161.4358551245999</v>
       </c>
       <c r="P43">
-        <v>379.0500918567997</v>
+        <v>464.2845135753996</v>
       </c>
       <c r="Q43">
-        <v>1727.4500918568</v>
+        <v>1812.6845135754</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.08078501184431652</v>
+        <v>0.08076251959223661</v>
       </c>
       <c r="T43">
         <v>0.8074484894280974</v>
       </c>
       <c r="U43">
-        <v>0.0772</v>
+        <v>0.0641</v>
       </c>
       <c r="V43">
         <v>0.258</v>
       </c>
       <c r="W43">
-        <v>0.0572824</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>1.75463263446797</v>
+        <v>2.113223703290597</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.07266891920381022</v>
+        <v>0.06710849506287143</v>
       </c>
       <c r="C44">
-        <v>9180.877998899876</v>
+        <v>11731.02958242397</v>
       </c>
       <c r="D44">
-        <v>17667.24399889988</v>
+        <v>20217.39558242397</v>
       </c>
       <c r="E44">
         <v>1747.566000000001</v>
@@ -4901,45 +4901,45 @@
         <v>1187.8</v>
       </c>
       <c r="M44">
-        <v>735.6803454000001</v>
+        <v>575.7888906000001</v>
       </c>
       <c r="N44">
-        <v>452.1196545999996</v>
+        <v>612.0111093999997</v>
       </c>
       <c r="O44">
-        <v>116.6468708867999</v>
+        <v>157.8988662251999</v>
       </c>
       <c r="P44">
-        <v>335.4727837131998</v>
+        <v>454.1122431747997</v>
       </c>
       <c r="Q44">
-        <v>1683.8727837132</v>
+        <v>1802.5122431748</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.08128552276519002</v>
+        <v>0.08126270872908867</v>
       </c>
       <c r="T44">
         <v>0.8190002015955816</v>
       </c>
       <c r="U44">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V44">
         <v>0.258</v>
       </c>
       <c r="W44">
-        <v>0.0607698</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>1.614559920523873</v>
+        <v>2.06290885321225</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.07275906341947368</v>
+        <v>0.06706660156632328</v>
       </c>
       <c r="C45">
-        <v>8930.863127052377</v>
+        <v>11539.22142211025</v>
       </c>
       <c r="D45">
-        <v>17631.10212705238</v>
+        <v>20239.46042211026</v>
       </c>
       <c r="E45">
         <v>1961.439</v>
@@ -4983,45 +4983,45 @@
         <v>1187.8</v>
       </c>
       <c r="M45">
-        <v>753.1965441000001</v>
+        <v>589.4981499</v>
       </c>
       <c r="N45">
-        <v>434.6034558999996</v>
+        <v>598.3018500999997</v>
       </c>
       <c r="O45">
-        <v>112.1276916221999</v>
+        <v>154.3618773257999</v>
       </c>
       <c r="P45">
-        <v>322.4757642777997</v>
+        <v>443.9399727741998</v>
       </c>
       <c r="Q45">
-        <v>1670.8757642778</v>
+        <v>1792.3399727742</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.08180359547276084</v>
+        <v>0.08178044836197065</v>
       </c>
       <c r="T45">
         <v>0.8309572369970127</v>
       </c>
       <c r="U45">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V45">
         <v>0.258</v>
       </c>
       <c r="W45">
-        <v>0.0607698</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>1.577012015395411</v>
+        <v>2.014934228718942</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.07284920763513714</v>
+        <v>0.0695712520697751</v>
       </c>
       <c r="C46">
-        <v>8680.995824140015</v>
+        <v>10085.62801558429</v>
       </c>
       <c r="D46">
-        <v>17595.10782414002</v>
+        <v>18999.7400155843</v>
       </c>
       <c r="E46">
         <v>2175.312000000002</v>
@@ -5065,45 +5065,45 @@
         <v>1187.8</v>
       </c>
       <c r="M46">
-        <v>770.7127428000002</v>
+        <v>676.6086228000001</v>
       </c>
       <c r="N46">
-        <v>417.0872571999995</v>
+        <v>511.1913771999996</v>
       </c>
       <c r="O46">
-        <v>107.6085123575999</v>
+        <v>131.8873753175999</v>
       </c>
       <c r="P46">
-        <v>309.4787448423996</v>
+        <v>379.3040018823997</v>
       </c>
       <c r="Q46">
-        <v>1657.8787448424</v>
+        <v>1727.7040018824</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.0823401707770306</v>
+        <v>0.08231667869602696</v>
       </c>
       <c r="T46">
         <v>0.8433413093770662</v>
       </c>
       <c r="U46">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V46">
         <v>0.258</v>
       </c>
       <c r="W46">
-        <v>0.0607698</v>
+        <v>0.0533498</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>1.541170833227333</v>
+        <v>1.755520045080926</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.07293935185080061</v>
+        <v>0.07088944457322693</v>
       </c>
       <c r="C47">
-        <v>8431.275188207963</v>
+        <v>9278.386224084339</v>
       </c>
       <c r="D47">
-        <v>17559.26018820797</v>
+        <v>18406.37122408434</v>
       </c>
       <c r="E47">
         <v>2389.185000000001</v>
@@ -5147,37 +5147,37 @@
         <v>1187.8</v>
       </c>
       <c r="M47">
-        <v>788.2289415000001</v>
+        <v>729.5208030000002</v>
       </c>
       <c r="N47">
-        <v>399.5710584999996</v>
+        <v>458.2791969999995</v>
       </c>
       <c r="O47">
-        <v>103.0893330929999</v>
+        <v>118.2360328259999</v>
       </c>
       <c r="P47">
-        <v>296.4817254069997</v>
+        <v>340.0431641739996</v>
       </c>
       <c r="Q47">
-        <v>1644.881725407</v>
+        <v>1688.443164174</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.08289625791054656</v>
+        <v>0.08287240831495805</v>
       </c>
       <c r="T47">
         <v>0.856175711661849</v>
       </c>
       <c r="U47">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V47">
         <v>0.258</v>
       </c>
       <c r="W47">
-        <v>0.0607698</v>
+        <v>0.0562436</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.506922592488948</v>
+        <v>1.62819208871827</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.09117343329104195</v>
+        <v>0.07093436507667877</v>
       </c>
       <c r="C48">
-        <v>3092.897758464827</v>
+        <v>9044.945106678113</v>
       </c>
       <c r="D48">
-        <v>12434.75575846483</v>
+        <v>18386.80310667812</v>
       </c>
       <c r="E48">
         <v>2603.058000000001</v>
@@ -5229,45 +5229,45 @@
         <v>1187.8</v>
       </c>
       <c r="M48">
-        <v>1287.8148822</v>
+        <v>745.7323764000001</v>
       </c>
       <c r="N48">
-        <v>-100.0148822000006</v>
+        <v>442.0676235999996</v>
       </c>
       <c r="O48">
-        <v>-25.80383960760014</v>
+        <v>114.0534468887999</v>
       </c>
       <c r="P48">
-        <v>-74.21104259240042</v>
+        <v>328.0141767111997</v>
       </c>
       <c r="Q48">
-        <v>1274.1889574076</v>
+        <v>1676.4141767112</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.08386693034214153</v>
+        <v>0.08344872051236808</v>
       </c>
       <c r="T48">
-        <v>0.8785786764545619</v>
+        <v>0.8694854621794016</v>
       </c>
       <c r="U48">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V48">
-        <v>0.237963083231715</v>
+        <v>0.258</v>
       </c>
       <c r="W48">
-        <v>0.09975063240496852</v>
+        <v>0.0562436</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.9223375319058721</v>
+        <v>1.592796608528742</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.09202443329104196</v>
+        <v>0.07097928558013059</v>
       </c>
       <c r="C49">
-        <v>2711.933693990142</v>
+        <v>8811.545551464384</v>
       </c>
       <c r="D49">
-        <v>12267.66469399015</v>
+        <v>18367.27655146439</v>
       </c>
       <c r="E49">
         <v>2816.931000000002</v>
@@ -5311,45 +5311,45 @@
         <v>1187.8</v>
       </c>
       <c r="M49">
-        <v>1315.8108579</v>
+        <v>761.9439498000003</v>
       </c>
       <c r="N49">
-        <v>-128.0108579000007</v>
+        <v>425.8560501999995</v>
       </c>
       <c r="O49">
-        <v>-33.02680133820018</v>
+        <v>109.8708609515999</v>
       </c>
       <c r="P49">
-        <v>-94.98405656180051</v>
+        <v>315.9851892483996</v>
       </c>
       <c r="Q49">
-        <v>1253.4159434382</v>
+        <v>1664.3851892484</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.08458517431086118</v>
+        <v>0.08404678033986904</v>
       </c>
       <c r="T49">
-        <v>0.895155632614082</v>
+        <v>0.8832974674334654</v>
       </c>
       <c r="U49">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V49">
-        <v>0.2329000389076359</v>
+        <v>0.258</v>
       </c>
       <c r="W49">
-        <v>0.1004133849069905</v>
+        <v>0.0562436</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y49">
-        <v>0.9027133290993641</v>
+        <v>1.558907318985577</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.09287543329104193</v>
+        <v>0.07102420608358243</v>
       </c>
       <c r="C50">
-        <v>2335.40063462441</v>
+        <v>8578.187426168019</v>
       </c>
       <c r="D50">
-        <v>12105.00463462441</v>
+        <v>18347.79142616802</v>
       </c>
       <c r="E50">
         <v>3030.804</v>
@@ -5393,45 +5393,45 @@
         <v>1187.8</v>
       </c>
       <c r="M50">
-        <v>1343.8068336</v>
+        <v>778.1555232000001</v>
       </c>
       <c r="N50">
-        <v>-156.0068336000004</v>
+        <v>409.6444767999997</v>
       </c>
       <c r="O50">
-        <v>-40.2497630688001</v>
+        <v>105.6882750143999</v>
       </c>
       <c r="P50">
-        <v>-115.7570705312003</v>
+        <v>303.9562017855998</v>
       </c>
       <c r="Q50">
-        <v>1232.6429294688</v>
+        <v>1652.3562017856</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.08533104304760851</v>
+        <v>0.08466784246842773</v>
       </c>
       <c r="T50">
-        <v>0.9123701640105065</v>
+        <v>0.8976407036588394</v>
       </c>
       <c r="U50">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V50">
-        <v>0.2280479547637269</v>
+        <v>0.258</v>
       </c>
       <c r="W50">
-        <v>0.1010485227214282</v>
+        <v>0.0562436</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y50">
-        <v>0.8839068014097943</v>
+        <v>1.526430083173378</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.09372643329104194</v>
+        <v>0.07623196258703427</v>
       </c>
       <c r="C51">
-        <v>1963.124631359429</v>
+        <v>6354.883973784854</v>
       </c>
       <c r="D51">
-        <v>11946.60163135943</v>
+        <v>16338.36097378485</v>
       </c>
       <c r="E51">
         <v>3244.677000000001</v>
@@ -5475,45 +5475,45 @@
         <v>1187.8</v>
       </c>
       <c r="M51">
-        <v>1371.8028093</v>
+        <v>943.1799300000002</v>
       </c>
       <c r="N51">
-        <v>-184.0028093000008</v>
+        <v>244.6200699999995</v>
       </c>
       <c r="O51">
-        <v>-47.4727247994002</v>
+        <v>63.11197805999987</v>
       </c>
       <c r="P51">
-        <v>-136.5300845006006</v>
+        <v>181.5080919399996</v>
       </c>
       <c r="Q51">
-        <v>1211.869915499399</v>
+        <v>1529.90809194</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.0861061615387381</v>
+        <v>0.08531325997457698</v>
       </c>
       <c r="T51">
-        <v>0.9302597750695361</v>
+        <v>0.912546419736189</v>
       </c>
       <c r="U51">
-        <v>0.1309</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V51">
-        <v>0.2233939148705896</v>
+        <v>0.258</v>
       </c>
       <c r="W51">
-        <v>0.1016577365434398</v>
+        <v>0.06678000000000001</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>0.8658678870953084</v>
+        <v>1.259356738008621</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.09457743329104194</v>
+        <v>0.08815234001280614</v>
       </c>
       <c r="C52">
-        <v>1594.940722589599</v>
+        <v>2866.178920247334</v>
       </c>
       <c r="D52">
-        <v>11792.2907225896</v>
+        <v>13063.52892024734</v>
       </c>
       <c r="E52">
         <v>3458.550000000001</v>
@@ -5557,37 +5557,37 @@
         <v>1187.8</v>
       </c>
       <c r="M52">
-        <v>1399.798785</v>
+        <v>1268.26689</v>
       </c>
       <c r="N52">
-        <v>-211.9987850000007</v>
+        <v>-80.4668900000006</v>
       </c>
       <c r="O52">
-        <v>-54.69568653000017</v>
+        <v>-20.76045762000016</v>
       </c>
       <c r="P52">
-        <v>-157.3030984700005</v>
+        <v>-59.70643238000045</v>
       </c>
       <c r="Q52">
-        <v>1191.09690153</v>
+        <v>1288.69356762</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.08691228476951285</v>
+        <v>0.08636209821304125</v>
       </c>
       <c r="T52">
-        <v>0.9488649705709269</v>
+        <v>0.9367690118485277</v>
       </c>
       <c r="U52">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V52">
-        <v>0.2189260365731778</v>
+        <v>0.2416308447506659</v>
       </c>
       <c r="W52">
-        <v>0.102242581812571</v>
+        <v>0.08994258181257103</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8485505293534024</v>
+        <v>0.9365536618242863</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.09542843329104195</v>
+        <v>0.08888034001280613</v>
       </c>
       <c r="C53">
-        <v>1230.692361074802</v>
+        <v>2494.327253319532</v>
       </c>
       <c r="D53">
-        <v>11641.9153610748</v>
+        <v>12905.55025331953</v>
       </c>
       <c r="E53">
         <v>3672.423000000001</v>
@@ -5639,37 +5639,37 @@
         <v>1187.8</v>
       </c>
       <c r="M53">
-        <v>1427.7947607</v>
+        <v>1293.6322278</v>
       </c>
       <c r="N53">
-        <v>-239.9947607000006</v>
+        <v>-105.8322278000005</v>
       </c>
       <c r="O53">
-        <v>-61.91864826060016</v>
+        <v>-27.30471477240013</v>
       </c>
       <c r="P53">
-        <v>-178.0761124394004</v>
+        <v>-78.52751302760038</v>
       </c>
       <c r="Q53">
-        <v>1170.3238875606</v>
+        <v>1269.8724869724</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.08775131098929884</v>
+        <v>0.08718989613575637</v>
       </c>
       <c r="T53">
-        <v>0.9682295618070682</v>
+        <v>0.9558867467842119</v>
       </c>
       <c r="U53">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V53">
-        <v>0.21463336918939</v>
+        <v>0.2368929850496725</v>
       </c>
       <c r="W53">
-        <v>0.1028044919731089</v>
+        <v>0.09050449197310885</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8319122836798063</v>
+        <v>0.9181898645336142</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.09627943329104197</v>
+        <v>0.08960834001280615</v>
       </c>
       <c r="C54">
-        <v>870.230884195551</v>
+        <v>2126.250838047365</v>
       </c>
       <c r="D54">
-        <v>11495.32688419555</v>
+        <v>12751.34683804737</v>
       </c>
       <c r="E54">
         <v>3886.296000000002</v>
@@ -5721,37 +5721,37 @@
         <v>1187.8</v>
       </c>
       <c r="M54">
-        <v>1455.7907364</v>
+        <v>1318.9975656</v>
       </c>
       <c r="N54">
-        <v>-267.9907364000007</v>
+        <v>-131.1975656000006</v>
       </c>
       <c r="O54">
-        <v>-69.1416099912002</v>
+        <v>-33.84897192480017</v>
       </c>
       <c r="P54">
-        <v>-198.8491264088005</v>
+        <v>-97.34859367520048</v>
       </c>
       <c r="Q54">
-        <v>1149.550873591199</v>
+        <v>1251.0514063248</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.08862529663490923</v>
+        <v>0.08805218563858463</v>
       </c>
       <c r="T54">
-        <v>0.9884010110113822</v>
+        <v>0.9758010540088831</v>
       </c>
       <c r="U54">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V54">
-        <v>0.2105058043972863</v>
+        <v>0.2323373507217941</v>
       </c>
       <c r="W54">
-        <v>0.1033447902043952</v>
+        <v>0.09104479020439524</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8159139705321176</v>
+        <v>0.9005323671387369</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.09713043329104196</v>
+        <v>0.09033634001280613</v>
       </c>
       <c r="C55">
-        <v>513.4150237319554</v>
+        <v>1761.815945254883</v>
       </c>
       <c r="D55">
-        <v>11352.38402373196</v>
+        <v>12600.78494525489</v>
       </c>
       <c r="E55">
         <v>4100.169000000002</v>
@@ -5803,37 +5803,37 @@
         <v>1187.8</v>
       </c>
       <c r="M55">
-        <v>1483.7867121</v>
+        <v>1344.3629034</v>
       </c>
       <c r="N55">
-        <v>-295.9867121000007</v>
+        <v>-156.5629034000006</v>
       </c>
       <c r="O55">
-        <v>-76.36457172180017</v>
+        <v>-40.39322907720015</v>
       </c>
       <c r="P55">
-        <v>-219.6221403782005</v>
+        <v>-116.1696743228004</v>
       </c>
       <c r="Q55">
-        <v>1128.7778596218</v>
+        <v>1232.2303256772</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.08953647315905625</v>
+        <v>0.088951168311746</v>
       </c>
       <c r="T55">
-        <v>1.009430819756305</v>
+        <v>0.9965627785622635</v>
       </c>
       <c r="U55">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V55">
-        <v>0.2065339967671489</v>
+        <v>0.2279536271232697</v>
       </c>
       <c r="W55">
-        <v>0.1038646998231802</v>
+        <v>0.09156469982318022</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8005193673145305</v>
+        <v>0.8835411904002702</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1448214949579784</v>
+        <v>0.09106434001280614</v>
       </c>
       <c r="C56">
-        <v>-4362.631009255747</v>
+        <v>1400.895088103816</v>
       </c>
       <c r="D56">
-        <v>6690.210990744255</v>
+        <v>12453.73708810382</v>
       </c>
       <c r="E56">
         <v>4314.042000000001</v>
@@ -5885,45 +5885,45 @@
         <v>1187.8</v>
       </c>
       <c r="M56">
-        <v>2492.3048436</v>
+        <v>1369.7282412</v>
       </c>
       <c r="N56">
-        <v>-1304.504843600001</v>
+        <v>-181.9282412000007</v>
       </c>
       <c r="O56">
-        <v>-336.5622496488002</v>
+        <v>-46.93748622960018</v>
       </c>
       <c r="P56">
-        <v>-967.9425939512005</v>
+        <v>-134.9907549704005</v>
       </c>
       <c r="Q56">
-        <v>380.4574060487996</v>
+        <v>1213.4092450296</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.09264826967759328</v>
+        <v>0.08988923718808831</v>
       </c>
       <c r="T56">
-        <v>1.081250586731989</v>
+        <v>1.018227186791878</v>
       </c>
       <c r="U56">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V56">
-        <v>0.1229594368389326</v>
+        <v>0.223732263658024</v>
       </c>
       <c r="W56">
-        <v>0.1892653535301584</v>
+        <v>0.09206535353015838</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.4765869644919867</v>
+        <v>0.8671793165039688</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1465214949579784</v>
+        <v>0.09179234001280615</v>
       </c>
       <c r="C57">
-        <v>-4673.029380708705</v>
+        <v>1043.366662062861</v>
       </c>
       <c r="D57">
-        <v>6593.685619291298</v>
+        <v>12310.08166206286</v>
       </c>
       <c r="E57">
         <v>4527.915000000003</v>
@@ -5967,45 +5967,45 @@
         <v>1187.8</v>
       </c>
       <c r="M57">
-        <v>2538.458637000001</v>
+        <v>1395.093579000001</v>
       </c>
       <c r="N57">
-        <v>-1350.658637000001</v>
+        <v>-207.2935790000008</v>
       </c>
       <c r="O57">
-        <v>-348.4699283460004</v>
+        <v>-53.48174338200021</v>
       </c>
       <c r="P57">
-        <v>-1002.188708654001</v>
+        <v>-153.8118356180006</v>
       </c>
       <c r="Q57">
-        <v>346.2112913459991</v>
+        <v>1194.588164381999</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.09368934233709536</v>
+        <v>0.09086899801449028</v>
       </c>
       <c r="T57">
-        <v>1.105278377548256</v>
+        <v>1.040854457609475</v>
       </c>
       <c r="U57">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V57">
-        <v>0.1207238107145883</v>
+        <v>0.2196644043187872</v>
       </c>
       <c r="W57">
-        <v>0.1897478016477919</v>
+        <v>0.09254780164779185</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.4679217469557686</v>
+        <v>0.8514124198402602</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1482214949579784</v>
+        <v>0.09252034001280615</v>
       </c>
       <c r="C58">
-        <v>-4980.682059140182</v>
+        <v>689.1146095107615</v>
       </c>
       <c r="D58">
-        <v>6499.90594085982</v>
+        <v>12169.70260951076</v>
       </c>
       <c r="E58">
         <v>4741.788000000002</v>
@@ -6049,45 +6049,45 @@
         <v>1187.8</v>
       </c>
       <c r="M58">
-        <v>2584.612430400001</v>
+        <v>1420.4589168</v>
       </c>
       <c r="N58">
-        <v>-1396.812430400001</v>
+        <v>-232.6589168000007</v>
       </c>
       <c r="O58">
-        <v>-360.3776070432003</v>
+        <v>-60.02600053440019</v>
       </c>
       <c r="P58">
-        <v>-1036.434823356801</v>
+        <v>-172.6329162656005</v>
       </c>
       <c r="Q58">
-        <v>311.9651766431994</v>
+        <v>1175.7670837344</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.09477773648112026</v>
+        <v>0.0918932934239105</v>
       </c>
       <c r="T58">
-        <v>1.130398340674352</v>
+        <v>1.064510240736963</v>
       </c>
       <c r="U58">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V58">
-        <v>0.1185680283803992</v>
+        <v>0.2157418256702374</v>
       </c>
       <c r="W58">
-        <v>0.1902130194755099</v>
+        <v>0.09301301947550986</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.4595660014744156</v>
+        <v>0.8362086266288271</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1499214949579784</v>
+        <v>0.09324834001280613</v>
       </c>
       <c r="C59">
-        <v>-5285.704554775886</v>
+        <v>338.0281070290021</v>
       </c>
       <c r="D59">
-        <v>6408.756445224116</v>
+        <v>12032.48910702901</v>
       </c>
       <c r="E59">
         <v>4955.661000000002</v>
@@ -6131,45 +6131,45 @@
         <v>1187.8</v>
       </c>
       <c r="M59">
-        <v>2630.766223800001</v>
+        <v>1445.8242546</v>
       </c>
       <c r="N59">
-        <v>-1442.966223800001</v>
+        <v>-258.0242546000006</v>
       </c>
       <c r="O59">
-        <v>-372.2852857404002</v>
+        <v>-66.57025768680016</v>
       </c>
       <c r="P59">
-        <v>-1070.680938059601</v>
+        <v>-191.4539969132005</v>
       </c>
       <c r="Q59">
-        <v>277.7190619403993</v>
+        <v>1156.9460030868</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.09591675360858815</v>
+        <v>0.09296523048028052</v>
       </c>
       <c r="T59">
-        <v>1.156686674178407</v>
+        <v>1.089266292847125</v>
       </c>
       <c r="U59">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V59">
-        <v>0.1164878875316203</v>
+        <v>0.2119568813602332</v>
       </c>
       <c r="W59">
-        <v>0.1906619138706764</v>
+        <v>0.09346191387067634</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.4515034400450399</v>
+        <v>0.8215382998458652</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1516214949579784</v>
+        <v>0.09397634001280614</v>
       </c>
       <c r="C60">
-        <v>-5588.205988152383</v>
+        <v>-9.998726386687849</v>
       </c>
       <c r="D60">
-        <v>6320.128011847617</v>
+        <v>11898.33527361331</v>
       </c>
       <c r="E60">
         <v>5169.534</v>
@@ -6213,45 +6213,45 @@
         <v>1187.8</v>
       </c>
       <c r="M60">
-        <v>2676.9200172</v>
+        <v>1471.1895924</v>
       </c>
       <c r="N60">
-        <v>-1489.1200172</v>
+        <v>-283.3895924000003</v>
       </c>
       <c r="O60">
-        <v>-384.1929644376001</v>
+        <v>-73.11451483920008</v>
       </c>
       <c r="P60">
-        <v>-1104.9270527624</v>
+        <v>-210.2750775608002</v>
       </c>
       <c r="Q60">
-        <v>243.4729472375998</v>
+        <v>1138.1249224392</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.09711000964688787</v>
+        <v>0.09408821215838242</v>
       </c>
       <c r="T60">
-        <v>1.184226833087416</v>
+        <v>1.11520120458158</v>
       </c>
       <c r="U60">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V60">
-        <v>0.1144794756776269</v>
+        <v>0.2083024523712638</v>
       </c>
       <c r="W60">
-        <v>0.1910953291487681</v>
+        <v>0.09389532914876812</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.443718897975298</v>
+        <v>0.8073738464002471</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1533214949579784</v>
+        <v>0.1443432223090956</v>
       </c>
       <c r="C61">
-        <v>-5888.289525914093</v>
+        <v>-5405.173002832393</v>
       </c>
       <c r="D61">
-        <v>6233.917474085908</v>
+        <v>6717.033997167609</v>
       </c>
       <c r="E61">
         <v>5383.407000000001</v>
@@ -6295,37 +6295,37 @@
         <v>1187.8</v>
       </c>
       <c r="M61">
-        <v>2723.0738106</v>
+        <v>2533.796205600001</v>
       </c>
       <c r="N61">
-        <v>-1535.273810600001</v>
+        <v>-1345.996205600001</v>
       </c>
       <c r="O61">
-        <v>-396.1006431348002</v>
+        <v>-347.2670210448002</v>
       </c>
       <c r="P61">
-        <v>-1139.173167465201</v>
+        <v>-998.7291845552006</v>
       </c>
       <c r="Q61">
-        <v>209.2268325347995</v>
+        <v>349.6708154447995</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.09836147329681197</v>
+        <v>0.09804861317758565</v>
       </c>
       <c r="T61">
-        <v>1.213110414382231</v>
+        <v>1.206665431353017</v>
       </c>
       <c r="U61">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1125391455813959</v>
+        <v>0.1209459542652651</v>
       </c>
       <c r="W61">
-        <v>0.1915140523835348</v>
+        <v>0.1765140523835348</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.436198238687581</v>
+        <v>0.4687827684700198</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1550214949579784</v>
+        <v>0.1458932223090956</v>
       </c>
       <c r="C62">
-        <v>-6186.052781422964</v>
+        <v>-5707.871053386751</v>
       </c>
       <c r="D62">
-        <v>6150.027218577036</v>
+        <v>6628.20894661325</v>
       </c>
       <c r="E62">
         <v>5597.280000000001</v>
@@ -6377,37 +6377,37 @@
         <v>1187.8</v>
       </c>
       <c r="M62">
-        <v>2769.227604000001</v>
+        <v>2576.741904</v>
       </c>
       <c r="N62">
-        <v>-1581.427604000001</v>
+        <v>-1388.941904000001</v>
       </c>
       <c r="O62">
-        <v>-408.0083218320003</v>
+        <v>-358.3470112320002</v>
       </c>
       <c r="P62">
-        <v>-1173.419282168001</v>
+        <v>-1030.594892768001</v>
       </c>
       <c r="Q62">
-        <v>174.9807178319995</v>
+        <v>317.8051072319995</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.09967551012923226</v>
+        <v>0.09935482850702529</v>
       </c>
       <c r="T62">
-        <v>1.243438174741787</v>
+        <v>1.236832067136843</v>
       </c>
       <c r="U62">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1106634931550393</v>
+        <v>0.118930188360844</v>
       </c>
       <c r="W62">
-        <v>0.1919188181771425</v>
+        <v>0.1769188181771425</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4289282680427879</v>
+        <v>0.4609697223288528</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1567214949579784</v>
+        <v>0.1474432223090956</v>
       </c>
       <c r="C63">
-        <v>-6481.588183451473</v>
+        <v>-6008.250545901434</v>
       </c>
       <c r="D63">
-        <v>6068.364816548527</v>
+        <v>6541.702454098567</v>
       </c>
       <c r="E63">
         <v>5811.153</v>
@@ -6459,37 +6459,37 @@
         <v>1187.8</v>
       </c>
       <c r="M63">
-        <v>2815.3813974</v>
+        <v>2619.6876024</v>
       </c>
       <c r="N63">
-        <v>-1627.581397400001</v>
+        <v>-1431.887602400001</v>
       </c>
       <c r="O63">
-        <v>-419.9160005292002</v>
+        <v>-369.4270014192002</v>
       </c>
       <c r="P63">
-        <v>-1207.665396870801</v>
+        <v>-1062.4606009808</v>
       </c>
       <c r="Q63">
-        <v>140.7346031291995</v>
+        <v>285.9393990191998</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1010569334658793</v>
+        <v>0.1007280292379747</v>
       </c>
       <c r="T63">
-        <v>1.275321204863372</v>
+        <v>1.268545709883941</v>
       </c>
       <c r="U63">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1088493375295469</v>
+        <v>0.1169805131418138</v>
       </c>
       <c r="W63">
-        <v>0.1923103129611238</v>
+        <v>0.1773103129611238</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4218966570912669</v>
+        <v>0.4534128416349372</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1584214949579784</v>
+        <v>0.1489932223090956</v>
       </c>
       <c r="C64">
-        <v>-6774.983315886635</v>
+        <v>-6306.401091168829</v>
       </c>
       <c r="D64">
-        <v>5988.842684113367</v>
+        <v>6457.424908831173</v>
       </c>
       <c r="E64">
         <v>6025.026000000002</v>
@@ -6541,37 +6541,37 @@
         <v>1187.8</v>
       </c>
       <c r="M64">
-        <v>2861.535190800001</v>
+        <v>2662.633300800001</v>
       </c>
       <c r="N64">
-        <v>-1673.735190800001</v>
+        <v>-1474.833300800001</v>
       </c>
       <c r="O64">
-        <v>-431.8236792264003</v>
+        <v>-380.5069916064002</v>
       </c>
       <c r="P64">
-        <v>-1241.911511573601</v>
+        <v>-1094.326309193601</v>
       </c>
       <c r="Q64">
-        <v>106.4884884263993</v>
+        <v>254.0736908063996</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1025110632939287</v>
+        <v>0.1021735036916056</v>
       </c>
       <c r="T64">
-        <v>1.308882289201881</v>
+        <v>1.301928491722993</v>
       </c>
       <c r="U64">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1070937030532638</v>
+        <v>0.1150937306717845</v>
       </c>
       <c r="W64">
-        <v>0.1926891788811057</v>
+        <v>0.1776891788811057</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4150918722994722</v>
+        <v>0.4460997312859866</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1601214949579784</v>
+        <v>0.1505432223090956</v>
       </c>
       <c r="C65">
-        <v>-7066.321231069909</v>
+        <v>-6602.407740850372</v>
       </c>
       <c r="D65">
-        <v>5911.377768930092</v>
+        <v>6375.29125914963</v>
       </c>
       <c r="E65">
         <v>6238.899000000001</v>
@@ -6623,37 +6623,37 @@
         <v>1187.8</v>
       </c>
       <c r="M65">
-        <v>2907.688984200001</v>
+        <v>2705.5789992</v>
       </c>
       <c r="N65">
-        <v>-1719.888984200001</v>
+        <v>-1517.778999200001</v>
       </c>
       <c r="O65">
-        <v>-443.7313579236002</v>
+        <v>-391.5869817936002</v>
       </c>
       <c r="P65">
-        <v>-1276.157626276401</v>
+        <v>-1126.192017406401</v>
       </c>
       <c r="Q65">
-        <v>72.24237372359948</v>
+        <v>222.2079825935996</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1040437947343051</v>
+        <v>0.1036971118994868</v>
       </c>
       <c r="T65">
-        <v>1.344257486207337</v>
+        <v>1.337115748256047</v>
       </c>
       <c r="U65">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1053938030047993</v>
+        <v>0.1132668460579467</v>
       </c>
       <c r="W65">
-        <v>0.1930560173115643</v>
+        <v>0.1780560173115643</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4085031124217028</v>
+        <v>0.439018783170336</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1618214949579784</v>
+        <v>0.1520932223090956</v>
       </c>
       <c r="C66">
-        <v>-7355.680739129544</v>
+        <v>-6896.351273778801</v>
       </c>
       <c r="D66">
-        <v>5835.891260870459</v>
+        <v>6295.220726221201</v>
       </c>
       <c r="E66">
         <v>6452.772000000003</v>
@@ -6705,37 +6705,37 @@
         <v>1187.8</v>
       </c>
       <c r="M66">
-        <v>2953.842777600001</v>
+        <v>2748.524697600001</v>
       </c>
       <c r="N66">
-        <v>-1766.042777600001</v>
+        <v>-1560.724697600001</v>
       </c>
       <c r="O66">
-        <v>-455.6390366208003</v>
+        <v>-402.6669719808003</v>
       </c>
       <c r="P66">
-        <v>-1310.403740979201</v>
+        <v>-1158.057725619201</v>
       </c>
       <c r="Q66">
-        <v>37.99625902079924</v>
+        <v>190.3422743807994</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1056616779213692</v>
+        <v>0.1053053650078059</v>
       </c>
       <c r="T66">
-        <v>1.38159797193532</v>
+        <v>1.37425785237427</v>
       </c>
       <c r="U66">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1037470248328493</v>
+        <v>0.1114970515882913</v>
       </c>
       <c r="W66">
-        <v>0.1934113920410711</v>
+        <v>0.1784113920410711</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4021202512901136</v>
+        <v>0.4321591146832995</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1635214949579785</v>
+        <v>0.1536432223090957</v>
       </c>
       <c r="C67">
-        <v>-7643.136675424254</v>
+        <v>-7188.30846095313</v>
       </c>
       <c r="D67">
-        <v>5762.308324575748</v>
+        <v>6217.136539046873</v>
       </c>
       <c r="E67">
         <v>6666.645000000002</v>
@@ -6787,37 +6787,37 @@
         <v>1187.8</v>
       </c>
       <c r="M67">
-        <v>2999.996571000001</v>
+        <v>2791.470396000001</v>
       </c>
       <c r="N67">
-        <v>-1812.196571000001</v>
+        <v>-1603.670396000001</v>
       </c>
       <c r="O67">
-        <v>-467.5467153180003</v>
+        <v>-413.7469621680003</v>
       </c>
       <c r="P67">
-        <v>-1344.649855682001</v>
+        <v>-1189.923433832001</v>
       </c>
       <c r="Q67">
-        <v>3.750144317999002</v>
+        <v>158.4765661679994</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1073720115762655</v>
+        <v>0.1070055182937432</v>
       </c>
       <c r="T67">
-        <v>1.4210721997049</v>
+        <v>1.413522362442107</v>
       </c>
       <c r="U67">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1021509167584978</v>
+        <v>0.1097817123330868</v>
       </c>
       <c r="W67">
-        <v>0.1937558321635162</v>
+        <v>0.1787558321635162</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3959337858856504</v>
+        <v>0.425510512918941</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1652214949579784</v>
+        <v>0.1551932223090957</v>
       </c>
       <c r="C68">
-        <v>-7928.760148006253</v>
+        <v>-7478.352311053668</v>
       </c>
       <c r="D68">
-        <v>5690.557851993749</v>
+        <v>6140.965688946334</v>
       </c>
       <c r="E68">
         <v>6880.518000000002</v>
@@ -6869,37 +6869,37 @@
         <v>1187.8</v>
       </c>
       <c r="M68">
-        <v>3046.150364400001</v>
+        <v>2834.4160944</v>
       </c>
       <c r="N68">
-        <v>-1858.350364400001</v>
+        <v>-1646.616094400001</v>
       </c>
       <c r="O68">
-        <v>-479.4543940152003</v>
+        <v>-424.8269523552002</v>
       </c>
       <c r="P68">
-        <v>-1378.895970384801</v>
+        <v>-1221.7891420448</v>
       </c>
       <c r="Q68">
-        <v>-30.49597038480078</v>
+        <v>126.6108579551997</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1091829530932144</v>
+        <v>0.1088056805965003</v>
       </c>
       <c r="T68">
-        <v>1.462868440872691</v>
+        <v>1.455096549572757</v>
       </c>
       <c r="U68">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1006031755954903</v>
+        <v>0.1081183530553128</v>
       </c>
       <c r="W68">
-        <v>0.1940898347064932</v>
+        <v>0.1790898347064932</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3899347891298072</v>
+        <v>0.4190633839353207</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1669214949579785</v>
+        <v>0.1567432223090956</v>
       </c>
       <c r="C69">
-        <v>-8212.61876682358</v>
+        <v>-7766.552298127575</v>
       </c>
       <c r="D69">
-        <v>5620.572233176423</v>
+        <v>6066.638701872428</v>
       </c>
       <c r="E69">
         <v>7094.391000000003</v>
@@ -6951,37 +6951,37 @@
         <v>1187.8</v>
       </c>
       <c r="M69">
-        <v>3092.304157800001</v>
+        <v>2877.361792800001</v>
       </c>
       <c r="N69">
-        <v>-1904.504157800001</v>
+        <v>-1689.561792800001</v>
       </c>
       <c r="O69">
-        <v>-491.3620727124004</v>
+        <v>-435.9069425424003</v>
       </c>
       <c r="P69">
-        <v>-1413.142085087601</v>
+        <v>-1253.654850257601</v>
       </c>
       <c r="Q69">
-        <v>-64.74208508760103</v>
+        <v>94.74514974239924</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1111036486414937</v>
+        <v>0.1107149436448792</v>
       </c>
       <c r="T69">
-        <v>1.507197787565803</v>
+        <v>1.499190384408295</v>
       </c>
       <c r="U69">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.0991016356612292</v>
+        <v>0.1065046462932931</v>
       </c>
       <c r="W69">
-        <v>0.1944138670243068</v>
+        <v>0.1794138670243067</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3841148669039892</v>
+        <v>0.4128087065631517</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1686214949579784</v>
+        <v>0.1582932223090956</v>
       </c>
       <c r="C70">
-        <v>-8494.776856214801</v>
+        <v>-8052.974572937412</v>
       </c>
       <c r="D70">
-        <v>5552.287143785203</v>
+        <v>5994.089427062591</v>
       </c>
       <c r="E70">
         <v>7308.264000000003</v>
@@ -7033,37 +7033,37 @@
         <v>1187.8</v>
       </c>
       <c r="M70">
-        <v>3138.457951200001</v>
+        <v>2920.307491200001</v>
       </c>
       <c r="N70">
-        <v>-1950.657951200001</v>
+        <v>-1732.507491200001</v>
       </c>
       <c r="O70">
-        <v>-503.2697514096003</v>
+        <v>-446.9869327296003</v>
       </c>
       <c r="P70">
-        <v>-1447.388199790401</v>
+        <v>-1285.520558470401</v>
       </c>
       <c r="Q70">
-        <v>-98.98819979040081</v>
+        <v>62.87944152959949</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1131443876615403</v>
+        <v>0.1127435356337816</v>
       </c>
       <c r="T70">
-        <v>1.554297718427234</v>
+        <v>1.546040083921054</v>
       </c>
       <c r="U70">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.09764425866621114</v>
+        <v>0.1049384014948624</v>
       </c>
       <c r="W70">
-        <v>0.1947283689798316</v>
+        <v>0.1797283689798317</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3784661188612835</v>
+        <v>0.4067379902901642</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1703214949579784</v>
+        <v>0.1598432223090957</v>
       </c>
       <c r="C71">
-        <v>-8775.295652099867</v>
+        <v>-8337.682159324144</v>
       </c>
       <c r="D71">
-        <v>5485.641347900136</v>
+        <v>5923.25484067586</v>
       </c>
       <c r="E71">
         <v>7522.137000000002</v>
@@ -7115,37 +7115,37 @@
         <v>1187.8</v>
       </c>
       <c r="M71">
-        <v>3184.611744600001</v>
+        <v>2963.2531896</v>
       </c>
       <c r="N71">
-        <v>-1996.811744600001</v>
+        <v>-1775.453189600001</v>
       </c>
       <c r="O71">
-        <v>-515.1774301068003</v>
+        <v>-458.0669229168002</v>
       </c>
       <c r="P71">
-        <v>-1481.634314493201</v>
+        <v>-1317.386266683201</v>
       </c>
       <c r="Q71">
-        <v>-133.2343144932006</v>
+        <v>31.01373331679952</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1153167872635255</v>
+        <v>0.1149030045251939</v>
       </c>
       <c r="T71">
-        <v>1.604436354505532</v>
+        <v>1.595912344692701</v>
       </c>
       <c r="U71">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.09622912448264287</v>
+        <v>0.1034175550963861</v>
       </c>
       <c r="W71">
-        <v>0.1950337549366457</v>
+        <v>0.1800337549366457</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3729811026459026</v>
+        <v>0.4008432368076981</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1720214949579785</v>
+        <v>0.1613932223090957</v>
       </c>
       <c r="C72">
-        <v>-9054.233485137771</v>
+        <v>-8620.735136809773</v>
       </c>
       <c r="D72">
-        <v>5420.576514862232</v>
+        <v>5854.07486319023</v>
       </c>
       <c r="E72">
         <v>7736.010000000004</v>
@@ -7197,37 +7197,37 @@
         <v>1187.8</v>
       </c>
       <c r="M72">
-        <v>3230.765538000001</v>
+        <v>3006.198888000001</v>
       </c>
       <c r="N72">
-        <v>-2042.965538000001</v>
+        <v>-1818.398888000001</v>
       </c>
       <c r="O72">
-        <v>-527.0851088040004</v>
+        <v>-469.1469131040003</v>
       </c>
       <c r="P72">
-        <v>-1515.880429196001</v>
+        <v>-1349.251974896001</v>
       </c>
       <c r="Q72">
-        <v>-167.4804291960008</v>
+        <v>-0.8519748960006837</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.117634013505643</v>
+        <v>0.1172064380093671</v>
       </c>
       <c r="T72">
-        <v>1.657917566322384</v>
+        <v>1.649109422849125</v>
       </c>
       <c r="U72">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.09485442270431937</v>
+        <v>0.101940161452152</v>
       </c>
       <c r="W72">
-        <v>0.1953304155804079</v>
+        <v>0.1803304155804079</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3676528011795325</v>
+        <v>0.3951169048533024</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1737214949579784</v>
+        <v>0.1629432223090956</v>
       </c>
       <c r="C73">
-        <v>-9331.645951002465</v>
+        <v>-8902.190810551552</v>
       </c>
       <c r="D73">
-        <v>5357.037048997536</v>
+        <v>5786.49218944845</v>
       </c>
       <c r="E73">
         <v>7949.883000000002</v>
@@ -7279,37 +7279,37 @@
         <v>1187.8</v>
       </c>
       <c r="M73">
-        <v>3276.919331400001</v>
+        <v>3049.144586400001</v>
       </c>
       <c r="N73">
-        <v>-2089.119331400001</v>
+        <v>-1861.344586400001</v>
       </c>
       <c r="O73">
-        <v>-538.9927875012003</v>
+        <v>-480.2269032912002</v>
       </c>
       <c r="P73">
-        <v>-1550.126543898801</v>
+        <v>-1381.117683108801</v>
       </c>
       <c r="Q73">
-        <v>-201.7265438988006</v>
+        <v>-32.71768310880066</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1201110484541135</v>
+        <v>0.1196687289752073</v>
       </c>
       <c r="T73">
-        <v>1.715087137574879</v>
+        <v>1.705975265016335</v>
       </c>
       <c r="U73">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.09351844491975152</v>
+        <v>0.1005043845302907</v>
       </c>
       <c r="W73">
-        <v>0.1956187195863177</v>
+        <v>0.1806187195863176</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3624745927122152</v>
+        <v>0.3895518780243826</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1754214949579784</v>
+        <v>0.1644932223090956</v>
       </c>
       <c r="C74">
-        <v>-9607.586068821811</v>
+        <v>-9182.103869658291</v>
       </c>
       <c r="D74">
-        <v>5294.969931178191</v>
+        <v>5720.45213034171</v>
       </c>
       <c r="E74">
         <v>8163.756000000001</v>
@@ -7361,37 +7361,37 @@
         <v>1187.8</v>
       </c>
       <c r="M74">
-        <v>3323.073124800001</v>
+        <v>3092.090284800001</v>
       </c>
       <c r="N74">
-        <v>-2135.273124800001</v>
+        <v>-1904.290284800001</v>
       </c>
       <c r="O74">
-        <v>-550.9004661984003</v>
+        <v>-491.3068934784002</v>
       </c>
       <c r="P74">
-        <v>-1584.372658601601</v>
+        <v>-1412.9833913216</v>
       </c>
       <c r="Q74">
-        <v>-235.9726586016004</v>
+        <v>-64.5833913216004</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1227650144703318</v>
+        <v>0.122306897867179</v>
       </c>
       <c r="T74">
-        <v>1.776340249631125</v>
+        <v>1.766902953052633</v>
       </c>
       <c r="U74">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.09221957762919941</v>
+        <v>0.09910849030070336</v>
       </c>
       <c r="W74">
-        <v>0.1958990151476188</v>
+        <v>0.1808990151476188</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.35744022336899</v>
+        <v>0.384141435274044</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1771214949579784</v>
+        <v>0.1660432223090956</v>
       </c>
       <c r="C75">
-        <v>-9882.104428728469</v>
+        <v>-9460.526534787996</v>
       </c>
       <c r="D75">
-        <v>5234.324571271532</v>
+        <v>5655.902465212005</v>
       </c>
       <c r="E75">
         <v>8377.629000000001</v>
@@ -7443,37 +7443,37 @@
         <v>1187.8</v>
       </c>
       <c r="M75">
-        <v>3369.2269182</v>
+        <v>3135.0359832</v>
       </c>
       <c r="N75">
-        <v>-2181.426918200001</v>
+        <v>-1947.235983200001</v>
       </c>
       <c r="O75">
-        <v>-562.8081448956002</v>
+        <v>-502.3868836656002</v>
       </c>
       <c r="P75">
-        <v>-1618.618773304401</v>
+        <v>-1444.8490995344</v>
       </c>
       <c r="Q75">
-        <v>-270.2187733044004</v>
+        <v>-96.44909953440037</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1256155705618256</v>
+        <v>0.1251404866770745</v>
       </c>
       <c r="T75">
-        <v>1.842130629247092</v>
+        <v>1.832343803165693</v>
       </c>
       <c r="U75">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.09095629574386792</v>
+        <v>0.09775083974863893</v>
       </c>
       <c r="W75">
-        <v>0.1961716313784733</v>
+        <v>0.1811716313784733</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3525437819529764</v>
+        <v>0.3788792238319338</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1788214949579784</v>
+        <v>0.1675932223090957</v>
       </c>
       <c r="C76">
-        <v>-10155.24932938599</v>
+        <v>-9737.508695864059</v>
       </c>
       <c r="D76">
-        <v>5175.052670614014</v>
+        <v>5592.793304135944</v>
       </c>
       <c r="E76">
         <v>8591.502000000002</v>
@@ -7525,37 +7525,37 @@
         <v>1187.8</v>
       </c>
       <c r="M76">
-        <v>3415.380711600001</v>
+        <v>3177.981681600001</v>
       </c>
       <c r="N76">
-        <v>-2227.580711600001</v>
+        <v>-1990.181681600001</v>
       </c>
       <c r="O76">
-        <v>-574.7158235928002</v>
+        <v>-513.4668738528003</v>
       </c>
       <c r="P76">
-        <v>-1652.864888007201</v>
+        <v>-1476.714807747201</v>
       </c>
       <c r="Q76">
-        <v>-304.4648880072007</v>
+        <v>-128.3148077472006</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1286854001988189</v>
+        <v>0.128192043856962</v>
       </c>
       <c r="T76">
-        <v>1.912981807295057</v>
+        <v>1.902818564825912</v>
       </c>
       <c r="U76">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.08972715661219403</v>
+        <v>0.09642988245473841</v>
       </c>
       <c r="W76">
-        <v>0.1964368796030886</v>
+        <v>0.1814368796030885</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3477796767914497</v>
+        <v>0.3737592343206915</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1805214949579784</v>
+        <v>0.1691432223090956</v>
       </c>
       <c r="C77">
-        <v>-10427.06690627556</v>
+        <v>-10013.09804067326</v>
       </c>
       <c r="D77">
-        <v>5117.108093724446</v>
+        <v>5531.076959326741</v>
       </c>
       <c r="E77">
         <v>8805.375000000002</v>
@@ -7607,37 +7607,37 @@
         <v>1187.8</v>
       </c>
       <c r="M77">
-        <v>3461.534505000001</v>
+        <v>3220.927380000001</v>
       </c>
       <c r="N77">
-        <v>-2273.734505000001</v>
+        <v>-2033.127380000001</v>
       </c>
       <c r="O77">
-        <v>-586.6235022900004</v>
+        <v>-524.5468640400002</v>
       </c>
       <c r="P77">
-        <v>-1687.111002710001</v>
+        <v>-1508.580515960001</v>
       </c>
       <c r="Q77">
-        <v>-338.7110027100007</v>
+        <v>-160.1805159600005</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1320008162067716</v>
+        <v>0.1314877256112405</v>
       </c>
       <c r="T77">
-        <v>1.98950107958686</v>
+        <v>1.978931307418949</v>
       </c>
       <c r="U77">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.08853079452403143</v>
+        <v>0.09514415068867522</v>
       </c>
       <c r="W77">
-        <v>0.196695054541714</v>
+        <v>0.181695054541714</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3431426144342303</v>
+        <v>0.3687757778630822</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1822214949579785</v>
+        <v>0.1706932223090956</v>
       </c>
       <c r="C78">
-        <v>-10697.60125145981</v>
+        <v>-10287.34017504227</v>
       </c>
       <c r="D78">
-        <v>5060.44674854019</v>
+        <v>5470.707824957729</v>
       </c>
       <c r="E78">
         <v>9019.248000000001</v>
@@ -7689,37 +7689,37 @@
         <v>1187.8</v>
       </c>
       <c r="M78">
-        <v>3507.688298400001</v>
+        <v>3263.8730784</v>
       </c>
       <c r="N78">
-        <v>-2319.888298400001</v>
+        <v>-2076.073078400001</v>
       </c>
       <c r="O78">
-        <v>-598.5311809872003</v>
+        <v>-535.6268542272002</v>
       </c>
       <c r="P78">
-        <v>-1721.357117412801</v>
+        <v>-1540.446224172801</v>
       </c>
       <c r="Q78">
-        <v>-372.9571174128007</v>
+        <v>-192.0462241728005</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1355925168820538</v>
+        <v>0.1350580475117088</v>
       </c>
       <c r="T78">
-        <v>2.072396957902979</v>
+        <v>2.061386778561405</v>
       </c>
       <c r="U78">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.08736591564871524</v>
+        <v>0.0938922539690874</v>
       </c>
       <c r="W78">
-        <v>0.1969464354030073</v>
+        <v>0.1819464354030073</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.33862758003378</v>
+        <v>0.3639234649964628</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1839214949579784</v>
+        <v>0.1722432223090956</v>
       </c>
       <c r="C79">
-        <v>-10966.8945254769</v>
+        <v>-10560.27873522908</v>
       </c>
       <c r="D79">
-        <v>5005.0264745231</v>
+        <v>5411.642264770921</v>
       </c>
       <c r="E79">
         <v>9233.121000000001</v>
@@ -7771,37 +7771,37 @@
         <v>1187.8</v>
       </c>
       <c r="M79">
-        <v>3553.842091800001</v>
+        <v>3306.8187768</v>
       </c>
       <c r="N79">
-        <v>-2366.042091800001</v>
+        <v>-2119.018776800001</v>
       </c>
       <c r="O79">
-        <v>-610.4388596844002</v>
+        <v>-546.7068444144002</v>
       </c>
       <c r="P79">
-        <v>-1755.603232115601</v>
+        <v>-1572.3119323856</v>
       </c>
       <c r="Q79">
-        <v>-407.2032321156007</v>
+        <v>-223.9119323856003</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1394965393551865</v>
+        <v>0.1389388321861309</v>
       </c>
       <c r="T79">
-        <v>2.162501173463978</v>
+        <v>2.15101229067277</v>
       </c>
       <c r="U79">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.08623129336756309</v>
+        <v>0.09267287404741094</v>
       </c>
       <c r="W79">
-        <v>0.1971912868912799</v>
+        <v>0.1821912868912799</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3342298192541205</v>
+        <v>0.359197186230275</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1856214949579784</v>
+        <v>0.1737932223090956</v>
       </c>
       <c r="C80">
-        <v>-11234.98706196169</v>
+        <v>-10831.95549311146</v>
       </c>
       <c r="D80">
-        <v>4950.806938038313</v>
+        <v>5353.838506888547</v>
       </c>
       <c r="E80">
         <v>9446.994000000004</v>
@@ -7853,37 +7853,37 @@
         <v>1187.8</v>
       </c>
       <c r="M80">
-        <v>3599.995885200001</v>
+        <v>3349.764475200001</v>
       </c>
       <c r="N80">
-        <v>-2412.195885200002</v>
+        <v>-2161.964475200001</v>
       </c>
       <c r="O80">
-        <v>-622.3465383816005</v>
+        <v>-557.7868346016004</v>
       </c>
       <c r="P80">
-        <v>-1789.849346818401</v>
+        <v>-1604.177640598401</v>
       </c>
       <c r="Q80">
-        <v>-441.449346818401</v>
+        <v>-255.7776405984009</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1437554729622405</v>
+        <v>0.1431724154673187</v>
       </c>
       <c r="T80">
-        <v>2.260796681348705</v>
+        <v>2.248785576612442</v>
       </c>
       <c r="U80">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.08512576396541482</v>
+        <v>0.09148476027757232</v>
       </c>
       <c r="W80">
-        <v>0.1974298601362635</v>
+        <v>0.1824298601362635</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3299448215713753</v>
+        <v>0.3545920940991175</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1873214949579785</v>
+        <v>0.1753432223090956</v>
       </c>
       <c r="C81">
-        <v>-11501.91746553963</v>
+        <v>-11102.41045470533</v>
       </c>
       <c r="D81">
-        <v>4897.749534460376</v>
+        <v>5297.256545294675</v>
       </c>
       <c r="E81">
         <v>9660.867000000004</v>
@@ -7935,37 +7935,37 @@
         <v>1187.8</v>
       </c>
       <c r="M81">
-        <v>3646.149678600001</v>
+        <v>3392.710173600001</v>
       </c>
       <c r="N81">
-        <v>-2458.349678600001</v>
+        <v>-2204.910173600001</v>
       </c>
       <c r="O81">
-        <v>-634.2542170788004</v>
+        <v>-568.8668247888003</v>
       </c>
       <c r="P81">
-        <v>-1824.095461521201</v>
+        <v>-1636.043348811201</v>
       </c>
       <c r="Q81">
-        <v>-475.695461521201</v>
+        <v>-287.6433488112007</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1484200192937758</v>
+        <v>0.1478091971562387</v>
       </c>
       <c r="T81">
-        <v>2.368453666174834</v>
+        <v>2.355870604070178</v>
       </c>
       <c r="U81">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.08404822264939693</v>
+        <v>0.09032672533734989</v>
       </c>
       <c r="W81">
-        <v>0.1976623935522602</v>
+        <v>0.1826623935522602</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3257683048426238</v>
+        <v>0.3501035865788755</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1890214949579784</v>
+        <v>0.1768932223090957</v>
       </c>
       <c r="C82">
-        <v>-11767.72270349266</v>
+        <v>-11371.68195250135</v>
       </c>
       <c r="D82">
-        <v>4845.817296507344</v>
+        <v>5241.858047498657</v>
       </c>
       <c r="E82">
         <v>9874.740000000003</v>
@@ -8017,37 +8017,37 @@
         <v>1187.8</v>
       </c>
       <c r="M82">
-        <v>3692.303472000001</v>
+        <v>3435.655872000001</v>
       </c>
       <c r="N82">
-        <v>-2504.503472000001</v>
+        <v>-2247.855872000001</v>
       </c>
       <c r="O82">
-        <v>-646.1618957760004</v>
+        <v>-579.9468149760003</v>
       </c>
       <c r="P82">
-        <v>-1858.341576224001</v>
+        <v>-1667.909057024001</v>
       </c>
       <c r="Q82">
-        <v>-509.9415762240008</v>
+        <v>-319.5090570240006</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1535510202584645</v>
+        <v>0.1529096570140506</v>
       </c>
       <c r="T82">
-        <v>2.486876349483575</v>
+        <v>2.473664134273687</v>
       </c>
       <c r="U82">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.08299761986627947</v>
+        <v>0.08919764127063301</v>
       </c>
       <c r="W82">
-        <v>0.1978891136328569</v>
+        <v>0.1828891136328569</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.321696201032091</v>
+        <v>0.3457272917466396</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1907214949579784</v>
+        <v>0.1784432223090956</v>
       </c>
       <c r="C83">
-        <v>-12032.43819165456</v>
+        <v>-11639.80673206749</v>
       </c>
       <c r="D83">
-        <v>4794.974808345439</v>
+        <v>5187.606267932509</v>
       </c>
       <c r="E83">
         <v>10088.613</v>
@@ -8099,37 +8099,37 @@
         <v>1187.8</v>
       </c>
       <c r="M83">
-        <v>3738.457265400001</v>
+        <v>3478.601570400001</v>
       </c>
       <c r="N83">
-        <v>-2550.657265400002</v>
+        <v>-2290.801570400001</v>
       </c>
       <c r="O83">
-        <v>-658.0695744732004</v>
+        <v>-591.0268051632003</v>
       </c>
       <c r="P83">
-        <v>-1892.587690926801</v>
+        <v>-1699.774765236801</v>
       </c>
       <c r="Q83">
-        <v>-544.187690926801</v>
+        <v>-351.3747652368006</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1592221265878574</v>
+        <v>0.1585470073832112</v>
       </c>
       <c r="T83">
-        <v>2.617764578403763</v>
+        <v>2.603856983445986</v>
       </c>
       <c r="U83">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.08197295789262168</v>
+        <v>0.08809643582284743</v>
       </c>
       <c r="W83">
-        <v>0.1981102356867722</v>
+        <v>0.1831102356867722</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3177246429946577</v>
+        <v>0.341459053576928</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1924214949579784</v>
+        <v>0.1799932223090956</v>
       </c>
       <c r="C84">
-        <v>-12296.09787495513</v>
+        <v>-11906.82003332892</v>
       </c>
       <c r="D84">
-        <v>4745.18812504487</v>
+        <v>5134.465966671079</v>
       </c>
       <c r="E84">
         <v>10302.486</v>
@@ -8181,37 +8181,37 @@
         <v>1187.8</v>
       </c>
       <c r="M84">
-        <v>3784.611058800001</v>
+        <v>3521.547268800001</v>
       </c>
       <c r="N84">
-        <v>-2596.811058800001</v>
+        <v>-2333.747268800001</v>
       </c>
       <c r="O84">
-        <v>-669.9772531704003</v>
+        <v>-602.1067953504003</v>
       </c>
       <c r="P84">
-        <v>-1926.833805629601</v>
+        <v>-1731.640473449601</v>
       </c>
       <c r="Q84">
-        <v>-578.433805629601</v>
+        <v>-383.2404734496008</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1655233558427384</v>
+        <v>0.1648107300156118</v>
       </c>
       <c r="T84">
-        <v>2.763195943870639</v>
+        <v>2.748515704748541</v>
       </c>
       <c r="U84">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.080973287674419</v>
+        <v>0.08702208904452001</v>
       </c>
       <c r="W84">
-        <v>0.1983259645198604</v>
+        <v>0.1833259645198604</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3138499522264302</v>
+        <v>0.3372949187772093</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1941214949579784</v>
+        <v>0.1815432223090956</v>
       </c>
       <c r="C85">
-        <v>-12558.7343029981</v>
+        <v>-12172.75566690279</v>
       </c>
       <c r="D85">
-        <v>4696.424697001902</v>
+        <v>5082.403333097207</v>
       </c>
       <c r="E85">
         <v>10516.359</v>
@@ -8263,37 +8263,37 @@
         <v>1187.8</v>
       </c>
       <c r="M85">
-        <v>3830.764852200001</v>
+        <v>3564.492967200001</v>
       </c>
       <c r="N85">
-        <v>-2642.964852200001</v>
+        <v>-2376.692967200001</v>
       </c>
       <c r="O85">
-        <v>-681.8849318676004</v>
+        <v>-613.1867855376003</v>
       </c>
       <c r="P85">
-        <v>-1961.079920332401</v>
+        <v>-1763.506181662401</v>
       </c>
       <c r="Q85">
-        <v>-612.6799203324008</v>
+        <v>-415.1061816624006</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.1725659061864289</v>
+        <v>0.1718113611930008</v>
       </c>
       <c r="T85">
-        <v>2.925736881745383</v>
+        <v>2.910193099145514</v>
       </c>
       <c r="U85">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.07999770589520912</v>
+        <v>0.08597363014036917</v>
       </c>
       <c r="W85">
-        <v>0.1985364950678139</v>
+        <v>0.1835364950678139</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3100686275008105</v>
+        <v>0.3332311245750743</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1958214949579784</v>
+        <v>0.1830932223090956</v>
       </c>
       <c r="C86">
-        <v>-12820.37870102651</v>
+        <v>-12437.6460858356</v>
       </c>
       <c r="D86">
-        <v>4648.653298973494</v>
+        <v>5031.385914164404</v>
       </c>
       <c r="E86">
         <v>10730.232</v>
@@ -8345,37 +8345,37 @@
         <v>1187.8</v>
       </c>
       <c r="M86">
-        <v>3876.918645600001</v>
+        <v>3607.438665600001</v>
       </c>
       <c r="N86">
-        <v>-2689.118645600001</v>
+        <v>-2419.638665600001</v>
       </c>
       <c r="O86">
-        <v>-693.7926105648003</v>
+        <v>-624.2667757248003</v>
       </c>
       <c r="P86">
-        <v>-1995.326035035201</v>
+        <v>-1795.371889875201</v>
       </c>
       <c r="Q86">
-        <v>-646.9260350352006</v>
+        <v>-446.9718898752005</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.1804887753230807</v>
+        <v>0.1796870712675632</v>
       </c>
       <c r="T86">
-        <v>3.108595436854468</v>
+        <v>3.092080167842107</v>
       </c>
       <c r="U86">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.0790453522535995</v>
+        <v>0.08495013454346002</v>
       </c>
       <c r="W86">
-        <v>0.1987420129836732</v>
+        <v>0.1837420129836732</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3063773343162771</v>
+        <v>0.329264087377752</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1975214949579784</v>
+        <v>0.1846432223090956</v>
       </c>
       <c r="C87">
-        <v>-13081.06103660055</v>
+        <v>-12701.5224530628</v>
       </c>
       <c r="D87">
-        <v>4601.843963399451</v>
+        <v>4981.382546937197</v>
       </c>
       <c r="E87">
         <v>10944.105</v>
@@ -8427,37 +8427,37 @@
         <v>1187.8</v>
       </c>
       <c r="M87">
-        <v>3923.072439000001</v>
+        <v>3650.384364</v>
       </c>
       <c r="N87">
-        <v>-2735.272439000001</v>
+        <v>-2462.584364000001</v>
       </c>
       <c r="O87">
-        <v>-705.7002892620003</v>
+        <v>-635.3467659120003</v>
       </c>
       <c r="P87">
-        <v>-2029.572149738001</v>
+        <v>-1827.237598088001</v>
       </c>
       <c r="Q87">
-        <v>-681.1721497380008</v>
+        <v>-478.8375980880005</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.189468027011286</v>
+        <v>0.1886128760187341</v>
       </c>
       <c r="T87">
-        <v>3.315835132644766</v>
+        <v>3.298218845698248</v>
       </c>
       <c r="U87">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.07811540693296891</v>
+        <v>0.08395072119588991</v>
       </c>
       <c r="W87">
-        <v>0.1989426951838653</v>
+        <v>0.1839426951838653</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3027728950890268</v>
+        <v>0.3253903922321314</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1992214949579784</v>
+        <v>0.1861932223090957</v>
       </c>
       <c r="C88">
-        <v>-13340.81008228713</v>
+        <v>-12964.4147048855</v>
       </c>
       <c r="D88">
-        <v>4555.967917712866</v>
+        <v>4932.363295114495</v>
       </c>
       <c r="E88">
         <v>11157.978</v>
@@ -8509,37 +8509,37 @@
         <v>1187.8</v>
       </c>
       <c r="M88">
-        <v>3969.226232400001</v>
+        <v>3693.3300624</v>
       </c>
       <c r="N88">
-        <v>-2781.426232400001</v>
+        <v>-2505.530062400001</v>
       </c>
       <c r="O88">
-        <v>-717.6079679592003</v>
+        <v>-646.4267560992001</v>
       </c>
       <c r="P88">
-        <v>-2063.818264440801</v>
+        <v>-1859.1033063008</v>
       </c>
       <c r="Q88">
-        <v>-715.4182644408006</v>
+        <v>-510.7033063008003</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.1997300289406636</v>
+        <v>0.198813795734358</v>
       </c>
       <c r="T88">
-        <v>3.552680499262249</v>
+        <v>3.533805906105266</v>
       </c>
       <c r="U88">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.07720708824770182</v>
+        <v>0.08297455001919352</v>
       </c>
       <c r="W88">
-        <v>0.199138710356146</v>
+        <v>0.184138710356146</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.299252280029852</v>
+        <v>0.3216067830201299</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2009214949579784</v>
+        <v>0.1877432223090956</v>
       </c>
       <c r="C89">
-        <v>-13599.65347463672</v>
+        <v>-13226.3516107357</v>
       </c>
       <c r="D89">
-        <v>4510.997525363284</v>
+        <v>4884.299389264298</v>
       </c>
       <c r="E89">
         <v>11371.851</v>
@@ -8591,37 +8591,37 @@
         <v>1187.8</v>
       </c>
       <c r="M89">
-        <v>4015.380025800001</v>
+        <v>3736.2757608</v>
       </c>
       <c r="N89">
-        <v>-2827.580025800001</v>
+        <v>-2548.4757608</v>
       </c>
       <c r="O89">
-        <v>-729.5156466564002</v>
+        <v>-657.5067462864001</v>
       </c>
       <c r="P89">
-        <v>-2098.0643791436</v>
+        <v>-1890.9690145136</v>
       </c>
       <c r="Q89">
-        <v>-749.6643791436004</v>
+        <v>-542.5690145136002</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2115708003976377</v>
+        <v>0.210584087713924</v>
       </c>
       <c r="T89">
-        <v>3.825963614590114</v>
+        <v>3.805637129651824</v>
       </c>
       <c r="U89">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.07631965045175124</v>
+        <v>0.08202081955920279</v>
       </c>
       <c r="W89">
-        <v>0.1993302194325121</v>
+        <v>0.1843302194325121</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2958125986501986</v>
+        <v>0.3179101533302434</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2026214949579784</v>
+        <v>0.1892932223090956</v>
       </c>
       <c r="C90">
-        <v>-13857.61776970145</v>
+        <v>-13487.36082948102</v>
       </c>
       <c r="D90">
-        <v>4466.906230298553</v>
+        <v>4837.163170518986</v>
       </c>
       <c r="E90">
         <v>11585.724</v>
@@ -8673,37 +8673,37 @@
         <v>1187.8</v>
       </c>
       <c r="M90">
-        <v>4061.533819200001</v>
+        <v>3779.221459200001</v>
       </c>
       <c r="N90">
-        <v>-2873.733819200002</v>
+        <v>-2591.421459200001</v>
       </c>
       <c r="O90">
-        <v>-741.4233253536004</v>
+        <v>-668.5867364736004</v>
       </c>
       <c r="P90">
-        <v>-2132.310493846401</v>
+        <v>-1922.834722726401</v>
       </c>
       <c r="Q90">
-        <v>-783.9104938464011</v>
+        <v>-574.4347227264007</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2253850337641076</v>
+        <v>0.2243160950234177</v>
       </c>
       <c r="T90">
-        <v>4.144793915805958</v>
+        <v>4.122773557122811</v>
       </c>
       <c r="U90">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.07545238169661769</v>
+        <v>0.08108876479148455</v>
       </c>
       <c r="W90">
-        <v>0.1995173760298699</v>
+        <v>0.1845173760298699</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2924510918473554</v>
+        <v>0.3142975379514905</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2043214949579784</v>
+        <v>0.1908432223090956</v>
       </c>
       <c r="C91">
-        <v>-14114.72849532895</v>
+        <v>-13747.4689625003</v>
       </c>
       <c r="D91">
-        <v>4423.668504671051</v>
+        <v>4790.928037499703</v>
       </c>
       <c r="E91">
         <v>11799.597</v>
@@ -8755,37 +8755,37 @@
         <v>1187.8</v>
       </c>
       <c r="M91">
-        <v>4107.687612600002</v>
+        <v>3822.167157600001</v>
       </c>
       <c r="N91">
-        <v>-2919.887612600002</v>
+        <v>-2634.367157600001</v>
       </c>
       <c r="O91">
-        <v>-753.3310040508005</v>
+        <v>-679.6667266608004</v>
       </c>
       <c r="P91">
-        <v>-2166.556608549201</v>
+        <v>-1954.700430939201</v>
       </c>
       <c r="Q91">
-        <v>-818.1566085492013</v>
+        <v>-606.3004309392006</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.241710945924481</v>
+        <v>0.2405448309346375</v>
       </c>
       <c r="T91">
-        <v>4.521593362697409</v>
+        <v>4.497571153224885</v>
       </c>
       <c r="U91">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.07460460212699277</v>
+        <v>0.08017765507472631</v>
       </c>
       <c r="W91">
-        <v>0.199700326860995</v>
+        <v>0.184700326860995</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2891651245232278</v>
+        <v>0.3107661049407996</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2060214949579784</v>
+        <v>0.1923932223090956</v>
       </c>
       <c r="C92">
-        <v>-14371.01020044815</v>
+        <v>-14006.70160374421</v>
       </c>
       <c r="D92">
-        <v>4381.259799551854</v>
+        <v>4745.568396255795</v>
       </c>
       <c r="E92">
         <v>12013.47</v>
@@ -8837,37 +8837,37 @@
         <v>1187.8</v>
       </c>
       <c r="M92">
-        <v>4153.841406000001</v>
+        <v>3865.112856000001</v>
       </c>
       <c r="N92">
-        <v>-2966.041406000002</v>
+        <v>-2677.312856000001</v>
       </c>
       <c r="O92">
-        <v>-765.2386827480004</v>
+        <v>-690.7467168480002</v>
       </c>
       <c r="P92">
-        <v>-2200.802723252001</v>
+        <v>-1986.566139152001</v>
       </c>
       <c r="Q92">
-        <v>-852.4027232520011</v>
+        <v>-638.1661391520006</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.2613020405169291</v>
+        <v>0.2600193140281012</v>
       </c>
       <c r="T92">
-        <v>4.97375269896715</v>
+        <v>4.947328268547373</v>
       </c>
       <c r="U92">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.07377566210335952</v>
+        <v>0.07928679224056269</v>
       </c>
       <c r="W92">
-        <v>0.199879212118095</v>
+        <v>0.184879212118095</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.285952178695192</v>
+        <v>0.3073131482192352</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2077214949579784</v>
+        <v>0.1939432223090956</v>
       </c>
       <c r="C93">
-        <v>-14626.48650154704</v>
+        <v>-14265.08338697865</v>
       </c>
       <c r="D93">
-        <v>4339.656498452967</v>
+        <v>4701.059613021353</v>
       </c>
       <c r="E93">
         <v>12227.343</v>
@@ -8919,37 +8919,37 @@
         <v>1187.8</v>
       </c>
       <c r="M93">
-        <v>4199.995199400001</v>
+        <v>3908.058554400001</v>
       </c>
       <c r="N93">
-        <v>-3012.195199400001</v>
+        <v>-2720.258554400001</v>
       </c>
       <c r="O93">
-        <v>-777.1463614452003</v>
+        <v>-701.8267070352002</v>
       </c>
       <c r="P93">
-        <v>-2235.048837954801</v>
+        <v>-2018.4318473648</v>
       </c>
       <c r="Q93">
-        <v>-886.6488379548009</v>
+        <v>-670.0318473648003</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.2852467116854768</v>
+        <v>0.2838214600312236</v>
       </c>
       <c r="T93">
-        <v>5.526391887741279</v>
+        <v>5.497031409497082</v>
       </c>
       <c r="U93">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.07296494054178414</v>
+        <v>0.07841550880934772</v>
       </c>
       <c r="W93">
-        <v>0.200054165831083</v>
+        <v>0.185054165831083</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2828098470611788</v>
+        <v>0.3039360806563864</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2094214949579785</v>
+        <v>0.1954932223090956</v>
       </c>
       <c r="C94">
-        <v>-14881.18012652734</v>
+        <v>-14522.63803039434</v>
       </c>
       <c r="D94">
-        <v>4298.835873472663</v>
+        <v>4657.377969605658</v>
       </c>
       <c r="E94">
         <v>12441.216</v>
@@ -9001,37 +9001,37 @@
         <v>1187.8</v>
       </c>
       <c r="M94">
-        <v>4246.148992800001</v>
+        <v>3951.004252800001</v>
       </c>
       <c r="N94">
-        <v>-3058.348992800001</v>
+        <v>-2763.204252800001</v>
       </c>
       <c r="O94">
-        <v>-789.0540401424004</v>
+        <v>-712.9066972224003</v>
       </c>
       <c r="P94">
-        <v>-2269.294952657601</v>
+        <v>-2050.297555577601</v>
       </c>
       <c r="Q94">
-        <v>-920.8949526576007</v>
+        <v>-701.8975555776005</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3151775506461615</v>
+        <v>0.3135741425351266</v>
       </c>
       <c r="T94">
-        <v>6.21719087370894</v>
+        <v>6.184160335684219</v>
       </c>
       <c r="U94">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.07217184336198215</v>
+        <v>0.07756316632228959</v>
       </c>
       <c r="W94">
-        <v>0.2002253162024843</v>
+        <v>0.1852253162024843</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2797358269844269</v>
+        <v>0.3006324276057736</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2111214949579785</v>
+        <v>0.1970432223090956</v>
       </c>
       <c r="C95">
-        <v>-15135.11295610713</v>
+        <v>-14779.38837875226</v>
       </c>
       <c r="D95">
-        <v>4258.776043892874</v>
+        <v>4614.500621247742</v>
       </c>
       <c r="E95">
         <v>12655.089</v>
@@ -9083,37 +9083,37 @@
         <v>1187.8</v>
       </c>
       <c r="M95">
-        <v>4292.302786200001</v>
+        <v>3993.949951200001</v>
       </c>
       <c r="N95">
-        <v>-3104.502786200001</v>
+        <v>-2806.149951200001</v>
       </c>
       <c r="O95">
-        <v>-800.9617188396003</v>
+        <v>-723.9866874096002</v>
       </c>
       <c r="P95">
-        <v>-2303.541067360401</v>
+        <v>-2082.163263790401</v>
       </c>
       <c r="Q95">
-        <v>-955.1410673604009</v>
+        <v>-733.7632637904007</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.3536600578813274</v>
+        <v>0.3518275914687162</v>
       </c>
       <c r="T95">
-        <v>7.105360998524503</v>
+        <v>7.067611812210536</v>
       </c>
       <c r="U95">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.07139580203550923</v>
+        <v>0.0767291537811897</v>
       </c>
       <c r="W95">
-        <v>0.2003927859207371</v>
+        <v>0.1853927859207371</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2767279148663149</v>
+        <v>0.2973998208573244</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2128214949579785</v>
+        <v>0.1985932223090957</v>
       </c>
       <c r="C96">
-        <v>-15388.30606292989</v>
+        <v>-15035.35644322225</v>
       </c>
       <c r="D96">
-        <v>4219.455937070113</v>
+        <v>4572.405556777756</v>
       </c>
       <c r="E96">
         <v>12868.962</v>
@@ -9165,37 +9165,37 @@
         <v>1187.8</v>
       </c>
       <c r="M96">
-        <v>4338.456579600002</v>
+        <v>4036.895649600001</v>
       </c>
       <c r="N96">
-        <v>-3150.656579600002</v>
+        <v>-2849.095649600001</v>
       </c>
       <c r="O96">
-        <v>-812.8693975368005</v>
+        <v>-735.0666775968003</v>
       </c>
       <c r="P96">
-        <v>-2337.787182063201</v>
+        <v>-2114.028972003201</v>
       </c>
       <c r="Q96">
-        <v>-989.3871820632012</v>
+        <v>-765.6289720032009</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.4049700675282155</v>
+        <v>0.4028321900468356</v>
       </c>
       <c r="T96">
-        <v>8.289587831611923</v>
+        <v>8.245547114245628</v>
       </c>
       <c r="U96">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.07063627222662081</v>
+        <v>0.07591288618777278</v>
       </c>
       <c r="W96">
-        <v>0.2005566924534952</v>
+        <v>0.1855566924534952</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2737840008783753</v>
+        <v>0.2942359929758634</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2145214949579784</v>
+        <v>0.2001432223090956</v>
       </c>
       <c r="C97">
-        <v>-15640.77974852691</v>
+        <v>-15290.56343906084</v>
       </c>
       <c r="D97">
-        <v>4180.855251473097</v>
+        <v>4531.071560939163</v>
       </c>
       <c r="E97">
         <v>13082.835</v>
@@ -9247,37 +9247,37 @@
         <v>1187.8</v>
       </c>
       <c r="M97">
-        <v>4384.610373000001</v>
+        <v>4079.841348000001</v>
       </c>
       <c r="N97">
-        <v>-3196.810373000002</v>
+        <v>-2892.041348000002</v>
       </c>
       <c r="O97">
-        <v>-824.7770762340004</v>
+        <v>-746.1466677840004</v>
       </c>
       <c r="P97">
-        <v>-2372.033296766001</v>
+        <v>-2145.894680216001</v>
       </c>
       <c r="Q97">
-        <v>-1023.633296766001</v>
+        <v>-797.4946802160011</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.4768040810338587</v>
+        <v>0.4742386280562029</v>
       </c>
       <c r="T97">
-        <v>9.947505397934313</v>
+        <v>9.894656537094757</v>
       </c>
       <c r="U97">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.06989273251897218</v>
+        <v>0.0751138031752699</v>
       </c>
       <c r="W97">
-        <v>0.2007171483224058</v>
+        <v>0.1857171483224058</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.270902064027024</v>
+        <v>0.2911387719971702</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2162214949579784</v>
+        <v>0.2016932223090956</v>
       </c>
       <c r="C98">
-        <v>-15892.5535782692</v>
+        <v>-15545.02982126379</v>
       </c>
       <c r="D98">
-        <v>4142.954421730804</v>
+        <v>4490.478178736211</v>
       </c>
       <c r="E98">
         <v>13296.708</v>
@@ -9329,37 +9329,37 @@
         <v>1187.8</v>
       </c>
       <c r="M98">
-        <v>4430.7641664</v>
+        <v>4122.787046400001</v>
       </c>
       <c r="N98">
-        <v>-3242.964166400001</v>
+        <v>-2934.987046400001</v>
       </c>
       <c r="O98">
-        <v>-836.6847549312001</v>
+        <v>-757.2266579712003</v>
       </c>
       <c r="P98">
-        <v>-2406.2794114688</v>
+        <v>-2177.760388428801</v>
       </c>
       <c r="Q98">
-        <v>-1057.8794114688</v>
+        <v>-829.3603884288004</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.5845551012923221</v>
+        <v>0.5813482850702525</v>
       </c>
       <c r="T98">
-        <v>12.43438174741786</v>
+        <v>12.36832067136842</v>
       </c>
       <c r="U98">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.06916468322189957</v>
+        <v>0.07433136772552751</v>
       </c>
       <c r="W98">
-        <v>0.2008742613607141</v>
+        <v>0.1858742613607141</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2680801675267425</v>
+        <v>0.288106076455533</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2179214949579784</v>
+        <v>0.2032432223090956</v>
       </c>
       <c r="C99">
-        <v>-16143.64641443542</v>
+        <v>-15798.77531831913</v>
       </c>
       <c r="D99">
-        <v>4105.734585564578</v>
+        <v>4450.605681680868</v>
       </c>
       <c r="E99">
         <v>13510.581</v>
@@ -9411,37 +9411,37 @@
         <v>1187.8</v>
       </c>
       <c r="M99">
-        <v>4476.9179598</v>
+        <v>4165.732744800001</v>
       </c>
       <c r="N99">
-        <v>-3289.1179598</v>
+        <v>-2977.932744800001</v>
       </c>
       <c r="O99">
-        <v>-848.5924336284002</v>
+        <v>-768.3066481584002</v>
       </c>
       <c r="P99">
-        <v>-2440.5255261716</v>
+        <v>-2209.626096641601</v>
       </c>
       <c r="Q99">
-        <v>-1092.1255261716</v>
+        <v>-861.2260966416006</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.7641401350564296</v>
+        <v>0.75986438009367</v>
       </c>
       <c r="T99">
-        <v>16.57917566322382</v>
+        <v>16.49109422849123</v>
       </c>
       <c r="U99">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.06845164525053977</v>
+        <v>0.07356506496547054</v>
       </c>
       <c r="W99">
-        <v>0.2010281349549335</v>
+        <v>0.1860281349549335</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2653164544594565</v>
+        <v>0.285135910718878</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2196214949579784</v>
+        <v>0.2047932223090956</v>
       </c>
       <c r="C100">
-        <v>-16394.07644751318</v>
+        <v>-16051.81896417787</v>
       </c>
       <c r="D100">
-        <v>4069.177552486824</v>
+        <v>4411.435035822131</v>
       </c>
       <c r="E100">
         <v>13724.454</v>
@@ -9493,37 +9493,37 @@
         <v>1187.8</v>
       </c>
       <c r="M100">
-        <v>4523.071753200001</v>
+        <v>4208.678443200001</v>
       </c>
       <c r="N100">
-        <v>-3335.271753200001</v>
+        <v>-3020.878443200002</v>
       </c>
       <c r="O100">
-        <v>-860.5001123256003</v>
+        <v>-779.3866383456004</v>
       </c>
       <c r="P100">
-        <v>-2474.771640874401</v>
+        <v>-2241.491804854401</v>
       </c>
       <c r="Q100">
-        <v>-1126.371640874401</v>
+        <v>-893.0918048544013</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.123310202584644</v>
+        <v>1.116896570140505</v>
       </c>
       <c r="T100">
-        <v>24.86876349483573</v>
+        <v>24.73664134273684</v>
       </c>
       <c r="U100">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.06775315907451385</v>
+        <v>0.07281440103725144</v>
       </c>
       <c r="W100">
-        <v>0.2011788682717199</v>
+        <v>0.1861788682717199</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2626091436996661</v>
+        <v>0.2822263606095017</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2213214949579784</v>
+        <v>0.2063432223090956</v>
       </c>
       <c r="C101">
-        <v>-16643.86122584284</v>
+        <v>-16304.17912855109</v>
       </c>
       <c r="D101">
-        <v>4033.265774157158</v>
+        <v>4372.94787144891</v>
       </c>
       <c r="E101">
         <v>13938.327</v>
@@ -9575,37 +9575,37 @@
         <v>1187.8</v>
       </c>
       <c r="M101">
-        <v>4569.225546600002</v>
+        <v>4251.624141600001</v>
       </c>
       <c r="N101">
-        <v>-3381.425546600002</v>
+        <v>-3063.824141600001</v>
       </c>
       <c r="O101">
-        <v>-872.4077910228004</v>
+        <v>-790.4666285328004</v>
       </c>
       <c r="P101">
-        <v>-2509.017755577202</v>
+        <v>-2273.357513067201</v>
       </c>
       <c r="Q101">
-        <v>-1160.617755577201</v>
+        <v>-924.957513067201</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.200820405169289</v>
+        <v>2.18799314028101</v>
       </c>
       <c r="T101">
-        <v>49.73752698967144</v>
+        <v>49.47328268547368</v>
       </c>
       <c r="U101">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V101">
-        <v>0.06706878373032683</v>
+        <v>0.07207890203687516</v>
       </c>
       <c r="W101">
-        <v>0.2013265564709955</v>
+        <v>0.1863265564709955</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.2599565260865381</v>
+        <v>0.2793755892902138</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/netherlands/netherlands_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_telecom_services.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06886802191789448</v>
+        <v>0.06872373242134631</v>
       </c>
       <c r="C2">
-        <v>19828.51329561332</v>
+        <v>19684.30134491922</v>
       </c>
       <c r="D2">
-        <v>19332.21329561332</v>
+        <v>19401.87434491922</v>
       </c>
       <c r="E2">
-        <v>-7235.1</v>
+        <v>-7021.227000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>213.873</v>
       </c>
       <c r="G2">
         <v>496.3</v>
@@ -1457,28 +1457,28 @@
         <v>1187.8</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>10.7578119</v>
       </c>
       <c r="N2">
-        <v>1187.8</v>
+        <v>1177.0421881</v>
       </c>
       <c r="O2">
-        <v>306.4524</v>
+        <v>303.6768845298</v>
       </c>
       <c r="P2">
-        <v>881.3475999999998</v>
+        <v>873.3653035701998</v>
       </c>
       <c r="Q2">
-        <v>2229.7476</v>
+        <v>2221.7653035702</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06886802191789448</v>
+        <v>0.06904091557711749</v>
       </c>
       <c r="T2">
-        <v>0.532748774085323</v>
+        <v>0.5367416992405887</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>110.4127875669586</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06872373242134631</v>
+        <v>0.06857944292479813</v>
       </c>
       <c r="C3">
-        <v>19684.30134491922</v>
+        <v>19540.59323833968</v>
       </c>
       <c r="D3">
-        <v>19401.87434491922</v>
+        <v>19472.03923833968</v>
       </c>
       <c r="E3">
-        <v>-7021.227000000001</v>
+        <v>-6807.354</v>
       </c>
       <c r="F3">
-        <v>213.873</v>
+        <v>427.7460000000001</v>
       </c>
       <c r="G3">
         <v>496.3</v>
@@ -1539,28 +1539,28 @@
         <v>1187.8</v>
       </c>
       <c r="M3">
-        <v>10.7578119</v>
+        <v>21.51562380000001</v>
       </c>
       <c r="N3">
-        <v>1177.0421881</v>
+        <v>1166.2843762</v>
       </c>
       <c r="O3">
-        <v>303.6768845298</v>
+        <v>300.9013690596</v>
       </c>
       <c r="P3">
-        <v>873.3653035701998</v>
+        <v>865.3830071403997</v>
       </c>
       <c r="Q3">
-        <v>2221.7653035702</v>
+        <v>2213.7830071404</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06904091557711749</v>
+        <v>0.06921733767836545</v>
       </c>
       <c r="T3">
-        <v>0.5367416992405887</v>
+        <v>0.5408161126643293</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>110.4127875669586</v>
+        <v>55.20639378347931</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06857944292479813</v>
+        <v>0.06843515342824996</v>
       </c>
       <c r="C4">
-        <v>19540.59323833968</v>
+        <v>19397.39446201685</v>
       </c>
       <c r="D4">
-        <v>19472.03923833968</v>
+        <v>19542.71346201685</v>
       </c>
       <c r="E4">
-        <v>-6807.354</v>
+        <v>-6593.481000000001</v>
       </c>
       <c r="F4">
-        <v>427.7460000000001</v>
+        <v>641.619</v>
       </c>
       <c r="G4">
         <v>496.3</v>
@@ -1621,28 +1621,28 @@
         <v>1187.8</v>
       </c>
       <c r="M4">
-        <v>21.51562380000001</v>
+        <v>32.27343570000001</v>
       </c>
       <c r="N4">
-        <v>1166.2843762</v>
+        <v>1155.5265643</v>
       </c>
       <c r="O4">
-        <v>300.9013690596</v>
+        <v>298.1258535894</v>
       </c>
       <c r="P4">
-        <v>865.3830071403997</v>
+        <v>857.4007107105998</v>
       </c>
       <c r="Q4">
-        <v>2213.7830071404</v>
+        <v>2205.8007107106</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06921733767836545</v>
+        <v>0.06939739734871131</v>
       </c>
       <c r="T4">
-        <v>0.5408161126643293</v>
+        <v>0.5449745346122706</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>55.20639378347931</v>
+        <v>36.80426252231954</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06843515342824996</v>
+        <v>0.06829086393170181</v>
       </c>
       <c r="C5">
-        <v>19397.39446201685</v>
+        <v>19254.7105820313</v>
       </c>
       <c r="D5">
-        <v>19542.71346201685</v>
+        <v>19613.9025820313</v>
       </c>
       <c r="E5">
-        <v>-6593.481000000001</v>
+        <v>-6379.608</v>
       </c>
       <c r="F5">
-        <v>641.619</v>
+        <v>855.4920000000002</v>
       </c>
       <c r="G5">
         <v>496.3</v>
@@ -1703,28 +1703,28 @@
         <v>1187.8</v>
       </c>
       <c r="M5">
-        <v>32.27343570000001</v>
+        <v>43.03124760000001</v>
       </c>
       <c r="N5">
-        <v>1155.5265643</v>
+        <v>1144.7687524</v>
       </c>
       <c r="O5">
-        <v>298.1258535894</v>
+        <v>295.3503381191999</v>
       </c>
       <c r="P5">
-        <v>857.4007107105998</v>
+        <v>849.4184142807999</v>
       </c>
       <c r="Q5">
-        <v>2205.8007107106</v>
+        <v>2197.8184142808</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06939739734871131</v>
+        <v>0.06958120826218939</v>
       </c>
       <c r="T5">
-        <v>0.5449745346122706</v>
+        <v>0.5492195903507942</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>36.80426252231954</v>
+        <v>27.60319689173965</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06829086393170181</v>
+        <v>0.06814657443515362</v>
       </c>
       <c r="C6">
-        <v>19254.7105820313</v>
+        <v>19112.54724586345</v>
       </c>
       <c r="D6">
-        <v>19613.9025820313</v>
+        <v>19685.61224586345</v>
       </c>
       <c r="E6">
-        <v>-6379.608</v>
+        <v>-6165.735000000001</v>
       </c>
       <c r="F6">
-        <v>855.4920000000002</v>
+        <v>1069.365</v>
       </c>
       <c r="G6">
         <v>496.3</v>
@@ -1785,28 +1785,28 @@
         <v>1187.8</v>
       </c>
       <c r="M6">
-        <v>43.03124760000001</v>
+        <v>53.78905950000001</v>
       </c>
       <c r="N6">
-        <v>1144.7687524</v>
+        <v>1134.0109405</v>
       </c>
       <c r="O6">
-        <v>295.3503381191999</v>
+        <v>292.5748226489999</v>
       </c>
       <c r="P6">
-        <v>849.4184142807999</v>
+        <v>841.4361178509997</v>
       </c>
       <c r="Q6">
-        <v>2197.8184142808</v>
+        <v>2189.836117851</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.06958120826218939</v>
+        <v>0.06976888887910909</v>
       </c>
       <c r="T6">
-        <v>0.5492195903507942</v>
+        <v>0.553554015683813</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>27.60319689173965</v>
+        <v>22.08255751339172</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06814657443515362</v>
+        <v>0.06800228493860548</v>
       </c>
       <c r="C7">
-        <v>19112.54724586345</v>
+        <v>18970.91018388685</v>
       </c>
       <c r="D7">
-        <v>19685.61224586345</v>
+        <v>19757.84818388685</v>
       </c>
       <c r="E7">
-        <v>-6165.735000000001</v>
+        <v>-5951.862</v>
       </c>
       <c r="F7">
-        <v>1069.365</v>
+        <v>1283.238</v>
       </c>
       <c r="G7">
         <v>496.3</v>
@@ -1867,28 +1867,28 @@
         <v>1187.8</v>
       </c>
       <c r="M7">
-        <v>53.78905950000001</v>
+        <v>64.54687140000001</v>
       </c>
       <c r="N7">
-        <v>1134.0109405</v>
+        <v>1123.2531286</v>
       </c>
       <c r="O7">
-        <v>292.5748226489999</v>
+        <v>289.7993071787999</v>
       </c>
       <c r="P7">
-        <v>841.4361178509997</v>
+        <v>833.4538214211998</v>
       </c>
       <c r="Q7">
-        <v>2189.836117851</v>
+        <v>2181.8538214212</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.06976888887910909</v>
+        <v>0.06996056270064413</v>
       </c>
       <c r="T7">
-        <v>0.553554015683813</v>
+        <v>0.5579806628324279</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>22.08255751339172</v>
+        <v>18.40213126115977</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06800228493860548</v>
+        <v>0.06785799544205731</v>
       </c>
       <c r="C8">
-        <v>18970.91018388685</v>
+        <v>18829.80521089487</v>
       </c>
       <c r="D8">
-        <v>19757.84818388685</v>
+        <v>19830.61621089487</v>
       </c>
       <c r="E8">
-        <v>-5951.862</v>
+        <v>-5737.989</v>
       </c>
       <c r="F8">
-        <v>1283.238</v>
+        <v>1497.111</v>
       </c>
       <c r="G8">
         <v>496.3</v>
@@ -1949,28 +1949,28 @@
         <v>1187.8</v>
       </c>
       <c r="M8">
-        <v>64.54687140000001</v>
+        <v>75.30468330000001</v>
       </c>
       <c r="N8">
-        <v>1123.2531286</v>
+        <v>1112.4953167</v>
       </c>
       <c r="O8">
-        <v>289.7993071787999</v>
+        <v>287.0237917085999</v>
       </c>
       <c r="P8">
-        <v>833.4538214211998</v>
+        <v>825.4715249913997</v>
       </c>
       <c r="Q8">
-        <v>2181.8538214212</v>
+        <v>2173.8715249914</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.06996056270064413</v>
+        <v>0.07015635853984656</v>
       </c>
       <c r="T8">
-        <v>0.5579806628324279</v>
+        <v>0.5625025066939161</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>18.40213126115977</v>
+        <v>15.77325536670837</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0678579954420573</v>
+        <v>0.06771370594550914</v>
       </c>
       <c r="C9">
-        <v>18829.80521089487</v>
+        <v>18689.23822766086</v>
       </c>
       <c r="D9">
-        <v>19830.61621089487</v>
+        <v>19903.92222766086</v>
       </c>
       <c r="E9">
-        <v>-5737.989</v>
+        <v>-5524.116</v>
       </c>
       <c r="F9">
-        <v>1497.111</v>
+        <v>1710.984</v>
       </c>
       <c r="G9">
         <v>496.3</v>
@@ -2031,28 +2031,28 @@
         <v>1187.8</v>
       </c>
       <c r="M9">
-        <v>75.30468330000002</v>
+        <v>86.06249520000003</v>
       </c>
       <c r="N9">
-        <v>1112.4953167</v>
+        <v>1101.7375048</v>
       </c>
       <c r="O9">
-        <v>287.0237917085999</v>
+        <v>284.2482762383999</v>
       </c>
       <c r="P9">
-        <v>825.4715249913997</v>
+        <v>817.4892285615997</v>
       </c>
       <c r="Q9">
-        <v>2173.8715249914</v>
+        <v>2165.8892285616</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07015635853984656</v>
+        <v>0.07035641081033601</v>
       </c>
       <c r="T9">
-        <v>0.5625025066939161</v>
+        <v>0.5671226515089151</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>15.77325536670837</v>
+        <v>13.80159844586982</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06771370594550914</v>
+        <v>0.06756941644896097</v>
       </c>
       <c r="C10">
-        <v>18689.23822766086</v>
+        <v>18549.21522253331</v>
       </c>
       <c r="D10">
-        <v>19903.92222766086</v>
+        <v>19977.77222253331</v>
       </c>
       <c r="E10">
-        <v>-5524.116</v>
+        <v>-5310.243</v>
       </c>
       <c r="F10">
-        <v>1710.984</v>
+        <v>1924.857</v>
       </c>
       <c r="G10">
         <v>496.3</v>
@@ -2113,28 +2113,28 @@
         <v>1187.8</v>
       </c>
       <c r="M10">
-        <v>86.06249520000003</v>
+        <v>96.82030710000002</v>
       </c>
       <c r="N10">
-        <v>1101.7375048</v>
+        <v>1090.9796929</v>
       </c>
       <c r="O10">
-        <v>284.2482762383999</v>
+        <v>281.4727607681999</v>
       </c>
       <c r="P10">
-        <v>817.4892285615997</v>
+        <v>809.5069321317998</v>
       </c>
       <c r="Q10">
-        <v>2165.8892285616</v>
+        <v>2157.9069321318</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07035641081033601</v>
+        <v>0.07056085983402305</v>
       </c>
       <c r="T10">
-        <v>0.5671226515089151</v>
+        <v>0.5718443379681998</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>13.80159844586982</v>
+        <v>12.26808750743985</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06756941644896097</v>
+        <v>0.0674251269524128</v>
       </c>
       <c r="C11">
-        <v>18549.21522253331</v>
+        <v>18409.74227306654</v>
       </c>
       <c r="D11">
-        <v>19977.77222253331</v>
+        <v>20052.17227306654</v>
       </c>
       <c r="E11">
-        <v>-5310.243</v>
+        <v>-5096.370000000001</v>
       </c>
       <c r="F11">
-        <v>1924.857</v>
+        <v>2138.73</v>
       </c>
       <c r="G11">
         <v>496.3</v>
@@ -2195,28 +2195,28 @@
         <v>1187.8</v>
       </c>
       <c r="M11">
-        <v>96.82030710000002</v>
+        <v>107.578119</v>
       </c>
       <c r="N11">
-        <v>1090.9796929</v>
+        <v>1080.221881</v>
       </c>
       <c r="O11">
-        <v>281.4727607681999</v>
+        <v>278.6972452979999</v>
       </c>
       <c r="P11">
-        <v>809.5069321317998</v>
+        <v>801.5246357019998</v>
       </c>
       <c r="Q11">
-        <v>2157.9069321318</v>
+        <v>2149.924635702</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07056085983402305</v>
+        <v>0.07076985216934756</v>
       </c>
       <c r="T11">
-        <v>0.5718443379681998</v>
+        <v>0.5766709507932463</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>12.26808750743985</v>
+        <v>11.04127875669586</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0674251269524128</v>
+        <v>0.06728083745586465</v>
       </c>
       <c r="C12">
-        <v>18409.74227306654</v>
+        <v>18270.82554768797</v>
       </c>
       <c r="D12">
-        <v>20052.17227306654</v>
+        <v>20127.12854768797</v>
       </c>
       <c r="E12">
-        <v>-5096.37</v>
+        <v>-4882.496999999999</v>
       </c>
       <c r="F12">
-        <v>2138.73</v>
+        <v>2352.603000000001</v>
       </c>
       <c r="G12">
         <v>496.3</v>
@@ -2277,28 +2277,28 @@
         <v>1187.8</v>
       </c>
       <c r="M12">
-        <v>107.578119</v>
+        <v>118.3359309</v>
       </c>
       <c r="N12">
-        <v>1080.221881</v>
+        <v>1069.4640691</v>
       </c>
       <c r="O12">
-        <v>278.6972452979999</v>
+        <v>275.9217298277999</v>
       </c>
       <c r="P12">
-        <v>801.5246357019998</v>
+        <v>793.5423392721998</v>
       </c>
       <c r="Q12">
-        <v>2149.924635702</v>
+        <v>2141.9423392722</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07076985216934756</v>
+        <v>0.07098354096164566</v>
       </c>
       <c r="T12">
-        <v>0.5766709507932463</v>
+        <v>0.5816060268278443</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.04127875669586</v>
+        <v>10.03752614245078</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06728083745586465</v>
+        <v>0.06713654795931646</v>
       </c>
       <c r="C13">
-        <v>18270.82554768797</v>
+        <v>18132.471307403</v>
       </c>
       <c r="D13">
-        <v>20127.12854768797</v>
+        <v>20202.647307403</v>
       </c>
       <c r="E13">
-        <v>-4882.496999999999</v>
+        <v>-4668.624</v>
       </c>
       <c r="F13">
-        <v>2352.603000000001</v>
+        <v>2566.476</v>
       </c>
       <c r="G13">
         <v>496.3</v>
@@ -2359,28 +2359,28 @@
         <v>1187.8</v>
       </c>
       <c r="M13">
-        <v>118.3359309</v>
+        <v>129.0937428</v>
       </c>
       <c r="N13">
-        <v>1069.4640691</v>
+        <v>1058.7062572</v>
       </c>
       <c r="O13">
-        <v>275.9217298277999</v>
+        <v>273.1462143575999</v>
       </c>
       <c r="P13">
-        <v>793.5423392721998</v>
+        <v>785.5600428423998</v>
       </c>
       <c r="Q13">
-        <v>2141.9423392722</v>
+        <v>2133.9600428424</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07098354096164566</v>
+        <v>0.07120208631740507</v>
       </c>
       <c r="T13">
-        <v>0.5816060268278443</v>
+        <v>0.5866532636814107</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.03752614245078</v>
+        <v>9.201065630579885</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06713654795931646</v>
+        <v>0.0671369484627683</v>
       </c>
       <c r="C14">
-        <v>18132.471307403</v>
+        <v>17918.38790614465</v>
       </c>
       <c r="D14">
-        <v>20202.647307403</v>
+        <v>20202.43690614466</v>
       </c>
       <c r="E14">
-        <v>-4668.624</v>
+        <v>-4454.751</v>
       </c>
       <c r="F14">
-        <v>2566.476</v>
+        <v>2780.349000000001</v>
       </c>
       <c r="G14">
         <v>496.3</v>
@@ -2441,45 +2441,45 @@
         <v>1187.8</v>
       </c>
       <c r="M14">
-        <v>129.0937428</v>
+        <v>144.0220782</v>
       </c>
       <c r="N14">
-        <v>1058.7062572</v>
+        <v>1043.7779218</v>
       </c>
       <c r="O14">
-        <v>273.1462143575999</v>
+        <v>269.2947038243999</v>
       </c>
       <c r="P14">
-        <v>785.5600428423998</v>
+        <v>774.4832179755997</v>
       </c>
       <c r="Q14">
-        <v>2133.9600428424</v>
+        <v>2122.8832179756</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07120208631740507</v>
+        <v>0.07142565570433138</v>
       </c>
       <c r="T14">
-        <v>0.5866532636814107</v>
+        <v>0.5918165289683922</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V14">
         <v>0.258</v>
       </c>
       <c r="W14">
-        <v>0.0373226</v>
+        <v>0.03843560000000001</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>9.201065630579885</v>
+        <v>8.247346621054376</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0671369484627683</v>
+        <v>0.06700378896622013</v>
       </c>
       <c r="C15">
-        <v>17918.38790614465</v>
+        <v>17774.7115099576</v>
       </c>
       <c r="D15">
-        <v>20202.43690614466</v>
+        <v>20272.6335099576</v>
       </c>
       <c r="E15">
-        <v>-4454.751</v>
+        <v>-4240.878</v>
       </c>
       <c r="F15">
-        <v>2780.349000000001</v>
+        <v>2994.222000000001</v>
       </c>
       <c r="G15">
         <v>496.3</v>
@@ -2523,28 +2523,28 @@
         <v>1187.8</v>
       </c>
       <c r="M15">
-        <v>144.0220782</v>
+        <v>155.1006996</v>
       </c>
       <c r="N15">
-        <v>1043.7779218</v>
+        <v>1032.6993004</v>
       </c>
       <c r="O15">
-        <v>269.2947038243999</v>
+        <v>266.4364195031999</v>
       </c>
       <c r="P15">
-        <v>774.4832179755997</v>
+        <v>766.2628808967997</v>
       </c>
       <c r="Q15">
-        <v>2122.8832179756</v>
+        <v>2114.6628808968</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07142565570433138</v>
+        <v>0.07165442437932573</v>
       </c>
       <c r="T15">
-        <v>0.5918165289683922</v>
+        <v>0.5970998701922804</v>
       </c>
       <c r="U15">
         <v>0.05180000000000001</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.247346621054376</v>
+        <v>7.658250433836208</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06700378896622013</v>
+        <v>0.06687062946967197</v>
       </c>
       <c r="C16">
-        <v>17774.7115099576</v>
+        <v>17631.52463337818</v>
       </c>
       <c r="D16">
-        <v>20272.6335099576</v>
+        <v>20343.31963337818</v>
       </c>
       <c r="E16">
-        <v>-4240.878</v>
+        <v>-4027.005</v>
       </c>
       <c r="F16">
-        <v>2994.222000000001</v>
+        <v>3208.095000000001</v>
       </c>
       <c r="G16">
         <v>496.3</v>
@@ -2605,28 +2605,28 @@
         <v>1187.8</v>
       </c>
       <c r="M16">
-        <v>155.1006996</v>
+        <v>166.179321</v>
       </c>
       <c r="N16">
-        <v>1032.6993004</v>
+        <v>1021.620679</v>
       </c>
       <c r="O16">
-        <v>266.4364195031999</v>
+        <v>263.5781351819999</v>
       </c>
       <c r="P16">
-        <v>766.2628808967997</v>
+        <v>758.0425438179998</v>
       </c>
       <c r="Q16">
-        <v>2114.6628808968</v>
+        <v>2106.442543818</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07165442437932573</v>
+        <v>0.07188857584667289</v>
       </c>
       <c r="T16">
-        <v>0.5970998701922804</v>
+        <v>0.6025075253273188</v>
       </c>
       <c r="U16">
         <v>0.05180000000000001</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.658250433836208</v>
+        <v>7.147700404913794</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06687062946967195</v>
+        <v>0.06693929397312379</v>
       </c>
       <c r="C17">
-        <v>17631.52463337819</v>
+        <v>17381.14045858625</v>
       </c>
       <c r="D17">
-        <v>20343.31963337819</v>
+        <v>20306.80845858626</v>
       </c>
       <c r="E17">
-        <v>-4027.005</v>
+        <v>-3813.132</v>
       </c>
       <c r="F17">
-        <v>3208.095</v>
+        <v>3421.968000000001</v>
       </c>
       <c r="G17">
         <v>496.3</v>
@@ -2687,45 +2687,45 @@
         <v>1187.8</v>
       </c>
       <c r="M17">
-        <v>166.179321</v>
+        <v>183.0752880000001</v>
       </c>
       <c r="N17">
-        <v>1021.620679</v>
+        <v>1004.724712</v>
       </c>
       <c r="O17">
-        <v>263.5781351819999</v>
+        <v>259.2189756959999</v>
       </c>
       <c r="P17">
-        <v>758.0425438179998</v>
+        <v>745.5057363039998</v>
       </c>
       <c r="Q17">
-        <v>2106.442543818</v>
+        <v>2093.905736304</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07188857584667289</v>
+        <v>0.0721283023489569</v>
       </c>
       <c r="T17">
-        <v>0.6025075253273188</v>
+        <v>0.6080439341560486</v>
       </c>
       <c r="U17">
-        <v>0.05180000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V17">
         <v>0.258</v>
       </c>
       <c r="W17">
-        <v>0.03843560000000001</v>
+        <v>0.039697</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>7.147700404913794</v>
+        <v>6.488041138572451</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06693929397312379</v>
+        <v>0.06681874847657562</v>
       </c>
       <c r="C18">
-        <v>17381.14045858625</v>
+        <v>17231.45265941477</v>
       </c>
       <c r="D18">
-        <v>20306.80845858626</v>
+        <v>20370.99365941477</v>
       </c>
       <c r="E18">
-        <v>-3813.132</v>
+        <v>-3599.259</v>
       </c>
       <c r="F18">
-        <v>3421.968000000001</v>
+        <v>3635.841000000001</v>
       </c>
       <c r="G18">
         <v>496.3</v>
@@ -2769,28 +2769,28 @@
         <v>1187.8</v>
       </c>
       <c r="M18">
-        <v>183.0752880000001</v>
+        <v>194.5174935000001</v>
       </c>
       <c r="N18">
-        <v>1004.724712</v>
+        <v>993.2825064999997</v>
       </c>
       <c r="O18">
-        <v>259.2189756959999</v>
+        <v>256.2668866769999</v>
       </c>
       <c r="P18">
-        <v>745.5057363039998</v>
+        <v>737.0156198229997</v>
       </c>
       <c r="Q18">
-        <v>2093.905736304</v>
+        <v>2085.415619823</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0721283023489569</v>
+        <v>0.07237380539346461</v>
       </c>
       <c r="T18">
-        <v>0.6080439341560486</v>
+        <v>0.6137137504264346</v>
       </c>
       <c r="U18">
         <v>0.05350000000000001</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.488041138572451</v>
+        <v>6.106391659832895</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06681874847657562</v>
+        <v>0.06669820298002746</v>
       </c>
       <c r="C19">
-        <v>17231.45265941477</v>
+        <v>17082.17189642164</v>
       </c>
       <c r="D19">
-        <v>20370.99365941477</v>
+        <v>20435.58589642164</v>
       </c>
       <c r="E19">
-        <v>-3599.259</v>
+        <v>-3385.386</v>
       </c>
       <c r="F19">
-        <v>3635.841000000001</v>
+        <v>3849.714000000001</v>
       </c>
       <c r="G19">
         <v>496.3</v>
@@ -2851,28 +2851,28 @@
         <v>1187.8</v>
       </c>
       <c r="M19">
-        <v>194.5174935000001</v>
+        <v>205.9596990000001</v>
       </c>
       <c r="N19">
-        <v>993.2825064999997</v>
+        <v>981.8403009999997</v>
       </c>
       <c r="O19">
-        <v>256.2668866769999</v>
+        <v>253.3147976579999</v>
       </c>
       <c r="P19">
-        <v>737.0156198229997</v>
+        <v>728.5255033419998</v>
       </c>
       <c r="Q19">
-        <v>2085.415619823</v>
+        <v>2076.925503342</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07237380539346461</v>
+        <v>0.07262529631710665</v>
       </c>
       <c r="T19">
-        <v>0.6137137504264346</v>
+        <v>0.6195218548985372</v>
       </c>
       <c r="U19">
         <v>0.05350000000000001</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.106391659832895</v>
+        <v>5.767147678731068</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06669820298002746</v>
+        <v>0.0666904414834793</v>
       </c>
       <c r="C20">
-        <v>17082.17189642164</v>
+        <v>16872.47180007003</v>
       </c>
       <c r="D20">
-        <v>20435.58589642164</v>
+        <v>20439.75880007003</v>
       </c>
       <c r="E20">
-        <v>-3385.386</v>
+        <v>-3171.513</v>
       </c>
       <c r="F20">
-        <v>3849.714</v>
+        <v>4063.587</v>
       </c>
       <c r="G20">
         <v>496.3</v>
@@ -2933,45 +2933,45 @@
         <v>1187.8</v>
       </c>
       <c r="M20">
-        <v>205.9596990000001</v>
+        <v>220.6527741</v>
       </c>
       <c r="N20">
-        <v>981.8403009999997</v>
+        <v>967.1472258999997</v>
       </c>
       <c r="O20">
-        <v>253.3147976579999</v>
+        <v>249.5239842821999</v>
       </c>
       <c r="P20">
-        <v>728.5255033419998</v>
+        <v>717.6232416177997</v>
       </c>
       <c r="Q20">
-        <v>2076.925503342</v>
+        <v>2066.0232416178</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07262529631710665</v>
+        <v>0.07288299689318431</v>
       </c>
       <c r="T20">
-        <v>0.6195218548985372</v>
+        <v>0.6254733693576054</v>
       </c>
       <c r="U20">
-        <v>0.05350000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V20">
         <v>0.258</v>
       </c>
       <c r="W20">
-        <v>0.039697</v>
+        <v>0.0402906</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>5.767147678731068</v>
+        <v>5.383118362525947</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0666904414834793</v>
+        <v>0.06657583198693112</v>
       </c>
       <c r="C21">
-        <v>16872.47180007003</v>
+        <v>16720.41661643094</v>
       </c>
       <c r="D21">
-        <v>20439.75880007003</v>
+        <v>20501.57661643094</v>
       </c>
       <c r="E21">
-        <v>-3171.513</v>
+        <v>-2957.639999999999</v>
       </c>
       <c r="F21">
-        <v>4063.587</v>
+        <v>4277.460000000001</v>
       </c>
       <c r="G21">
         <v>496.3</v>
@@ -3015,28 +3015,28 @@
         <v>1187.8</v>
       </c>
       <c r="M21">
-        <v>220.6527741</v>
+        <v>232.2660780000001</v>
       </c>
       <c r="N21">
-        <v>967.1472258999997</v>
+        <v>955.5339219999996</v>
       </c>
       <c r="O21">
-        <v>249.5239842821999</v>
+        <v>246.5277518759999</v>
       </c>
       <c r="P21">
-        <v>717.6232416177997</v>
+        <v>709.0061701239997</v>
       </c>
       <c r="Q21">
-        <v>2066.0232416178</v>
+        <v>2057.406170124</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07288299689318431</v>
+        <v>0.0731471399836639</v>
       </c>
       <c r="T21">
-        <v>0.6254733693576054</v>
+        <v>0.6315736716781504</v>
       </c>
       <c r="U21">
         <v>0.05430000000000001</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.383118362525947</v>
+        <v>5.113962444399648</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06657583198693112</v>
+        <v>0.06646122249038296</v>
       </c>
       <c r="C22">
-        <v>16720.41661643094</v>
+        <v>16568.73648956747</v>
       </c>
       <c r="D22">
-        <v>20501.57661643094</v>
+        <v>20563.76948956747</v>
       </c>
       <c r="E22">
-        <v>-2957.639999999999</v>
+        <v>-2743.766999999999</v>
       </c>
       <c r="F22">
-        <v>4277.460000000001</v>
+        <v>4491.333000000001</v>
       </c>
       <c r="G22">
         <v>496.3</v>
@@ -3097,28 +3097,28 @@
         <v>1187.8</v>
       </c>
       <c r="M22">
-        <v>232.2660780000001</v>
+        <v>243.8793819000001</v>
       </c>
       <c r="N22">
-        <v>955.5339219999996</v>
+        <v>943.9206180999996</v>
       </c>
       <c r="O22">
-        <v>246.5277518759999</v>
+        <v>243.5315194697999</v>
       </c>
       <c r="P22">
-        <v>709.0061701239997</v>
+        <v>700.3890986301997</v>
       </c>
       <c r="Q22">
-        <v>2057.406170124</v>
+        <v>2048.7890986302</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0731471399836639</v>
+        <v>0.07341797024099109</v>
       </c>
       <c r="T22">
-        <v>0.6315736716781504</v>
+        <v>0.6378284120321268</v>
       </c>
       <c r="U22">
         <v>0.05430000000000001</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.113962444399648</v>
+        <v>4.87044042323776</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06646122249038296</v>
+        <v>0.06634661299383479</v>
       </c>
       <c r="C23">
-        <v>16568.73648956747</v>
+        <v>16417.43484314328</v>
       </c>
       <c r="D23">
-        <v>20563.76948956747</v>
+        <v>20626.34084314329</v>
       </c>
       <c r="E23">
-        <v>-2743.767</v>
+        <v>-2529.893999999999</v>
       </c>
       <c r="F23">
-        <v>4491.333000000001</v>
+        <v>4705.206000000001</v>
       </c>
       <c r="G23">
         <v>496.3</v>
@@ -3179,28 +3179,28 @@
         <v>1187.8</v>
       </c>
       <c r="M23">
-        <v>243.8793819000001</v>
+        <v>255.4926858000001</v>
       </c>
       <c r="N23">
-        <v>943.9206180999997</v>
+        <v>932.3073141999996</v>
       </c>
       <c r="O23">
-        <v>243.5315194697999</v>
+        <v>240.5352870635999</v>
       </c>
       <c r="P23">
-        <v>700.3890986301998</v>
+        <v>691.7720271363997</v>
       </c>
       <c r="Q23">
-        <v>2048.7890986302</v>
+        <v>2040.1720271364</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07341797024099109</v>
+        <v>0.07369574486389076</v>
       </c>
       <c r="T23">
-        <v>0.6378284120321267</v>
+        <v>0.6442435303438975</v>
       </c>
       <c r="U23">
         <v>0.05430000000000001</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.870440423237761</v>
+        <v>4.649056767636043</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06634661299383479</v>
+        <v>0.06623200349728663</v>
       </c>
       <c r="C24">
-        <v>16417.43484314328</v>
+        <v>16266.51514261928</v>
       </c>
       <c r="D24">
-        <v>20626.34084314329</v>
+        <v>20689.29414261928</v>
       </c>
       <c r="E24">
-        <v>-2529.893999999999</v>
+        <v>-2316.021</v>
       </c>
       <c r="F24">
-        <v>4705.206000000001</v>
+        <v>4919.079000000001</v>
       </c>
       <c r="G24">
         <v>496.3</v>
@@ -3261,28 +3261,28 @@
         <v>1187.8</v>
       </c>
       <c r="M24">
-        <v>255.4926858000001</v>
+        <v>267.1059897000001</v>
       </c>
       <c r="N24">
-        <v>932.3073141999996</v>
+        <v>920.6940102999997</v>
       </c>
       <c r="O24">
-        <v>240.5352870635999</v>
+        <v>237.5390546573999</v>
       </c>
       <c r="P24">
-        <v>691.7720271363997</v>
+        <v>683.1549556425998</v>
       </c>
       <c r="Q24">
-        <v>2040.1720271364</v>
+        <v>2031.5549556426</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07369574486389076</v>
+        <v>0.07398073441206054</v>
       </c>
       <c r="T24">
-        <v>0.6442435303438975</v>
+        <v>0.6508252751053245</v>
       </c>
       <c r="U24">
         <v>0.05430000000000001</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.649056767636043</v>
+        <v>4.446923864695346</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06623200349728663</v>
+        <v>0.06611739400073846</v>
       </c>
       <c r="C25">
-        <v>16266.51514261928</v>
+        <v>16115.98089589333</v>
       </c>
       <c r="D25">
-        <v>20689.29414261928</v>
+        <v>20752.63289589333</v>
       </c>
       <c r="E25">
-        <v>-2316.021</v>
+        <v>-2102.147999999999</v>
       </c>
       <c r="F25">
-        <v>4919.079000000001</v>
+        <v>5132.952000000001</v>
       </c>
       <c r="G25">
         <v>496.3</v>
@@ -3343,28 +3343,28 @@
         <v>1187.8</v>
       </c>
       <c r="M25">
-        <v>267.1059897000001</v>
+        <v>278.7192936000001</v>
       </c>
       <c r="N25">
-        <v>920.6940102999997</v>
+        <v>909.0807063999996</v>
       </c>
       <c r="O25">
-        <v>237.5390546573999</v>
+        <v>234.5428222511999</v>
       </c>
       <c r="P25">
-        <v>683.1549556425998</v>
+        <v>674.5378841487997</v>
       </c>
       <c r="Q25">
-        <v>2031.5549556426</v>
+        <v>2022.9378841488</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07398073441206054</v>
+        <v>0.07427322368518217</v>
       </c>
       <c r="T25">
-        <v>0.6508252751053245</v>
+        <v>0.6575802236762629</v>
       </c>
       <c r="U25">
         <v>0.05430000000000001</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.446923864695346</v>
+        <v>4.261635370333039</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06611739400073846</v>
+        <v>0.0661882845041903</v>
       </c>
       <c r="C26">
-        <v>16115.98089589333</v>
+        <v>15862.88470803122</v>
       </c>
       <c r="D26">
-        <v>20752.63289589333</v>
+        <v>20713.40970803122</v>
       </c>
       <c r="E26">
-        <v>-2102.148</v>
+        <v>-1888.275</v>
       </c>
       <c r="F26">
-        <v>5132.952</v>
+        <v>5346.825000000001</v>
       </c>
       <c r="G26">
         <v>496.3</v>
@@ -3425,45 +3425,45 @@
         <v>1187.8</v>
       </c>
       <c r="M26">
-        <v>278.7192936000001</v>
+        <v>295.6794225000001</v>
       </c>
       <c r="N26">
-        <v>909.0807063999996</v>
+        <v>892.1205774999996</v>
       </c>
       <c r="O26">
-        <v>234.5428222511999</v>
+        <v>230.1671089949999</v>
       </c>
       <c r="P26">
-        <v>674.5378841487997</v>
+        <v>661.9534685049997</v>
       </c>
       <c r="Q26">
-        <v>2022.9378841488</v>
+        <v>2010.353468505</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07427322368518217</v>
+        <v>0.07457351267225372</v>
       </c>
       <c r="T26">
-        <v>0.6575802236762629</v>
+        <v>0.6645153042090929</v>
       </c>
       <c r="U26">
-        <v>0.05430000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V26">
         <v>0.258</v>
       </c>
       <c r="W26">
-        <v>0.0402906</v>
+        <v>0.04103260000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.261635370333041</v>
+        <v>4.017188582002182</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0661882845041903</v>
+        <v>0.06608109500764212</v>
       </c>
       <c r="C27">
-        <v>15862.88470803122</v>
+        <v>15708.37641928318</v>
       </c>
       <c r="D27">
-        <v>20713.40970803122</v>
+        <v>20772.77441928318</v>
       </c>
       <c r="E27">
-        <v>-1888.275</v>
+        <v>-1674.401999999999</v>
       </c>
       <c r="F27">
-        <v>5346.825000000001</v>
+        <v>5560.698000000001</v>
       </c>
       <c r="G27">
         <v>496.3</v>
@@ -3507,28 +3507,28 @@
         <v>1187.8</v>
       </c>
       <c r="M27">
-        <v>295.6794225000001</v>
+        <v>307.5065994000001</v>
       </c>
       <c r="N27">
-        <v>892.1205774999996</v>
+        <v>880.2934005999996</v>
       </c>
       <c r="O27">
-        <v>230.1671089949999</v>
+        <v>227.1156973547999</v>
       </c>
       <c r="P27">
-        <v>661.9534685049997</v>
+        <v>653.1777032451997</v>
       </c>
       <c r="Q27">
-        <v>2010.353468505</v>
+        <v>2001.5777032452</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07457351267225372</v>
+        <v>0.07488191757789475</v>
       </c>
       <c r="T27">
-        <v>0.6645153042090929</v>
+        <v>0.6716378193509183</v>
       </c>
       <c r="U27">
         <v>0.05530000000000001</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.017188582002182</v>
+        <v>3.862681328848252</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06608109500764212</v>
+        <v>0.06597390551109396</v>
       </c>
       <c r="C28">
-        <v>15708.37641928318</v>
+        <v>15554.20938755694</v>
       </c>
       <c r="D28">
-        <v>20772.77441928318</v>
+        <v>20832.48038755695</v>
       </c>
       <c r="E28">
-        <v>-1674.401999999999</v>
+        <v>-1460.529</v>
       </c>
       <c r="F28">
-        <v>5560.698000000001</v>
+        <v>5774.571000000001</v>
       </c>
       <c r="G28">
         <v>496.3</v>
@@ -3589,28 +3589,28 @@
         <v>1187.8</v>
       </c>
       <c r="M28">
-        <v>307.5065994000001</v>
+        <v>319.3337763000001</v>
       </c>
       <c r="N28">
-        <v>880.2934005999996</v>
+        <v>868.4662236999995</v>
       </c>
       <c r="O28">
-        <v>227.1156973547999</v>
+        <v>224.0642857145999</v>
       </c>
       <c r="P28">
-        <v>653.1777032451997</v>
+        <v>644.4019379853996</v>
       </c>
       <c r="Q28">
-        <v>2001.5777032452</v>
+        <v>1992.8019379854</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07488191757789475</v>
+        <v>0.07519877193300542</v>
       </c>
       <c r="T28">
-        <v>0.6716378193509183</v>
+        <v>0.6789554718938896</v>
       </c>
       <c r="U28">
         <v>0.05530000000000001</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.862681328848252</v>
+        <v>3.719619057409428</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06597390551109396</v>
+        <v>0.06586671601454579</v>
       </c>
       <c r="C29">
-        <v>15554.20938755694</v>
+        <v>15400.38656389973</v>
       </c>
       <c r="D29">
-        <v>20832.48038755695</v>
+        <v>20892.53056389973</v>
       </c>
       <c r="E29">
-        <v>-1460.529</v>
+        <v>-1246.655999999999</v>
       </c>
       <c r="F29">
-        <v>5774.571000000001</v>
+        <v>5988.444000000001</v>
       </c>
       <c r="G29">
         <v>496.3</v>
@@ -3671,28 +3671,28 @@
         <v>1187.8</v>
       </c>
       <c r="M29">
-        <v>319.3337763000001</v>
+        <v>331.1609532000001</v>
       </c>
       <c r="N29">
-        <v>868.4662236999995</v>
+        <v>856.6390467999996</v>
       </c>
       <c r="O29">
-        <v>224.0642857145999</v>
+        <v>221.0128740743999</v>
       </c>
       <c r="P29">
-        <v>644.4019379853996</v>
+        <v>635.6261727255996</v>
       </c>
       <c r="Q29">
-        <v>1992.8019379854</v>
+        <v>1984.0261727256</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07519877193300542</v>
+        <v>0.07552442779798026</v>
       </c>
       <c r="T29">
-        <v>0.6789554718938896</v>
+        <v>0.6864763925630546</v>
       </c>
       <c r="U29">
         <v>0.05530000000000001</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.719619057409428</v>
+        <v>3.586775519644806</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06586671601454579</v>
+        <v>0.06575952651799762</v>
       </c>
       <c r="C30">
-        <v>15400.38656389973</v>
+        <v>15246.910933483</v>
       </c>
       <c r="D30">
-        <v>20892.53056389973</v>
+        <v>20952.927933483</v>
       </c>
       <c r="E30">
-        <v>-1246.655999999999</v>
+        <v>-1032.782999999999</v>
       </c>
       <c r="F30">
-        <v>5988.444000000001</v>
+        <v>6202.317000000002</v>
       </c>
       <c r="G30">
         <v>496.3</v>
@@ -3753,28 +3753,28 @@
         <v>1187.8</v>
       </c>
       <c r="M30">
-        <v>331.1609532000001</v>
+        <v>342.9881301000001</v>
       </c>
       <c r="N30">
-        <v>856.6390467999996</v>
+        <v>844.8118698999996</v>
       </c>
       <c r="O30">
-        <v>221.0128740743999</v>
+        <v>217.9614624341999</v>
       </c>
       <c r="P30">
-        <v>635.6261727255996</v>
+        <v>626.8504074657997</v>
       </c>
       <c r="Q30">
-        <v>1984.0261727256</v>
+        <v>1975.2504074658</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07552442779798026</v>
+        <v>0.07585925706760227</v>
       </c>
       <c r="T30">
-        <v>0.6864763925630546</v>
+        <v>0.6942091701524775</v>
       </c>
       <c r="U30">
         <v>0.05530000000000001</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.586775519644806</v>
+        <v>3.463093605174295</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06575952651799762</v>
+        <v>0.06565233702144944</v>
       </c>
       <c r="C31">
-        <v>15246.910933483</v>
+        <v>15093.78551609712</v>
       </c>
       <c r="D31">
-        <v>20952.927933483</v>
+        <v>21013.67551609712</v>
       </c>
       <c r="E31">
-        <v>-1032.783</v>
+        <v>-818.9099999999999</v>
       </c>
       <c r="F31">
-        <v>6202.317</v>
+        <v>6416.190000000001</v>
       </c>
       <c r="G31">
         <v>496.3</v>
@@ -3835,28 +3835,28 @@
         <v>1187.8</v>
       </c>
       <c r="M31">
-        <v>342.9881301</v>
+        <v>354.8153070000001</v>
       </c>
       <c r="N31">
-        <v>844.8118698999997</v>
+        <v>832.9846929999997</v>
       </c>
       <c r="O31">
-        <v>217.9614624341999</v>
+        <v>214.9100507939999</v>
       </c>
       <c r="P31">
-        <v>626.8504074657998</v>
+        <v>618.0746422059997</v>
       </c>
       <c r="Q31">
-        <v>1975.2504074658</v>
+        <v>1966.474642206</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07585925706760227</v>
+        <v>0.07620365288778493</v>
       </c>
       <c r="T31">
-        <v>0.6942091701524775</v>
+        <v>0.7021628842444557</v>
       </c>
       <c r="U31">
         <v>0.05530000000000001</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.463093605174296</v>
+        <v>3.347657151668486</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06565233702144944</v>
+        <v>0.06554514752490129</v>
       </c>
       <c r="C32">
-        <v>15093.78551609712</v>
+        <v>14941.01336665469</v>
       </c>
       <c r="D32">
-        <v>21013.67551609712</v>
+        <v>21074.7763666547</v>
       </c>
       <c r="E32">
-        <v>-818.9099999999999</v>
+        <v>-605.0369999999994</v>
       </c>
       <c r="F32">
-        <v>6416.190000000001</v>
+        <v>6630.063000000001</v>
       </c>
       <c r="G32">
         <v>496.3</v>
@@ -3917,28 +3917,28 @@
         <v>1187.8</v>
       </c>
       <c r="M32">
-        <v>354.8153070000001</v>
+        <v>366.6424839000001</v>
       </c>
       <c r="N32">
-        <v>832.9846929999997</v>
+        <v>821.1575160999996</v>
       </c>
       <c r="O32">
-        <v>214.9100507939999</v>
+        <v>211.8586391537999</v>
       </c>
       <c r="P32">
-        <v>618.0746422059997</v>
+        <v>609.2988769461997</v>
       </c>
       <c r="Q32">
-        <v>1966.474642206</v>
+        <v>1957.6988769462</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07620365288778493</v>
+        <v>0.07655803119550911</v>
       </c>
       <c r="T32">
-        <v>0.7021628842444557</v>
+        <v>0.7103471407738824</v>
       </c>
       <c r="U32">
         <v>0.05530000000000001</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.347657151668486</v>
+        <v>3.239668211292083</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06554514752490129</v>
+        <v>0.06543795802835312</v>
       </c>
       <c r="C33">
-        <v>14941.01336665469</v>
+        <v>14788.59757570266</v>
       </c>
       <c r="D33">
-        <v>21074.7763666547</v>
+        <v>21136.23357570267</v>
       </c>
       <c r="E33">
-        <v>-605.0369999999994</v>
+        <v>-391.1639999999989</v>
       </c>
       <c r="F33">
-        <v>6630.063000000001</v>
+        <v>6843.936000000002</v>
       </c>
       <c r="G33">
         <v>496.3</v>
@@ -3999,28 +3999,28 @@
         <v>1187.8</v>
       </c>
       <c r="M33">
-        <v>366.6424839000001</v>
+        <v>378.4696608000002</v>
       </c>
       <c r="N33">
-        <v>821.1575160999996</v>
+        <v>809.3303391999996</v>
       </c>
       <c r="O33">
-        <v>211.8586391537999</v>
+        <v>208.8072275135999</v>
       </c>
       <c r="P33">
-        <v>609.2988769461997</v>
+        <v>600.5231116863997</v>
       </c>
       <c r="Q33">
-        <v>1957.6988769462</v>
+        <v>1948.9231116864</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07655803119550911</v>
+        <v>0.07692283239463693</v>
       </c>
       <c r="T33">
-        <v>0.7103471407738824</v>
+        <v>0.7187721107306452</v>
       </c>
       <c r="U33">
         <v>0.05530000000000001</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.239668211292083</v>
+        <v>3.138428579689205</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06543795802835312</v>
+        <v>0.06533076853180493</v>
       </c>
       <c r="C34">
-        <v>14788.59757570266</v>
+        <v>14636.54126994341</v>
       </c>
       <c r="D34">
-        <v>21136.23357570267</v>
+        <v>21198.05026994341</v>
       </c>
       <c r="E34">
-        <v>-391.1639999999989</v>
+        <v>-177.2909999999993</v>
       </c>
       <c r="F34">
-        <v>6843.936000000002</v>
+        <v>7057.809000000001</v>
       </c>
       <c r="G34">
         <v>496.3</v>
@@ -4081,28 +4081,28 @@
         <v>1187.8</v>
       </c>
       <c r="M34">
-        <v>378.4696608000002</v>
+        <v>390.2968377000001</v>
       </c>
       <c r="N34">
-        <v>809.3303391999996</v>
+        <v>797.5031622999995</v>
       </c>
       <c r="O34">
-        <v>208.8072275135999</v>
+        <v>205.7558158733999</v>
       </c>
       <c r="P34">
-        <v>600.5231116863997</v>
+        <v>591.7473464265996</v>
       </c>
       <c r="Q34">
-        <v>1948.9231116864</v>
+        <v>1940.1473464266</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07692283239463693</v>
+        <v>0.07729852318179842</v>
       </c>
       <c r="T34">
-        <v>0.7187721107306452</v>
+        <v>0.7274485723279083</v>
       </c>
       <c r="U34">
         <v>0.05530000000000001</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.138428579689205</v>
+        <v>3.043324683334987</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06533076853180493</v>
+        <v>0.06585427903525677</v>
       </c>
       <c r="C35">
-        <v>14636.54126994341</v>
+        <v>14124.13848554221</v>
       </c>
       <c r="D35">
-        <v>21198.05026994341</v>
+        <v>20899.52048554221</v>
       </c>
       <c r="E35">
-        <v>-177.2909999999993</v>
+        <v>36.58200000000124</v>
       </c>
       <c r="F35">
-        <v>7057.809000000001</v>
+        <v>7271.682000000002</v>
       </c>
       <c r="G35">
         <v>496.3</v>
@@ -4163,45 +4163,45 @@
         <v>1187.8</v>
       </c>
       <c r="M35">
-        <v>390.2968377000001</v>
+        <v>420.3032196000001</v>
       </c>
       <c r="N35">
-        <v>797.5031622999995</v>
+        <v>767.4967803999996</v>
       </c>
       <c r="O35">
-        <v>205.7558158733999</v>
+        <v>198.0141693431999</v>
       </c>
       <c r="P35">
-        <v>591.7473464265996</v>
+        <v>569.4826110567997</v>
       </c>
       <c r="Q35">
-        <v>1940.1473464266</v>
+        <v>1917.8826110568</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07729852318179842</v>
+        <v>0.07768559853826784</v>
       </c>
       <c r="T35">
-        <v>0.7274485723279083</v>
+        <v>0.7363879570038764</v>
       </c>
       <c r="U35">
-        <v>0.05530000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V35">
         <v>0.258</v>
       </c>
       <c r="W35">
-        <v>0.04103260000000001</v>
+        <v>0.0428876</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>3.043324683334987</v>
+        <v>2.826054963676988</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06585427903525677</v>
+        <v>0.06576563953870861</v>
       </c>
       <c r="C36">
-        <v>14124.13848554221</v>
+        <v>13960.21908135855</v>
       </c>
       <c r="D36">
-        <v>20899.52048554221</v>
+        <v>20949.47408135855</v>
       </c>
       <c r="E36">
-        <v>36.58200000000124</v>
+        <v>250.4550000000017</v>
       </c>
       <c r="F36">
-        <v>7271.682000000002</v>
+        <v>7485.555000000002</v>
       </c>
       <c r="G36">
         <v>496.3</v>
@@ -4245,28 +4245,28 @@
         <v>1187.8</v>
       </c>
       <c r="M36">
-        <v>420.3032196000001</v>
+        <v>432.6650790000002</v>
       </c>
       <c r="N36">
-        <v>767.4967803999996</v>
+        <v>755.1349209999996</v>
       </c>
       <c r="O36">
-        <v>198.0141693431999</v>
+        <v>194.8248096179999</v>
       </c>
       <c r="P36">
-        <v>569.4826110567997</v>
+        <v>560.3101113819997</v>
       </c>
       <c r="Q36">
-        <v>1917.8826110568</v>
+        <v>1908.710111382</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07768559853826784</v>
+        <v>0.07808458390570555</v>
       </c>
       <c r="T36">
-        <v>0.7363879570038764</v>
+        <v>0.7456023996698743</v>
       </c>
       <c r="U36">
         <v>0.0578</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.826054963676988</v>
+        <v>2.74531053614336</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06576563953870861</v>
+        <v>0.06567700004216043</v>
       </c>
       <c r="C37">
-        <v>13960.21908135855</v>
+        <v>13796.53904538317</v>
       </c>
       <c r="D37">
-        <v>20949.47408135855</v>
+        <v>20999.66704538317</v>
       </c>
       <c r="E37">
-        <v>250.4550000000017</v>
+        <v>464.3280000000013</v>
       </c>
       <c r="F37">
-        <v>7485.555000000002</v>
+        <v>7699.428000000002</v>
       </c>
       <c r="G37">
         <v>496.3</v>
@@ -4327,28 +4327,28 @@
         <v>1187.8</v>
       </c>
       <c r="M37">
-        <v>432.6650790000002</v>
+        <v>445.0269384000001</v>
       </c>
       <c r="N37">
-        <v>755.1349209999996</v>
+        <v>742.7730615999997</v>
       </c>
       <c r="O37">
-        <v>194.8248096179999</v>
+        <v>191.6354498927999</v>
       </c>
       <c r="P37">
-        <v>560.3101113819997</v>
+        <v>551.1376117071998</v>
       </c>
       <c r="Q37">
-        <v>1908.710111382</v>
+        <v>1899.5376117072</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07808458390570555</v>
+        <v>0.07849603756587568</v>
       </c>
       <c r="T37">
-        <v>0.7456023996698743</v>
+        <v>0.7551047936691846</v>
       </c>
       <c r="U37">
         <v>0.0578</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.74531053614336</v>
+        <v>2.669051910139379</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06567700004216044</v>
+        <v>0.06558836054561228</v>
       </c>
       <c r="C38">
-        <v>13796.53904538316</v>
+        <v>13633.1001022591</v>
       </c>
       <c r="D38">
-        <v>20999.66704538316</v>
+        <v>21050.1011022591</v>
       </c>
       <c r="E38">
-        <v>464.3280000000004</v>
+        <v>678.2010000000009</v>
       </c>
       <c r="F38">
-        <v>7699.428000000001</v>
+        <v>7913.301000000001</v>
       </c>
       <c r="G38">
         <v>496.3</v>
@@ -4409,28 +4409,28 @@
         <v>1187.8</v>
       </c>
       <c r="M38">
-        <v>445.0269384000001</v>
+        <v>457.3887978000001</v>
       </c>
       <c r="N38">
-        <v>742.7730615999997</v>
+        <v>730.4112021999996</v>
       </c>
       <c r="O38">
-        <v>191.6354498927999</v>
+        <v>188.4460901675999</v>
       </c>
       <c r="P38">
-        <v>551.1376117071998</v>
+        <v>541.9651120323997</v>
       </c>
       <c r="Q38">
-        <v>1899.5376117072</v>
+        <v>1890.3651120324</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.07849603756587568</v>
+        <v>0.07892055324700362</v>
       </c>
       <c r="T38">
-        <v>0.7551047936691846</v>
+        <v>0.7649088509700603</v>
       </c>
       <c r="U38">
         <v>0.0578</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.669051910139379</v>
+        <v>2.596915372027503</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06558836054561228</v>
+        <v>0.06549972104906411</v>
       </c>
       <c r="C39">
-        <v>13633.1001022591</v>
+        <v>13469.90399323731</v>
       </c>
       <c r="D39">
-        <v>21050.1011022591</v>
+        <v>21100.77799323731</v>
       </c>
       <c r="E39">
-        <v>678.2010000000009</v>
+        <v>892.0740000000005</v>
       </c>
       <c r="F39">
-        <v>7913.301000000001</v>
+        <v>8127.174000000001</v>
       </c>
       <c r="G39">
         <v>496.3</v>
@@ -4491,28 +4491,28 @@
         <v>1187.8</v>
       </c>
       <c r="M39">
-        <v>457.3887978000001</v>
+        <v>469.7506572000001</v>
       </c>
       <c r="N39">
-        <v>730.4112021999996</v>
+        <v>718.0493427999996</v>
       </c>
       <c r="O39">
-        <v>188.4460901675999</v>
+        <v>185.2567304423999</v>
       </c>
       <c r="P39">
-        <v>541.9651120323997</v>
+        <v>532.7926123575998</v>
       </c>
       <c r="Q39">
-        <v>1890.3651120324</v>
+        <v>1881.1926123576</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.07892055324700362</v>
+        <v>0.07935876298236147</v>
       </c>
       <c r="T39">
-        <v>0.7649088509700603</v>
+        <v>0.7750291681838676</v>
       </c>
       <c r="U39">
         <v>0.0578</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.596915372027503</v>
+        <v>2.528575493816253</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06549972104906411</v>
+        <v>0.06642391155251594</v>
       </c>
       <c r="C40">
-        <v>13469.90399323731</v>
+        <v>12739.35077532824</v>
       </c>
       <c r="D40">
-        <v>21100.77799323731</v>
+        <v>20584.09777532825</v>
       </c>
       <c r="E40">
-        <v>892.0740000000005</v>
+        <v>1105.947000000002</v>
       </c>
       <c r="F40">
-        <v>8127.174000000001</v>
+        <v>8341.047000000002</v>
       </c>
       <c r="G40">
         <v>496.3</v>
@@ -4573,45 +4573,45 @@
         <v>1187.8</v>
       </c>
       <c r="M40">
-        <v>469.7506572000001</v>
+        <v>511.3061811000002</v>
       </c>
       <c r="N40">
-        <v>718.0493427999996</v>
+        <v>676.4938188999995</v>
       </c>
       <c r="O40">
-        <v>185.2567304423999</v>
+        <v>174.5354052761999</v>
       </c>
       <c r="P40">
-        <v>532.7926123575998</v>
+        <v>501.9584136237996</v>
       </c>
       <c r="Q40">
-        <v>1881.1926123576</v>
+        <v>1850.3584136238</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.07935876298236147</v>
+        <v>0.07981134025002612</v>
       </c>
       <c r="T40">
-        <v>0.7750291681838676</v>
+        <v>0.785481299076816</v>
       </c>
       <c r="U40">
-        <v>0.0578</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V40">
         <v>0.258</v>
       </c>
       <c r="W40">
-        <v>0.0428876</v>
+        <v>0.04548460000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.528575493816253</v>
+        <v>2.323069901960939</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06642391155251594</v>
+        <v>0.06636124205596777</v>
       </c>
       <c r="C41">
-        <v>12739.35077532824</v>
+        <v>12559.71287660862</v>
       </c>
       <c r="D41">
-        <v>20584.09777532825</v>
+        <v>20618.33287660863</v>
       </c>
       <c r="E41">
-        <v>1105.947000000002</v>
+        <v>1319.820000000002</v>
       </c>
       <c r="F41">
-        <v>8341.047000000002</v>
+        <v>8554.920000000002</v>
       </c>
       <c r="G41">
         <v>496.3</v>
@@ -4655,28 +4655,28 @@
         <v>1187.8</v>
       </c>
       <c r="M41">
-        <v>511.3061811000002</v>
+        <v>524.4165960000001</v>
       </c>
       <c r="N41">
-        <v>676.4938188999995</v>
+        <v>663.3834039999996</v>
       </c>
       <c r="O41">
-        <v>174.5354052761999</v>
+        <v>171.1529182319999</v>
       </c>
       <c r="P41">
-        <v>501.9584136237996</v>
+        <v>492.2304857679997</v>
       </c>
       <c r="Q41">
-        <v>1850.3584136238</v>
+        <v>1840.630485768</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.07981134025002612</v>
+        <v>0.08027900342661295</v>
       </c>
       <c r="T41">
-        <v>0.785481299076816</v>
+        <v>0.7962818343328628</v>
       </c>
       <c r="U41">
         <v>0.06130000000000001</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.323069901960939</v>
+        <v>2.264993154411916</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06636124205596777</v>
+        <v>0.0671503885594196</v>
       </c>
       <c r="C42">
-        <v>12559.71287660862</v>
+        <v>11922.88580004275</v>
       </c>
       <c r="D42">
-        <v>20618.33287660863</v>
+        <v>20195.37880004275</v>
       </c>
       <c r="E42">
-        <v>1319.820000000002</v>
+        <v>1533.693000000001</v>
       </c>
       <c r="F42">
-        <v>8554.920000000002</v>
+        <v>8768.793000000001</v>
       </c>
       <c r="G42">
         <v>496.3</v>
@@ -4737,45 +4737,45 @@
         <v>1187.8</v>
       </c>
       <c r="M42">
-        <v>524.4165960000001</v>
+        <v>562.0796313000002</v>
       </c>
       <c r="N42">
-        <v>663.3834039999996</v>
+        <v>625.7203686999995</v>
       </c>
       <c r="O42">
-        <v>171.1529182319999</v>
+        <v>161.4358551245999</v>
       </c>
       <c r="P42">
-        <v>492.2304857679997</v>
+        <v>464.2845135753996</v>
       </c>
       <c r="Q42">
-        <v>1840.630485768</v>
+        <v>1812.6845135754</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08027900342661295</v>
+        <v>0.08076251959223661</v>
       </c>
       <c r="T42">
-        <v>0.7962818343328628</v>
+        <v>0.8074484894280974</v>
       </c>
       <c r="U42">
-        <v>0.06130000000000001</v>
+        <v>0.0641</v>
       </c>
       <c r="V42">
         <v>0.258</v>
       </c>
       <c r="W42">
-        <v>0.04548460000000001</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.264993154411916</v>
+        <v>2.113223703290597</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0671503885594196</v>
+        <v>0.06710849506287142</v>
       </c>
       <c r="C43">
-        <v>11922.88580004275</v>
+        <v>11731.02958242397</v>
       </c>
       <c r="D43">
-        <v>20195.37880004275</v>
+        <v>20217.39558242398</v>
       </c>
       <c r="E43">
-        <v>1533.693000000001</v>
+        <v>1747.566000000003</v>
       </c>
       <c r="F43">
-        <v>8768.793000000001</v>
+        <v>8982.666000000003</v>
       </c>
       <c r="G43">
         <v>496.3</v>
@@ -4819,28 +4819,28 @@
         <v>1187.8</v>
       </c>
       <c r="M43">
-        <v>562.0796313000002</v>
+        <v>575.7888906000002</v>
       </c>
       <c r="N43">
-        <v>625.7203686999995</v>
+        <v>612.0111093999996</v>
       </c>
       <c r="O43">
-        <v>161.4358551245999</v>
+        <v>157.8988662251999</v>
       </c>
       <c r="P43">
-        <v>464.2845135753996</v>
+        <v>454.1122431747997</v>
       </c>
       <c r="Q43">
-        <v>1812.6845135754</v>
+        <v>1802.5122431748</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08076251959223661</v>
+        <v>0.08126270872908867</v>
       </c>
       <c r="T43">
-        <v>0.8074484894280974</v>
+        <v>0.8190002015955816</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.113223703290597</v>
+        <v>2.062908853212249</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06710849506287143</v>
+        <v>0.06706660156632328</v>
       </c>
       <c r="C44">
-        <v>11731.02958242397</v>
+        <v>11539.22142211025</v>
       </c>
       <c r="D44">
-        <v>20217.39558242397</v>
+        <v>20239.46042211026</v>
       </c>
       <c r="E44">
-        <v>1747.566000000001</v>
+        <v>1961.439</v>
       </c>
       <c r="F44">
-        <v>8982.666000000001</v>
+        <v>9196.539000000001</v>
       </c>
       <c r="G44">
         <v>496.3</v>
@@ -4901,28 +4901,28 @@
         <v>1187.8</v>
       </c>
       <c r="M44">
-        <v>575.7888906000001</v>
+        <v>589.4981499</v>
       </c>
       <c r="N44">
-        <v>612.0111093999997</v>
+        <v>598.3018500999997</v>
       </c>
       <c r="O44">
-        <v>157.8988662251999</v>
+        <v>154.3618773257999</v>
       </c>
       <c r="P44">
-        <v>454.1122431747997</v>
+        <v>443.9399727741998</v>
       </c>
       <c r="Q44">
-        <v>1802.5122431748</v>
+        <v>1792.3399727742</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08126270872908867</v>
+        <v>0.08178044836197065</v>
       </c>
       <c r="T44">
-        <v>0.8190002015955816</v>
+        <v>0.8309572369970127</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.06290885321225</v>
+        <v>2.014934228718942</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06706660156632328</v>
+        <v>0.0695712520697751</v>
       </c>
       <c r="C45">
-        <v>11539.22142211025</v>
+        <v>10085.62801558429</v>
       </c>
       <c r="D45">
-        <v>20239.46042211026</v>
+        <v>18999.7400155843</v>
       </c>
       <c r="E45">
-        <v>1961.439</v>
+        <v>2175.312000000002</v>
       </c>
       <c r="F45">
-        <v>9196.539000000001</v>
+        <v>9410.412000000002</v>
       </c>
       <c r="G45">
         <v>496.3</v>
@@ -4983,45 +4983,45 @@
         <v>1187.8</v>
       </c>
       <c r="M45">
-        <v>589.4981499</v>
+        <v>676.6086228000001</v>
       </c>
       <c r="N45">
-        <v>598.3018500999997</v>
+        <v>511.1913771999996</v>
       </c>
       <c r="O45">
-        <v>154.3618773257999</v>
+        <v>131.8873753175999</v>
       </c>
       <c r="P45">
-        <v>443.9399727741998</v>
+        <v>379.3040018823997</v>
       </c>
       <c r="Q45">
-        <v>1792.3399727742</v>
+        <v>1727.7040018824</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08178044836197065</v>
+        <v>0.08231667869602696</v>
       </c>
       <c r="T45">
-        <v>0.8309572369970127</v>
+        <v>0.8433413093770662</v>
       </c>
       <c r="U45">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V45">
         <v>0.258</v>
       </c>
       <c r="W45">
-        <v>0.04756220000000001</v>
+        <v>0.0533498</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.014934228718942</v>
+        <v>1.755520045080926</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0695712520697751</v>
+        <v>0.07088944457322693</v>
       </c>
       <c r="C46">
-        <v>10085.62801558429</v>
+        <v>9278.386224084339</v>
       </c>
       <c r="D46">
-        <v>18999.7400155843</v>
+        <v>18406.37122408434</v>
       </c>
       <c r="E46">
-        <v>2175.312000000002</v>
+        <v>2389.185000000001</v>
       </c>
       <c r="F46">
-        <v>9410.412000000002</v>
+        <v>9624.285000000002</v>
       </c>
       <c r="G46">
         <v>496.3</v>
@@ -5065,45 +5065,45 @@
         <v>1187.8</v>
       </c>
       <c r="M46">
-        <v>676.6086228000001</v>
+        <v>729.5208030000002</v>
       </c>
       <c r="N46">
-        <v>511.1913771999996</v>
+        <v>458.2791969999995</v>
       </c>
       <c r="O46">
-        <v>131.8873753175999</v>
+        <v>118.2360328259999</v>
       </c>
       <c r="P46">
-        <v>379.3040018823997</v>
+        <v>340.0431641739996</v>
       </c>
       <c r="Q46">
-        <v>1727.7040018824</v>
+        <v>1688.443164174</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08231667869602696</v>
+        <v>0.08287240831495805</v>
       </c>
       <c r="T46">
-        <v>0.8433413093770662</v>
+        <v>0.856175711661849</v>
       </c>
       <c r="U46">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V46">
         <v>0.258</v>
       </c>
       <c r="W46">
-        <v>0.0533498</v>
+        <v>0.0562436</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y46">
-        <v>1.755520045080926</v>
+        <v>1.62819208871827</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07088944457322693</v>
+        <v>0.07093436507667877</v>
       </c>
       <c r="C47">
-        <v>9278.386224084339</v>
+        <v>9044.945106678113</v>
       </c>
       <c r="D47">
-        <v>18406.37122408434</v>
+        <v>18386.80310667812</v>
       </c>
       <c r="E47">
-        <v>2389.185000000001</v>
+        <v>2603.058000000001</v>
       </c>
       <c r="F47">
-        <v>9624.285000000002</v>
+        <v>9838.158000000001</v>
       </c>
       <c r="G47">
         <v>496.3</v>
@@ -5147,28 +5147,28 @@
         <v>1187.8</v>
       </c>
       <c r="M47">
-        <v>729.5208030000002</v>
+        <v>745.7323764000001</v>
       </c>
       <c r="N47">
-        <v>458.2791969999995</v>
+        <v>442.0676235999996</v>
       </c>
       <c r="O47">
-        <v>118.2360328259999</v>
+        <v>114.0534468887999</v>
       </c>
       <c r="P47">
-        <v>340.0431641739996</v>
+        <v>328.0141767111997</v>
       </c>
       <c r="Q47">
-        <v>1688.443164174</v>
+        <v>1676.4141767112</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08287240831495805</v>
+        <v>0.08344872051236808</v>
       </c>
       <c r="T47">
-        <v>0.856175711661849</v>
+        <v>0.8694854621794016</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.62819208871827</v>
+        <v>1.592796608528742</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07093436507667877</v>
+        <v>0.07097928558013059</v>
       </c>
       <c r="C48">
-        <v>9044.945106678113</v>
+        <v>8811.545551464384</v>
       </c>
       <c r="D48">
-        <v>18386.80310667812</v>
+        <v>18367.27655146439</v>
       </c>
       <c r="E48">
-        <v>2603.058000000001</v>
+        <v>2816.931000000002</v>
       </c>
       <c r="F48">
-        <v>9838.158000000001</v>
+        <v>10052.031</v>
       </c>
       <c r="G48">
         <v>496.3</v>
@@ -5229,28 +5229,28 @@
         <v>1187.8</v>
       </c>
       <c r="M48">
-        <v>745.7323764000001</v>
+        <v>761.9439498000003</v>
       </c>
       <c r="N48">
-        <v>442.0676235999996</v>
+        <v>425.8560501999995</v>
       </c>
       <c r="O48">
-        <v>114.0534468887999</v>
+        <v>109.8708609515999</v>
       </c>
       <c r="P48">
-        <v>328.0141767111997</v>
+        <v>315.9851892483996</v>
       </c>
       <c r="Q48">
-        <v>1676.4141767112</v>
+        <v>1664.3851892484</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08344872051236808</v>
+        <v>0.08404678033986904</v>
       </c>
       <c r="T48">
-        <v>0.8694854621794016</v>
+        <v>0.8832974674334654</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.592796608528742</v>
+        <v>1.558907318985577</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07097928558013059</v>
+        <v>0.07102420608358243</v>
       </c>
       <c r="C49">
-        <v>8811.545551464384</v>
+        <v>8578.187426168017</v>
       </c>
       <c r="D49">
-        <v>18367.27655146439</v>
+        <v>18347.79142616802</v>
       </c>
       <c r="E49">
-        <v>2816.931000000002</v>
+        <v>3030.804000000002</v>
       </c>
       <c r="F49">
-        <v>10052.031</v>
+        <v>10265.904</v>
       </c>
       <c r="G49">
         <v>496.3</v>
@@ -5311,28 +5311,28 @@
         <v>1187.8</v>
       </c>
       <c r="M49">
-        <v>761.9439498000003</v>
+        <v>778.1555232000003</v>
       </c>
       <c r="N49">
-        <v>425.8560501999995</v>
+        <v>409.6444767999994</v>
       </c>
       <c r="O49">
-        <v>109.8708609515999</v>
+        <v>105.6882750143999</v>
       </c>
       <c r="P49">
-        <v>315.9851892483996</v>
+        <v>303.9562017855995</v>
       </c>
       <c r="Q49">
-        <v>1664.3851892484</v>
+        <v>1652.3562017856</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08404678033986904</v>
+        <v>0.08466784246842773</v>
       </c>
       <c r="T49">
-        <v>0.8832974674334654</v>
+        <v>0.8976407036588395</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.558907318985577</v>
+        <v>1.526430083173378</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07102420608358243</v>
+        <v>0.07623196258703427</v>
       </c>
       <c r="C50">
-        <v>8578.187426168019</v>
+        <v>6354.883973784854</v>
       </c>
       <c r="D50">
-        <v>18347.79142616802</v>
+        <v>16338.36097378485</v>
       </c>
       <c r="E50">
-        <v>3030.804</v>
+        <v>3244.677000000001</v>
       </c>
       <c r="F50">
-        <v>10265.904</v>
+        <v>10479.777</v>
       </c>
       <c r="G50">
         <v>496.3</v>
@@ -5393,45 +5393,45 @@
         <v>1187.8</v>
       </c>
       <c r="M50">
-        <v>778.1555232000001</v>
+        <v>943.1799300000002</v>
       </c>
       <c r="N50">
-        <v>409.6444767999997</v>
+        <v>244.6200699999995</v>
       </c>
       <c r="O50">
-        <v>105.6882750143999</v>
+        <v>63.11197805999987</v>
       </c>
       <c r="P50">
-        <v>303.9562017855998</v>
+        <v>181.5080919399996</v>
       </c>
       <c r="Q50">
-        <v>1652.3562017856</v>
+        <v>1529.90809194</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08466784246842773</v>
+        <v>0.08531325997457698</v>
       </c>
       <c r="T50">
-        <v>0.8976407036588394</v>
+        <v>0.912546419736189</v>
       </c>
       <c r="U50">
-        <v>0.07580000000000001</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V50">
         <v>0.258</v>
       </c>
       <c r="W50">
-        <v>0.0562436</v>
+        <v>0.06678000000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>1.526430083173378</v>
+        <v>1.259356738008621</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07623196258703427</v>
+        <v>0.08815234001280614</v>
       </c>
       <c r="C51">
-        <v>6354.883973784854</v>
+        <v>2866.178920247334</v>
       </c>
       <c r="D51">
-        <v>16338.36097378485</v>
+        <v>13063.52892024734</v>
       </c>
       <c r="E51">
-        <v>3244.677000000001</v>
+        <v>3458.550000000001</v>
       </c>
       <c r="F51">
-        <v>10479.777</v>
+        <v>10693.65</v>
       </c>
       <c r="G51">
         <v>496.3</v>
@@ -5475,45 +5475,45 @@
         <v>1187.8</v>
       </c>
       <c r="M51">
-        <v>943.1799300000002</v>
+        <v>1268.26689</v>
       </c>
       <c r="N51">
-        <v>244.6200699999995</v>
+        <v>-80.4668900000006</v>
       </c>
       <c r="O51">
-        <v>63.11197805999987</v>
+        <v>-20.76045762000016</v>
       </c>
       <c r="P51">
-        <v>181.5080919399996</v>
+        <v>-59.70643238000045</v>
       </c>
       <c r="Q51">
-        <v>1529.90809194</v>
+        <v>1288.69356762</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08531325997457698</v>
+        <v>0.08636209821304125</v>
       </c>
       <c r="T51">
-        <v>0.912546419736189</v>
+        <v>0.9367690118485277</v>
       </c>
       <c r="U51">
-        <v>0.09000000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V51">
-        <v>0.258</v>
+        <v>0.2416308447506659</v>
       </c>
       <c r="W51">
-        <v>0.06678000000000001</v>
+        <v>0.08994258181257103</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y51">
-        <v>1.259356738008621</v>
+        <v>0.9365536618242863</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08815234001280614</v>
+        <v>0.08888034001280613</v>
       </c>
       <c r="C52">
-        <v>2866.178920247334</v>
+        <v>2494.327253319532</v>
       </c>
       <c r="D52">
-        <v>13063.52892024734</v>
+        <v>12905.55025331953</v>
       </c>
       <c r="E52">
-        <v>3458.550000000001</v>
+        <v>3672.423000000001</v>
       </c>
       <c r="F52">
-        <v>10693.65</v>
+        <v>10907.523</v>
       </c>
       <c r="G52">
         <v>496.3</v>
@@ -5557,37 +5557,37 @@
         <v>1187.8</v>
       </c>
       <c r="M52">
-        <v>1268.26689</v>
+        <v>1293.6322278</v>
       </c>
       <c r="N52">
-        <v>-80.4668900000006</v>
+        <v>-105.8322278000005</v>
       </c>
       <c r="O52">
-        <v>-20.76045762000016</v>
+        <v>-27.30471477240013</v>
       </c>
       <c r="P52">
-        <v>-59.70643238000045</v>
+        <v>-78.52751302760038</v>
       </c>
       <c r="Q52">
-        <v>1288.69356762</v>
+        <v>1269.8724869724</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08636209821304125</v>
+        <v>0.08718989613575637</v>
       </c>
       <c r="T52">
-        <v>0.9367690118485277</v>
+        <v>0.9558867467842119</v>
       </c>
       <c r="U52">
         <v>0.1186</v>
       </c>
       <c r="V52">
-        <v>0.2416308447506659</v>
+        <v>0.2368929850496725</v>
       </c>
       <c r="W52">
-        <v>0.08994258181257103</v>
+        <v>0.09050449197310885</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.9365536618242863</v>
+        <v>0.9181898645336142</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08888034001280613</v>
+        <v>0.08960834001280615</v>
       </c>
       <c r="C53">
-        <v>2494.327253319532</v>
+        <v>2126.250838047365</v>
       </c>
       <c r="D53">
-        <v>12905.55025331953</v>
+        <v>12751.34683804737</v>
       </c>
       <c r="E53">
-        <v>3672.423000000001</v>
+        <v>3886.296000000002</v>
       </c>
       <c r="F53">
-        <v>10907.523</v>
+        <v>11121.396</v>
       </c>
       <c r="G53">
         <v>496.3</v>
@@ -5639,37 +5639,37 @@
         <v>1187.8</v>
       </c>
       <c r="M53">
-        <v>1293.6322278</v>
+        <v>1318.9975656</v>
       </c>
       <c r="N53">
-        <v>-105.8322278000005</v>
+        <v>-131.1975656000006</v>
       </c>
       <c r="O53">
-        <v>-27.30471477240013</v>
+        <v>-33.84897192480017</v>
       </c>
       <c r="P53">
-        <v>-78.52751302760038</v>
+        <v>-97.34859367520048</v>
       </c>
       <c r="Q53">
-        <v>1269.8724869724</v>
+        <v>1251.0514063248</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.08718989613575637</v>
+        <v>0.08805218563858463</v>
       </c>
       <c r="T53">
-        <v>0.9558867467842119</v>
+        <v>0.9758010540088831</v>
       </c>
       <c r="U53">
         <v>0.1186</v>
       </c>
       <c r="V53">
-        <v>0.2368929850496725</v>
+        <v>0.2323373507217941</v>
       </c>
       <c r="W53">
-        <v>0.09050449197310885</v>
+        <v>0.09104479020439524</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.9181898645336142</v>
+        <v>0.9005323671387369</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08960834001280615</v>
+        <v>0.09033634001280613</v>
       </c>
       <c r="C54">
-        <v>2126.250838047365</v>
+        <v>1761.815945254883</v>
       </c>
       <c r="D54">
-        <v>12751.34683804737</v>
+        <v>12600.78494525489</v>
       </c>
       <c r="E54">
-        <v>3886.296000000002</v>
+        <v>4100.169000000002</v>
       </c>
       <c r="F54">
-        <v>11121.396</v>
+        <v>11335.269</v>
       </c>
       <c r="G54">
         <v>496.3</v>
@@ -5721,37 +5721,37 @@
         <v>1187.8</v>
       </c>
       <c r="M54">
-        <v>1318.9975656</v>
+        <v>1344.3629034</v>
       </c>
       <c r="N54">
-        <v>-131.1975656000006</v>
+        <v>-156.5629034000006</v>
       </c>
       <c r="O54">
-        <v>-33.84897192480017</v>
+        <v>-40.39322907720015</v>
       </c>
       <c r="P54">
-        <v>-97.34859367520048</v>
+        <v>-116.1696743228004</v>
       </c>
       <c r="Q54">
-        <v>1251.0514063248</v>
+        <v>1232.2303256772</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.08805218563858463</v>
+        <v>0.088951168311746</v>
       </c>
       <c r="T54">
-        <v>0.9758010540088831</v>
+        <v>0.9965627785622635</v>
       </c>
       <c r="U54">
         <v>0.1186</v>
       </c>
       <c r="V54">
-        <v>0.2323373507217941</v>
+        <v>0.2279536271232697</v>
       </c>
       <c r="W54">
-        <v>0.09104479020439524</v>
+        <v>0.09156469982318022</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.9005323671387369</v>
+        <v>0.8835411904002702</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09033634001280613</v>
+        <v>0.09106434001280614</v>
       </c>
       <c r="C55">
-        <v>1761.815945254883</v>
+        <v>1400.895088103816</v>
       </c>
       <c r="D55">
-        <v>12600.78494525489</v>
+        <v>12453.73708810382</v>
       </c>
       <c r="E55">
-        <v>4100.169000000002</v>
+        <v>4314.042000000001</v>
       </c>
       <c r="F55">
-        <v>11335.269</v>
+        <v>11549.142</v>
       </c>
       <c r="G55">
         <v>496.3</v>
@@ -5803,37 +5803,37 @@
         <v>1187.8</v>
       </c>
       <c r="M55">
-        <v>1344.3629034</v>
+        <v>1369.7282412</v>
       </c>
       <c r="N55">
-        <v>-156.5629034000006</v>
+        <v>-181.9282412000007</v>
       </c>
       <c r="O55">
-        <v>-40.39322907720015</v>
+        <v>-46.93748622960018</v>
       </c>
       <c r="P55">
-        <v>-116.1696743228004</v>
+        <v>-134.9907549704005</v>
       </c>
       <c r="Q55">
-        <v>1232.2303256772</v>
+        <v>1213.4092450296</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.088951168311746</v>
+        <v>0.08988923718808831</v>
       </c>
       <c r="T55">
-        <v>0.9965627785622635</v>
+        <v>1.018227186791878</v>
       </c>
       <c r="U55">
         <v>0.1186</v>
       </c>
       <c r="V55">
-        <v>0.2279536271232697</v>
+        <v>0.223732263658024</v>
       </c>
       <c r="W55">
-        <v>0.09156469982318022</v>
+        <v>0.09206535353015838</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8835411904002702</v>
+        <v>0.8671793165039688</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09106434001280614</v>
+        <v>0.09179234001280615</v>
       </c>
       <c r="C56">
-        <v>1400.895088103816</v>
+        <v>1043.366662062861</v>
       </c>
       <c r="D56">
-        <v>12453.73708810382</v>
+        <v>12310.08166206286</v>
       </c>
       <c r="E56">
-        <v>4314.042000000001</v>
+        <v>4527.915000000003</v>
       </c>
       <c r="F56">
-        <v>11549.142</v>
+        <v>11763.015</v>
       </c>
       <c r="G56">
         <v>496.3</v>
@@ -5885,37 +5885,37 @@
         <v>1187.8</v>
       </c>
       <c r="M56">
-        <v>1369.7282412</v>
+        <v>1395.093579000001</v>
       </c>
       <c r="N56">
-        <v>-181.9282412000007</v>
+        <v>-207.2935790000008</v>
       </c>
       <c r="O56">
-        <v>-46.93748622960018</v>
+        <v>-53.48174338200021</v>
       </c>
       <c r="P56">
-        <v>-134.9907549704005</v>
+        <v>-153.8118356180006</v>
       </c>
       <c r="Q56">
-        <v>1213.4092450296</v>
+        <v>1194.588164381999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.08988923718808831</v>
+        <v>0.09086899801449028</v>
       </c>
       <c r="T56">
-        <v>1.018227186791878</v>
+        <v>1.040854457609475</v>
       </c>
       <c r="U56">
         <v>0.1186</v>
       </c>
       <c r="V56">
-        <v>0.223732263658024</v>
+        <v>0.2196644043187872</v>
       </c>
       <c r="W56">
-        <v>0.09206535353015838</v>
+        <v>0.09254780164779185</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8671793165039688</v>
+        <v>0.8514124198402602</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09179234001280615</v>
+        <v>0.09252034001280615</v>
       </c>
       <c r="C57">
-        <v>1043.366662062861</v>
+        <v>689.1146095107615</v>
       </c>
       <c r="D57">
-        <v>12310.08166206286</v>
+        <v>12169.70260951076</v>
       </c>
       <c r="E57">
-        <v>4527.915000000003</v>
+        <v>4741.788000000002</v>
       </c>
       <c r="F57">
-        <v>11763.015</v>
+        <v>11976.888</v>
       </c>
       <c r="G57">
         <v>496.3</v>
@@ -5967,37 +5967,37 @@
         <v>1187.8</v>
       </c>
       <c r="M57">
-        <v>1395.093579000001</v>
+        <v>1420.4589168</v>
       </c>
       <c r="N57">
-        <v>-207.2935790000008</v>
+        <v>-232.6589168000007</v>
       </c>
       <c r="O57">
-        <v>-53.48174338200021</v>
+        <v>-60.02600053440019</v>
       </c>
       <c r="P57">
-        <v>-153.8118356180006</v>
+        <v>-172.6329162656005</v>
       </c>
       <c r="Q57">
-        <v>1194.588164381999</v>
+        <v>1175.7670837344</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09086899801449028</v>
+        <v>0.0918932934239105</v>
       </c>
       <c r="T57">
-        <v>1.040854457609475</v>
+        <v>1.064510240736963</v>
       </c>
       <c r="U57">
         <v>0.1186</v>
       </c>
       <c r="V57">
-        <v>0.2196644043187872</v>
+        <v>0.2157418256702374</v>
       </c>
       <c r="W57">
-        <v>0.09254780164779185</v>
+        <v>0.09301301947550986</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8514124198402602</v>
+        <v>0.8362086266288271</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09252034001280615</v>
+        <v>0.09324834001280613</v>
       </c>
       <c r="C58">
-        <v>689.1146095107615</v>
+        <v>338.0281070290021</v>
       </c>
       <c r="D58">
-        <v>12169.70260951076</v>
+        <v>12032.48910702901</v>
       </c>
       <c r="E58">
-        <v>4741.788000000002</v>
+        <v>4955.661000000002</v>
       </c>
       <c r="F58">
-        <v>11976.888</v>
+        <v>12190.761</v>
       </c>
       <c r="G58">
         <v>496.3</v>
@@ -6049,37 +6049,37 @@
         <v>1187.8</v>
       </c>
       <c r="M58">
-        <v>1420.4589168</v>
+        <v>1445.8242546</v>
       </c>
       <c r="N58">
-        <v>-232.6589168000007</v>
+        <v>-258.0242546000006</v>
       </c>
       <c r="O58">
-        <v>-60.02600053440019</v>
+        <v>-66.57025768680016</v>
       </c>
       <c r="P58">
-        <v>-172.6329162656005</v>
+        <v>-191.4539969132005</v>
       </c>
       <c r="Q58">
-        <v>1175.7670837344</v>
+        <v>1156.9460030868</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.0918932934239105</v>
+        <v>0.09296523048028052</v>
       </c>
       <c r="T58">
-        <v>1.064510240736963</v>
+        <v>1.089266292847125</v>
       </c>
       <c r="U58">
         <v>0.1186</v>
       </c>
       <c r="V58">
-        <v>0.2157418256702374</v>
+        <v>0.2119568813602332</v>
       </c>
       <c r="W58">
-        <v>0.09301301947550986</v>
+        <v>0.09346191387067634</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8362086266288271</v>
+        <v>0.8215382998458652</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09324834001280613</v>
+        <v>0.09397634001280614</v>
       </c>
       <c r="C59">
-        <v>338.0281070290021</v>
+        <v>-9.998726386691487</v>
       </c>
       <c r="D59">
-        <v>12032.48910702901</v>
+        <v>11898.33527361331</v>
       </c>
       <c r="E59">
-        <v>4955.661000000002</v>
+        <v>5169.534000000003</v>
       </c>
       <c r="F59">
-        <v>12190.761</v>
+        <v>12404.634</v>
       </c>
       <c r="G59">
         <v>496.3</v>
@@ -6131,37 +6131,37 @@
         <v>1187.8</v>
       </c>
       <c r="M59">
-        <v>1445.8242546</v>
+        <v>1471.1895924</v>
       </c>
       <c r="N59">
-        <v>-258.0242546000006</v>
+        <v>-283.3895924000008</v>
       </c>
       <c r="O59">
-        <v>-66.57025768680016</v>
+        <v>-73.1145148392002</v>
       </c>
       <c r="P59">
-        <v>-191.4539969132005</v>
+        <v>-210.2750775608006</v>
       </c>
       <c r="Q59">
-        <v>1156.9460030868</v>
+        <v>1138.1249224392</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09296523048028052</v>
+        <v>0.09408821215838244</v>
       </c>
       <c r="T59">
-        <v>1.089266292847125</v>
+        <v>1.115201204581581</v>
       </c>
       <c r="U59">
         <v>0.1186</v>
       </c>
       <c r="V59">
-        <v>0.2119568813602332</v>
+        <v>0.2083024523712637</v>
       </c>
       <c r="W59">
-        <v>0.09346191387067634</v>
+        <v>0.09389532914876814</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8215382998458652</v>
+        <v>0.8073738464002468</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09397634001280614</v>
+        <v>0.1443432223090956</v>
       </c>
       <c r="C60">
-        <v>-9.998726386687849</v>
+        <v>-5405.173002832393</v>
       </c>
       <c r="D60">
-        <v>11898.33527361331</v>
+        <v>6717.033997167609</v>
       </c>
       <c r="E60">
-        <v>5169.534</v>
+        <v>5383.407000000001</v>
       </c>
       <c r="F60">
-        <v>12404.634</v>
+        <v>12618.507</v>
       </c>
       <c r="G60">
         <v>496.3</v>
@@ -6213,45 +6213,45 @@
         <v>1187.8</v>
       </c>
       <c r="M60">
-        <v>1471.1895924</v>
+        <v>2533.796205600001</v>
       </c>
       <c r="N60">
-        <v>-283.3895924000003</v>
+        <v>-1345.996205600001</v>
       </c>
       <c r="O60">
-        <v>-73.11451483920008</v>
+        <v>-347.2670210448002</v>
       </c>
       <c r="P60">
-        <v>-210.2750775608002</v>
+        <v>-998.7291845552006</v>
       </c>
       <c r="Q60">
-        <v>1138.1249224392</v>
+        <v>349.6708154447995</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09408821215838242</v>
+        <v>0.09804861317758565</v>
       </c>
       <c r="T60">
-        <v>1.11520120458158</v>
+        <v>1.206665431353017</v>
       </c>
       <c r="U60">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.2083024523712638</v>
+        <v>0.1209459542652651</v>
       </c>
       <c r="W60">
-        <v>0.09389532914876812</v>
+        <v>0.1765140523835348</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.8073738464002471</v>
+        <v>0.4687827684700198</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1443432223090956</v>
+        <v>0.1458932223090956</v>
       </c>
       <c r="C61">
-        <v>-5405.173002832393</v>
+        <v>-5707.871053386751</v>
       </c>
       <c r="D61">
-        <v>6717.033997167609</v>
+        <v>6628.20894661325</v>
       </c>
       <c r="E61">
-        <v>5383.407000000001</v>
+        <v>5597.280000000001</v>
       </c>
       <c r="F61">
-        <v>12618.507</v>
+        <v>12832.38</v>
       </c>
       <c r="G61">
         <v>496.3</v>
@@ -6295,37 +6295,37 @@
         <v>1187.8</v>
       </c>
       <c r="M61">
-        <v>2533.796205600001</v>
+        <v>2576.741904</v>
       </c>
       <c r="N61">
-        <v>-1345.996205600001</v>
+        <v>-1388.941904000001</v>
       </c>
       <c r="O61">
-        <v>-347.2670210448002</v>
+        <v>-358.3470112320002</v>
       </c>
       <c r="P61">
-        <v>-998.7291845552006</v>
+        <v>-1030.594892768001</v>
       </c>
       <c r="Q61">
-        <v>349.6708154447995</v>
+        <v>317.8051072319995</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09804861317758565</v>
+        <v>0.09935482850702529</v>
       </c>
       <c r="T61">
-        <v>1.206665431353017</v>
+        <v>1.236832067136843</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1209459542652651</v>
+        <v>0.118930188360844</v>
       </c>
       <c r="W61">
-        <v>0.1765140523835348</v>
+        <v>0.1769188181771425</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.4687827684700198</v>
+        <v>0.4609697223288528</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1458932223090956</v>
+        <v>0.1474432223090956</v>
       </c>
       <c r="C62">
-        <v>-5707.871053386751</v>
+        <v>-6008.250545901434</v>
       </c>
       <c r="D62">
-        <v>6628.20894661325</v>
+        <v>6541.702454098567</v>
       </c>
       <c r="E62">
-        <v>5597.280000000001</v>
+        <v>5811.153</v>
       </c>
       <c r="F62">
-        <v>12832.38</v>
+        <v>13046.253</v>
       </c>
       <c r="G62">
         <v>496.3</v>
@@ -6377,37 +6377,37 @@
         <v>1187.8</v>
       </c>
       <c r="M62">
-        <v>2576.741904</v>
+        <v>2619.6876024</v>
       </c>
       <c r="N62">
-        <v>-1388.941904000001</v>
+        <v>-1431.887602400001</v>
       </c>
       <c r="O62">
-        <v>-358.3470112320002</v>
+        <v>-369.4270014192002</v>
       </c>
       <c r="P62">
-        <v>-1030.594892768001</v>
+        <v>-1062.4606009808</v>
       </c>
       <c r="Q62">
-        <v>317.8051072319995</v>
+        <v>285.9393990191998</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.09935482850702529</v>
+        <v>0.1007280292379747</v>
       </c>
       <c r="T62">
-        <v>1.236832067136843</v>
+        <v>1.268545709883941</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.118930188360844</v>
+        <v>0.1169805131418138</v>
       </c>
       <c r="W62">
-        <v>0.1769188181771425</v>
+        <v>0.1773103129611238</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4609697223288528</v>
+        <v>0.4534128416349372</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1474432223090956</v>
+        <v>0.1489932223090956</v>
       </c>
       <c r="C63">
-        <v>-6008.250545901434</v>
+        <v>-6306.401091168829</v>
       </c>
       <c r="D63">
-        <v>6541.702454098567</v>
+        <v>6457.424908831173</v>
       </c>
       <c r="E63">
-        <v>5811.153</v>
+        <v>6025.026000000002</v>
       </c>
       <c r="F63">
-        <v>13046.253</v>
+        <v>13260.126</v>
       </c>
       <c r="G63">
         <v>496.3</v>
@@ -6459,37 +6459,37 @@
         <v>1187.8</v>
       </c>
       <c r="M63">
-        <v>2619.6876024</v>
+        <v>2662.633300800001</v>
       </c>
       <c r="N63">
-        <v>-1431.887602400001</v>
+        <v>-1474.833300800001</v>
       </c>
       <c r="O63">
-        <v>-369.4270014192002</v>
+        <v>-380.5069916064002</v>
       </c>
       <c r="P63">
-        <v>-1062.4606009808</v>
+        <v>-1094.326309193601</v>
       </c>
       <c r="Q63">
-        <v>285.9393990191998</v>
+        <v>254.0736908063996</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1007280292379747</v>
+        <v>0.1021735036916056</v>
       </c>
       <c r="T63">
-        <v>1.268545709883941</v>
+        <v>1.301928491722993</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1169805131418138</v>
+        <v>0.1150937306717845</v>
       </c>
       <c r="W63">
-        <v>0.1773103129611238</v>
+        <v>0.1776891788811057</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4534128416349372</v>
+        <v>0.4460997312859866</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1489932223090956</v>
+        <v>0.1505432223090956</v>
       </c>
       <c r="C64">
-        <v>-6306.401091168829</v>
+        <v>-6602.407740850372</v>
       </c>
       <c r="D64">
-        <v>6457.424908831173</v>
+        <v>6375.29125914963</v>
       </c>
       <c r="E64">
-        <v>6025.026000000002</v>
+        <v>6238.899000000001</v>
       </c>
       <c r="F64">
-        <v>13260.126</v>
+        <v>13473.999</v>
       </c>
       <c r="G64">
         <v>496.3</v>
@@ -6541,37 +6541,37 @@
         <v>1187.8</v>
       </c>
       <c r="M64">
-        <v>2662.633300800001</v>
+        <v>2705.5789992</v>
       </c>
       <c r="N64">
-        <v>-1474.833300800001</v>
+        <v>-1517.778999200001</v>
       </c>
       <c r="O64">
-        <v>-380.5069916064002</v>
+        <v>-391.5869817936002</v>
       </c>
       <c r="P64">
-        <v>-1094.326309193601</v>
+        <v>-1126.192017406401</v>
       </c>
       <c r="Q64">
-        <v>254.0736908063996</v>
+        <v>222.2079825935996</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1021735036916056</v>
+        <v>0.1036971118994868</v>
       </c>
       <c r="T64">
-        <v>1.301928491722993</v>
+        <v>1.337115748256047</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1150937306717845</v>
+        <v>0.1132668460579467</v>
       </c>
       <c r="W64">
-        <v>0.1776891788811057</v>
+        <v>0.1780560173115643</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4460997312859866</v>
+        <v>0.439018783170336</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1505432223090956</v>
+        <v>0.1520932223090956</v>
       </c>
       <c r="C65">
-        <v>-6602.407740850372</v>
+        <v>-6896.351273778801</v>
       </c>
       <c r="D65">
-        <v>6375.29125914963</v>
+        <v>6295.220726221201</v>
       </c>
       <c r="E65">
-        <v>6238.899000000001</v>
+        <v>6452.772000000003</v>
       </c>
       <c r="F65">
-        <v>13473.999</v>
+        <v>13687.872</v>
       </c>
       <c r="G65">
         <v>496.3</v>
@@ -6623,37 +6623,37 @@
         <v>1187.8</v>
       </c>
       <c r="M65">
-        <v>2705.5789992</v>
+        <v>2748.524697600001</v>
       </c>
       <c r="N65">
-        <v>-1517.778999200001</v>
+        <v>-1560.724697600001</v>
       </c>
       <c r="O65">
-        <v>-391.5869817936002</v>
+        <v>-402.6669719808003</v>
       </c>
       <c r="P65">
-        <v>-1126.192017406401</v>
+        <v>-1158.057725619201</v>
       </c>
       <c r="Q65">
-        <v>222.2079825935996</v>
+        <v>190.3422743807994</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1036971118994868</v>
+        <v>0.1053053650078059</v>
       </c>
       <c r="T65">
-        <v>1.337115748256047</v>
+        <v>1.37425785237427</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1132668460579467</v>
+        <v>0.1114970515882913</v>
       </c>
       <c r="W65">
-        <v>0.1780560173115643</v>
+        <v>0.1784113920410711</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.439018783170336</v>
+        <v>0.4321591146832995</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1520932223090956</v>
+        <v>0.1536432223090957</v>
       </c>
       <c r="C66">
-        <v>-6896.351273778801</v>
+        <v>-7188.30846095313</v>
       </c>
       <c r="D66">
-        <v>6295.220726221201</v>
+        <v>6217.136539046873</v>
       </c>
       <c r="E66">
-        <v>6452.772000000003</v>
+        <v>6666.645000000002</v>
       </c>
       <c r="F66">
-        <v>13687.872</v>
+        <v>13901.745</v>
       </c>
       <c r="G66">
         <v>496.3</v>
@@ -6705,37 +6705,37 @@
         <v>1187.8</v>
       </c>
       <c r="M66">
-        <v>2748.524697600001</v>
+        <v>2791.470396000001</v>
       </c>
       <c r="N66">
-        <v>-1560.724697600001</v>
+        <v>-1603.670396000001</v>
       </c>
       <c r="O66">
-        <v>-402.6669719808003</v>
+        <v>-413.7469621680003</v>
       </c>
       <c r="P66">
-        <v>-1158.057725619201</v>
+        <v>-1189.923433832001</v>
       </c>
       <c r="Q66">
-        <v>190.3422743807994</v>
+        <v>158.4765661679994</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1053053650078059</v>
+        <v>0.1070055182937432</v>
       </c>
       <c r="T66">
-        <v>1.37425785237427</v>
+        <v>1.413522362442107</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1114970515882913</v>
+        <v>0.1097817123330868</v>
       </c>
       <c r="W66">
-        <v>0.1784113920410711</v>
+        <v>0.1787558321635162</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4321591146832995</v>
+        <v>0.425510512918941</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1536432223090957</v>
+        <v>0.1551932223090957</v>
       </c>
       <c r="C67">
-        <v>-7188.30846095313</v>
+        <v>-7478.352311053668</v>
       </c>
       <c r="D67">
-        <v>6217.136539046873</v>
+        <v>6140.965688946334</v>
       </c>
       <c r="E67">
-        <v>6666.645000000002</v>
+        <v>6880.518000000002</v>
       </c>
       <c r="F67">
-        <v>13901.745</v>
+        <v>14115.618</v>
       </c>
       <c r="G67">
         <v>496.3</v>
@@ -6787,37 +6787,37 @@
         <v>1187.8</v>
       </c>
       <c r="M67">
-        <v>2791.470396000001</v>
+        <v>2834.4160944</v>
       </c>
       <c r="N67">
-        <v>-1603.670396000001</v>
+        <v>-1646.616094400001</v>
       </c>
       <c r="O67">
-        <v>-413.7469621680003</v>
+        <v>-424.8269523552002</v>
       </c>
       <c r="P67">
-        <v>-1189.923433832001</v>
+        <v>-1221.7891420448</v>
       </c>
       <c r="Q67">
-        <v>158.4765661679994</v>
+        <v>126.6108579551997</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1070055182937432</v>
+        <v>0.1088056805965003</v>
       </c>
       <c r="T67">
-        <v>1.413522362442107</v>
+        <v>1.455096549572757</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1097817123330868</v>
+        <v>0.1081183530553128</v>
       </c>
       <c r="W67">
-        <v>0.1787558321635162</v>
+        <v>0.1790898347064932</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.425510512918941</v>
+        <v>0.4190633839353207</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1551932223090957</v>
+        <v>0.1567432223090956</v>
       </c>
       <c r="C68">
-        <v>-7478.352311053668</v>
+        <v>-7766.552298127575</v>
       </c>
       <c r="D68">
-        <v>6140.965688946334</v>
+        <v>6066.638701872428</v>
       </c>
       <c r="E68">
-        <v>6880.518000000002</v>
+        <v>7094.391000000003</v>
       </c>
       <c r="F68">
-        <v>14115.618</v>
+        <v>14329.491</v>
       </c>
       <c r="G68">
         <v>496.3</v>
@@ -6869,37 +6869,37 @@
         <v>1187.8</v>
       </c>
       <c r="M68">
-        <v>2834.4160944</v>
+        <v>2877.361792800001</v>
       </c>
       <c r="N68">
-        <v>-1646.616094400001</v>
+        <v>-1689.561792800001</v>
       </c>
       <c r="O68">
-        <v>-424.8269523552002</v>
+        <v>-435.9069425424003</v>
       </c>
       <c r="P68">
-        <v>-1221.7891420448</v>
+        <v>-1253.654850257601</v>
       </c>
       <c r="Q68">
-        <v>126.6108579551997</v>
+        <v>94.74514974239924</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1088056805965003</v>
+        <v>0.1107149436448792</v>
       </c>
       <c r="T68">
-        <v>1.455096549572757</v>
+        <v>1.499190384408295</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1081183530553128</v>
+        <v>0.1065046462932931</v>
       </c>
       <c r="W68">
-        <v>0.1790898347064932</v>
+        <v>0.1794138670243067</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4190633839353207</v>
+        <v>0.4128087065631517</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1567432223090956</v>
+        <v>0.1582932223090956</v>
       </c>
       <c r="C69">
-        <v>-7766.552298127575</v>
+        <v>-8052.974572937412</v>
       </c>
       <c r="D69">
-        <v>6066.638701872428</v>
+        <v>5994.089427062591</v>
       </c>
       <c r="E69">
-        <v>7094.391000000003</v>
+        <v>7308.264000000003</v>
       </c>
       <c r="F69">
-        <v>14329.491</v>
+        <v>14543.364</v>
       </c>
       <c r="G69">
         <v>496.3</v>
@@ -6951,37 +6951,37 @@
         <v>1187.8</v>
       </c>
       <c r="M69">
-        <v>2877.361792800001</v>
+        <v>2920.307491200001</v>
       </c>
       <c r="N69">
-        <v>-1689.561792800001</v>
+        <v>-1732.507491200001</v>
       </c>
       <c r="O69">
-        <v>-435.9069425424003</v>
+        <v>-446.9869327296003</v>
       </c>
       <c r="P69">
-        <v>-1253.654850257601</v>
+        <v>-1285.520558470401</v>
       </c>
       <c r="Q69">
-        <v>94.74514974239924</v>
+        <v>62.87944152959949</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1107149436448792</v>
+        <v>0.1127435356337816</v>
       </c>
       <c r="T69">
-        <v>1.499190384408295</v>
+        <v>1.546040083921054</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1065046462932931</v>
+        <v>0.1049384014948624</v>
       </c>
       <c r="W69">
-        <v>0.1794138670243067</v>
+        <v>0.1797283689798317</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4128087065631517</v>
+        <v>0.4067379902901642</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1582932223090956</v>
+        <v>0.1598432223090957</v>
       </c>
       <c r="C70">
-        <v>-8052.974572937412</v>
+        <v>-8337.682159324144</v>
       </c>
       <c r="D70">
-        <v>5994.089427062591</v>
+        <v>5923.25484067586</v>
       </c>
       <c r="E70">
-        <v>7308.264000000003</v>
+        <v>7522.137000000002</v>
       </c>
       <c r="F70">
-        <v>14543.364</v>
+        <v>14757.237</v>
       </c>
       <c r="G70">
         <v>496.3</v>
@@ -7033,37 +7033,37 @@
         <v>1187.8</v>
       </c>
       <c r="M70">
-        <v>2920.307491200001</v>
+        <v>2963.2531896</v>
       </c>
       <c r="N70">
-        <v>-1732.507491200001</v>
+        <v>-1775.453189600001</v>
       </c>
       <c r="O70">
-        <v>-446.9869327296003</v>
+        <v>-458.0669229168002</v>
       </c>
       <c r="P70">
-        <v>-1285.520558470401</v>
+        <v>-1317.386266683201</v>
       </c>
       <c r="Q70">
-        <v>62.87944152959949</v>
+        <v>31.01373331679952</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1127435356337816</v>
+        <v>0.1149030045251939</v>
       </c>
       <c r="T70">
-        <v>1.546040083921054</v>
+        <v>1.595912344692701</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1049384014948624</v>
+        <v>0.1034175550963861</v>
       </c>
       <c r="W70">
-        <v>0.1797283689798317</v>
+        <v>0.1800337549366457</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4067379902901642</v>
+        <v>0.4008432368076981</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1598432223090957</v>
+        <v>0.1613932223090957</v>
       </c>
       <c r="C71">
-        <v>-8337.682159324144</v>
+        <v>-8620.735136809773</v>
       </c>
       <c r="D71">
-        <v>5923.25484067586</v>
+        <v>5854.07486319023</v>
       </c>
       <c r="E71">
-        <v>7522.137000000002</v>
+        <v>7736.010000000004</v>
       </c>
       <c r="F71">
-        <v>14757.237</v>
+        <v>14971.11</v>
       </c>
       <c r="G71">
         <v>496.3</v>
@@ -7115,37 +7115,37 @@
         <v>1187.8</v>
       </c>
       <c r="M71">
-        <v>2963.2531896</v>
+        <v>3006.198888000001</v>
       </c>
       <c r="N71">
-        <v>-1775.453189600001</v>
+        <v>-1818.398888000001</v>
       </c>
       <c r="O71">
-        <v>-458.0669229168002</v>
+        <v>-469.1469131040003</v>
       </c>
       <c r="P71">
-        <v>-1317.386266683201</v>
+        <v>-1349.251974896001</v>
       </c>
       <c r="Q71">
-        <v>31.01373331679952</v>
+        <v>-0.8519748960006837</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1149030045251939</v>
+        <v>0.1172064380093671</v>
       </c>
       <c r="T71">
-        <v>1.595912344692701</v>
+        <v>1.649109422849125</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1034175550963861</v>
+        <v>0.101940161452152</v>
       </c>
       <c r="W71">
-        <v>0.1800337549366457</v>
+        <v>0.1803304155804079</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4008432368076981</v>
+        <v>0.3951169048533024</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1613932223090957</v>
+        <v>0.1629432223090956</v>
       </c>
       <c r="C72">
-        <v>-8620.735136809773</v>
+        <v>-8902.190810551554</v>
       </c>
       <c r="D72">
-        <v>5854.07486319023</v>
+        <v>5786.49218944845</v>
       </c>
       <c r="E72">
-        <v>7736.010000000004</v>
+        <v>7949.883000000003</v>
       </c>
       <c r="F72">
-        <v>14971.11</v>
+        <v>15184.983</v>
       </c>
       <c r="G72">
         <v>496.3</v>
@@ -7197,37 +7197,37 @@
         <v>1187.8</v>
       </c>
       <c r="M72">
-        <v>3006.198888000001</v>
+        <v>3049.144586400001</v>
       </c>
       <c r="N72">
-        <v>-1818.398888000001</v>
+        <v>-1861.344586400001</v>
       </c>
       <c r="O72">
-        <v>-469.1469131040003</v>
+        <v>-480.2269032912002</v>
       </c>
       <c r="P72">
-        <v>-1349.251974896001</v>
+        <v>-1381.117683108801</v>
       </c>
       <c r="Q72">
-        <v>-0.8519748960006837</v>
+        <v>-32.71768310880066</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1172064380093671</v>
+        <v>0.1196687289752073</v>
       </c>
       <c r="T72">
-        <v>1.649109422849125</v>
+        <v>1.705975265016336</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.101940161452152</v>
+        <v>0.1005043845302907</v>
       </c>
       <c r="W72">
-        <v>0.1803304155804079</v>
+        <v>0.1806187195863176</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3951169048533024</v>
+        <v>0.3895518780243826</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1629432223090956</v>
+        <v>0.1644932223090956</v>
       </c>
       <c r="C73">
-        <v>-8902.190810551552</v>
+        <v>-9182.103869658291</v>
       </c>
       <c r="D73">
-        <v>5786.49218944845</v>
+        <v>5720.45213034171</v>
       </c>
       <c r="E73">
-        <v>7949.883000000002</v>
+        <v>8163.756000000001</v>
       </c>
       <c r="F73">
-        <v>15184.983</v>
+        <v>15398.856</v>
       </c>
       <c r="G73">
         <v>496.3</v>
@@ -7279,37 +7279,37 @@
         <v>1187.8</v>
       </c>
       <c r="M73">
-        <v>3049.144586400001</v>
+        <v>3092.090284800001</v>
       </c>
       <c r="N73">
-        <v>-1861.344586400001</v>
+        <v>-1904.290284800001</v>
       </c>
       <c r="O73">
-        <v>-480.2269032912002</v>
+        <v>-491.3068934784002</v>
       </c>
       <c r="P73">
-        <v>-1381.117683108801</v>
+        <v>-1412.9833913216</v>
       </c>
       <c r="Q73">
-        <v>-32.71768310880066</v>
+        <v>-64.5833913216004</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1196687289752073</v>
+        <v>0.122306897867179</v>
       </c>
       <c r="T73">
-        <v>1.705975265016335</v>
+        <v>1.766902953052633</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1005043845302907</v>
+        <v>0.09910849030070336</v>
       </c>
       <c r="W73">
-        <v>0.1806187195863176</v>
+        <v>0.1808990151476188</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3895518780243826</v>
+        <v>0.384141435274044</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1644932223090956</v>
+        <v>0.1660432223090956</v>
       </c>
       <c r="C74">
-        <v>-9182.103869658291</v>
+        <v>-9460.526534787996</v>
       </c>
       <c r="D74">
-        <v>5720.45213034171</v>
+        <v>5655.902465212005</v>
       </c>
       <c r="E74">
-        <v>8163.756000000001</v>
+        <v>8377.629000000001</v>
       </c>
       <c r="F74">
-        <v>15398.856</v>
+        <v>15612.729</v>
       </c>
       <c r="G74">
         <v>496.3</v>
@@ -7361,37 +7361,37 @@
         <v>1187.8</v>
       </c>
       <c r="M74">
-        <v>3092.090284800001</v>
+        <v>3135.0359832</v>
       </c>
       <c r="N74">
-        <v>-1904.290284800001</v>
+        <v>-1947.235983200001</v>
       </c>
       <c r="O74">
-        <v>-491.3068934784002</v>
+        <v>-502.3868836656002</v>
       </c>
       <c r="P74">
-        <v>-1412.9833913216</v>
+        <v>-1444.8490995344</v>
       </c>
       <c r="Q74">
-        <v>-64.5833913216004</v>
+        <v>-96.44909953440037</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.122306897867179</v>
+        <v>0.1251404866770745</v>
       </c>
       <c r="T74">
-        <v>1.766902953052633</v>
+        <v>1.832343803165693</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.09910849030070336</v>
+        <v>0.09775083974863893</v>
       </c>
       <c r="W74">
-        <v>0.1808990151476188</v>
+        <v>0.1811716313784733</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.384141435274044</v>
+        <v>0.3788792238319338</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1660432223090956</v>
+        <v>0.1675932223090957</v>
       </c>
       <c r="C75">
-        <v>-9460.526534787996</v>
+        <v>-9737.508695864059</v>
       </c>
       <c r="D75">
-        <v>5655.902465212005</v>
+        <v>5592.793304135944</v>
       </c>
       <c r="E75">
-        <v>8377.629000000001</v>
+        <v>8591.502000000002</v>
       </c>
       <c r="F75">
-        <v>15612.729</v>
+        <v>15826.602</v>
       </c>
       <c r="G75">
         <v>496.3</v>
@@ -7443,37 +7443,37 @@
         <v>1187.8</v>
       </c>
       <c r="M75">
-        <v>3135.0359832</v>
+        <v>3177.981681600001</v>
       </c>
       <c r="N75">
-        <v>-1947.235983200001</v>
+        <v>-1990.181681600001</v>
       </c>
       <c r="O75">
-        <v>-502.3868836656002</v>
+        <v>-513.4668738528003</v>
       </c>
       <c r="P75">
-        <v>-1444.8490995344</v>
+        <v>-1476.714807747201</v>
       </c>
       <c r="Q75">
-        <v>-96.44909953440037</v>
+        <v>-128.3148077472006</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1251404866770745</v>
+        <v>0.128192043856962</v>
       </c>
       <c r="T75">
-        <v>1.832343803165693</v>
+        <v>1.902818564825912</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.09775083974863893</v>
+        <v>0.09642988245473841</v>
       </c>
       <c r="W75">
-        <v>0.1811716313784733</v>
+        <v>0.1814368796030885</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3788792238319338</v>
+        <v>0.3737592343206915</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1675932223090957</v>
+        <v>0.1691432223090956</v>
       </c>
       <c r="C76">
-        <v>-9737.508695864059</v>
+        <v>-10013.09804067326</v>
       </c>
       <c r="D76">
-        <v>5592.793304135944</v>
+        <v>5531.076959326741</v>
       </c>
       <c r="E76">
-        <v>8591.502000000002</v>
+        <v>8805.375000000002</v>
       </c>
       <c r="F76">
-        <v>15826.602</v>
+        <v>16040.475</v>
       </c>
       <c r="G76">
         <v>496.3</v>
@@ -7525,37 +7525,37 @@
         <v>1187.8</v>
       </c>
       <c r="M76">
-        <v>3177.981681600001</v>
+        <v>3220.927380000001</v>
       </c>
       <c r="N76">
-        <v>-1990.181681600001</v>
+        <v>-2033.127380000001</v>
       </c>
       <c r="O76">
-        <v>-513.4668738528003</v>
+        <v>-524.5468640400002</v>
       </c>
       <c r="P76">
-        <v>-1476.714807747201</v>
+        <v>-1508.580515960001</v>
       </c>
       <c r="Q76">
-        <v>-128.3148077472006</v>
+        <v>-160.1805159600005</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.128192043856962</v>
+        <v>0.1314877256112405</v>
       </c>
       <c r="T76">
-        <v>1.902818564825912</v>
+        <v>1.978931307418949</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.09642988245473841</v>
+        <v>0.09514415068867522</v>
       </c>
       <c r="W76">
-        <v>0.1814368796030885</v>
+        <v>0.181695054541714</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3737592343206915</v>
+        <v>0.3687757778630822</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1691432223090956</v>
+        <v>0.1706932223090956</v>
       </c>
       <c r="C77">
-        <v>-10013.09804067326</v>
+        <v>-10287.34017504227</v>
       </c>
       <c r="D77">
-        <v>5531.076959326741</v>
+        <v>5470.707824957729</v>
       </c>
       <c r="E77">
-        <v>8805.375000000002</v>
+        <v>9019.248000000001</v>
       </c>
       <c r="F77">
-        <v>16040.475</v>
+        <v>16254.348</v>
       </c>
       <c r="G77">
         <v>496.3</v>
@@ -7607,37 +7607,37 @@
         <v>1187.8</v>
       </c>
       <c r="M77">
-        <v>3220.927380000001</v>
+        <v>3263.8730784</v>
       </c>
       <c r="N77">
-        <v>-2033.127380000001</v>
+        <v>-2076.073078400001</v>
       </c>
       <c r="O77">
-        <v>-524.5468640400002</v>
+        <v>-535.6268542272002</v>
       </c>
       <c r="P77">
-        <v>-1508.580515960001</v>
+        <v>-1540.446224172801</v>
       </c>
       <c r="Q77">
-        <v>-160.1805159600005</v>
+        <v>-192.0462241728005</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1314877256112405</v>
+        <v>0.1350580475117088</v>
       </c>
       <c r="T77">
-        <v>1.978931307418949</v>
+        <v>2.061386778561405</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.09514415068867522</v>
+        <v>0.0938922539690874</v>
       </c>
       <c r="W77">
-        <v>0.181695054541714</v>
+        <v>0.1819464354030073</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3687757778630822</v>
+        <v>0.3639234649964628</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1706932223090956</v>
+        <v>0.1722432223090956</v>
       </c>
       <c r="C78">
-        <v>-10287.34017504227</v>
+        <v>-10560.27873522908</v>
       </c>
       <c r="D78">
-        <v>5470.707824957729</v>
+        <v>5411.642264770921</v>
       </c>
       <c r="E78">
-        <v>9019.248000000001</v>
+        <v>9233.121000000001</v>
       </c>
       <c r="F78">
-        <v>16254.348</v>
+        <v>16468.221</v>
       </c>
       <c r="G78">
         <v>496.3</v>
@@ -7689,37 +7689,37 @@
         <v>1187.8</v>
       </c>
       <c r="M78">
-        <v>3263.8730784</v>
+        <v>3306.8187768</v>
       </c>
       <c r="N78">
-        <v>-2076.073078400001</v>
+        <v>-2119.018776800001</v>
       </c>
       <c r="O78">
-        <v>-535.6268542272002</v>
+        <v>-546.7068444144002</v>
       </c>
       <c r="P78">
-        <v>-1540.446224172801</v>
+        <v>-1572.3119323856</v>
       </c>
       <c r="Q78">
-        <v>-192.0462241728005</v>
+        <v>-223.9119323856003</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1350580475117088</v>
+        <v>0.1389388321861309</v>
       </c>
       <c r="T78">
-        <v>2.061386778561405</v>
+        <v>2.15101229067277</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.0938922539690874</v>
+        <v>0.09267287404741094</v>
       </c>
       <c r="W78">
-        <v>0.1819464354030073</v>
+        <v>0.1821912868912799</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3639234649964628</v>
+        <v>0.359197186230275</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1722432223090956</v>
+        <v>0.1737932223090956</v>
       </c>
       <c r="C79">
-        <v>-10560.27873522908</v>
+        <v>-10831.95549311146</v>
       </c>
       <c r="D79">
-        <v>5411.642264770921</v>
+        <v>5353.838506888547</v>
       </c>
       <c r="E79">
-        <v>9233.121000000001</v>
+        <v>9446.994000000004</v>
       </c>
       <c r="F79">
-        <v>16468.221</v>
+        <v>16682.094</v>
       </c>
       <c r="G79">
         <v>496.3</v>
@@ -7771,37 +7771,37 @@
         <v>1187.8</v>
       </c>
       <c r="M79">
-        <v>3306.8187768</v>
+        <v>3349.764475200001</v>
       </c>
       <c r="N79">
-        <v>-2119.018776800001</v>
+        <v>-2161.964475200001</v>
       </c>
       <c r="O79">
-        <v>-546.7068444144002</v>
+        <v>-557.7868346016004</v>
       </c>
       <c r="P79">
-        <v>-1572.3119323856</v>
+        <v>-1604.177640598401</v>
       </c>
       <c r="Q79">
-        <v>-223.9119323856003</v>
+        <v>-255.7776405984009</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1389388321861309</v>
+        <v>0.1431724154673187</v>
       </c>
       <c r="T79">
-        <v>2.15101229067277</v>
+        <v>2.248785576612442</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.09267287404741094</v>
+        <v>0.09148476027757232</v>
       </c>
       <c r="W79">
-        <v>0.1821912868912799</v>
+        <v>0.1824298601362635</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.359197186230275</v>
+        <v>0.3545920940991175</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1737932223090956</v>
+        <v>0.1753432223090956</v>
       </c>
       <c r="C80">
-        <v>-10831.95549311146</v>
+        <v>-11102.41045470533</v>
       </c>
       <c r="D80">
-        <v>5353.838506888547</v>
+        <v>5297.256545294675</v>
       </c>
       <c r="E80">
-        <v>9446.994000000004</v>
+        <v>9660.867000000004</v>
       </c>
       <c r="F80">
-        <v>16682.094</v>
+        <v>16895.967</v>
       </c>
       <c r="G80">
         <v>496.3</v>
@@ -7853,37 +7853,37 @@
         <v>1187.8</v>
       </c>
       <c r="M80">
-        <v>3349.764475200001</v>
+        <v>3392.710173600001</v>
       </c>
       <c r="N80">
-        <v>-2161.964475200001</v>
+        <v>-2204.910173600001</v>
       </c>
       <c r="O80">
-        <v>-557.7868346016004</v>
+        <v>-568.8668247888003</v>
       </c>
       <c r="P80">
-        <v>-1604.177640598401</v>
+        <v>-1636.043348811201</v>
       </c>
       <c r="Q80">
-        <v>-255.7776405984009</v>
+        <v>-287.6433488112007</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1431724154673187</v>
+        <v>0.1478091971562387</v>
       </c>
       <c r="T80">
-        <v>2.248785576612442</v>
+        <v>2.355870604070178</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.09148476027757232</v>
+        <v>0.09032672533734989</v>
       </c>
       <c r="W80">
-        <v>0.1824298601362635</v>
+        <v>0.1826623935522602</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3545920940991175</v>
+        <v>0.3501035865788755</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1753432223090956</v>
+        <v>0.1768932223090957</v>
       </c>
       <c r="C81">
-        <v>-11102.41045470533</v>
+        <v>-11371.68195250135</v>
       </c>
       <c r="D81">
-        <v>5297.256545294675</v>
+        <v>5241.858047498657</v>
       </c>
       <c r="E81">
-        <v>9660.867000000004</v>
+        <v>9874.740000000003</v>
       </c>
       <c r="F81">
-        <v>16895.967</v>
+        <v>17109.84</v>
       </c>
       <c r="G81">
         <v>496.3</v>
@@ -7935,37 +7935,37 @@
         <v>1187.8</v>
       </c>
       <c r="M81">
-        <v>3392.710173600001</v>
+        <v>3435.655872000001</v>
       </c>
       <c r="N81">
-        <v>-2204.910173600001</v>
+        <v>-2247.855872000001</v>
       </c>
       <c r="O81">
-        <v>-568.8668247888003</v>
+        <v>-579.9468149760003</v>
       </c>
       <c r="P81">
-        <v>-1636.043348811201</v>
+        <v>-1667.909057024001</v>
       </c>
       <c r="Q81">
-        <v>-287.6433488112007</v>
+        <v>-319.5090570240006</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1478091971562387</v>
+        <v>0.1529096570140506</v>
       </c>
       <c r="T81">
-        <v>2.355870604070178</v>
+        <v>2.473664134273687</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.09032672533734989</v>
+        <v>0.08919764127063301</v>
       </c>
       <c r="W81">
-        <v>0.1826623935522602</v>
+        <v>0.1828891136328569</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3501035865788755</v>
+        <v>0.3457272917466396</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1768932223090957</v>
+        <v>0.1784432223090956</v>
       </c>
       <c r="C82">
-        <v>-11371.68195250135</v>
+        <v>-11639.80673206749</v>
       </c>
       <c r="D82">
-        <v>5241.858047498657</v>
+        <v>5187.606267932509</v>
       </c>
       <c r="E82">
-        <v>9874.740000000003</v>
+        <v>10088.613</v>
       </c>
       <c r="F82">
-        <v>17109.84</v>
+        <v>17323.713</v>
       </c>
       <c r="G82">
         <v>496.3</v>
@@ -8017,37 +8017,37 @@
         <v>1187.8</v>
       </c>
       <c r="M82">
-        <v>3435.655872000001</v>
+        <v>3478.601570400001</v>
       </c>
       <c r="N82">
-        <v>-2247.855872000001</v>
+        <v>-2290.801570400001</v>
       </c>
       <c r="O82">
-        <v>-579.9468149760003</v>
+        <v>-591.0268051632003</v>
       </c>
       <c r="P82">
-        <v>-1667.909057024001</v>
+        <v>-1699.774765236801</v>
       </c>
       <c r="Q82">
-        <v>-319.5090570240006</v>
+        <v>-351.3747652368006</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1529096570140506</v>
+        <v>0.1585470073832112</v>
       </c>
       <c r="T82">
-        <v>2.473664134273687</v>
+        <v>2.603856983445986</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.08919764127063301</v>
+        <v>0.08809643582284743</v>
       </c>
       <c r="W82">
-        <v>0.1828891136328569</v>
+        <v>0.1831102356867722</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3457272917466396</v>
+        <v>0.341459053576928</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1784432223090956</v>
+        <v>0.1799932223090956</v>
       </c>
       <c r="C83">
-        <v>-11639.80673206749</v>
+        <v>-11906.82003332892</v>
       </c>
       <c r="D83">
-        <v>5187.606267932509</v>
+        <v>5134.465966671079</v>
       </c>
       <c r="E83">
-        <v>10088.613</v>
+        <v>10302.486</v>
       </c>
       <c r="F83">
-        <v>17323.713</v>
+        <v>17537.586</v>
       </c>
       <c r="G83">
         <v>496.3</v>
@@ -8099,37 +8099,37 @@
         <v>1187.8</v>
       </c>
       <c r="M83">
-        <v>3478.601570400001</v>
+        <v>3521.547268800001</v>
       </c>
       <c r="N83">
-        <v>-2290.801570400001</v>
+        <v>-2333.747268800001</v>
       </c>
       <c r="O83">
-        <v>-591.0268051632003</v>
+        <v>-602.1067953504003</v>
       </c>
       <c r="P83">
-        <v>-1699.774765236801</v>
+        <v>-1731.640473449601</v>
       </c>
       <c r="Q83">
-        <v>-351.3747652368006</v>
+        <v>-383.2404734496008</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1585470073832112</v>
+        <v>0.1648107300156118</v>
       </c>
       <c r="T83">
-        <v>2.603856983445986</v>
+        <v>2.748515704748541</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.08809643582284743</v>
+        <v>0.08702208904452001</v>
       </c>
       <c r="W83">
-        <v>0.1831102356867722</v>
+        <v>0.1833259645198604</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.341459053576928</v>
+        <v>0.3372949187772093</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1799932223090956</v>
+        <v>0.1815432223090956</v>
       </c>
       <c r="C84">
-        <v>-11906.82003332892</v>
+        <v>-12172.75566690279</v>
       </c>
       <c r="D84">
-        <v>5134.465966671079</v>
+        <v>5082.403333097207</v>
       </c>
       <c r="E84">
-        <v>10302.486</v>
+        <v>10516.359</v>
       </c>
       <c r="F84">
-        <v>17537.586</v>
+        <v>17751.459</v>
       </c>
       <c r="G84">
         <v>496.3</v>
@@ -8181,37 +8181,37 @@
         <v>1187.8</v>
       </c>
       <c r="M84">
-        <v>3521.547268800001</v>
+        <v>3564.492967200001</v>
       </c>
       <c r="N84">
-        <v>-2333.747268800001</v>
+        <v>-2376.692967200001</v>
       </c>
       <c r="O84">
-        <v>-602.1067953504003</v>
+        <v>-613.1867855376003</v>
       </c>
       <c r="P84">
-        <v>-1731.640473449601</v>
+        <v>-1763.506181662401</v>
       </c>
       <c r="Q84">
-        <v>-383.2404734496008</v>
+        <v>-415.1061816624006</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1648107300156118</v>
+        <v>0.1718113611930008</v>
       </c>
       <c r="T84">
-        <v>2.748515704748541</v>
+        <v>2.910193099145514</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.08702208904452001</v>
+        <v>0.08597363014036917</v>
       </c>
       <c r="W84">
-        <v>0.1833259645198604</v>
+        <v>0.1835364950678139</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3372949187772093</v>
+        <v>0.3332311245750743</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1815432223090956</v>
+        <v>0.1830932223090957</v>
       </c>
       <c r="C85">
-        <v>-12172.75566690279</v>
+        <v>-12437.6460858356</v>
       </c>
       <c r="D85">
-        <v>5082.403333097207</v>
+        <v>5031.385914164404</v>
       </c>
       <c r="E85">
-        <v>10516.359</v>
+        <v>10730.23200000001</v>
       </c>
       <c r="F85">
-        <v>17751.459</v>
+        <v>17965.33200000001</v>
       </c>
       <c r="G85">
         <v>496.3</v>
@@ -8263,37 +8263,37 @@
         <v>1187.8</v>
       </c>
       <c r="M85">
-        <v>3564.492967200001</v>
+        <v>3607.438665600001</v>
       </c>
       <c r="N85">
-        <v>-2376.692967200001</v>
+        <v>-2419.638665600001</v>
       </c>
       <c r="O85">
-        <v>-613.1867855376003</v>
+        <v>-624.2667757248004</v>
       </c>
       <c r="P85">
-        <v>-1763.506181662401</v>
+        <v>-1795.371889875201</v>
       </c>
       <c r="Q85">
-        <v>-415.1061816624006</v>
+        <v>-446.9718898752008</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1718113611930008</v>
+        <v>0.1796870712675633</v>
       </c>
       <c r="T85">
-        <v>2.910193099145514</v>
+        <v>3.092080167842109</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.08597363014036917</v>
+        <v>0.08495013454346001</v>
       </c>
       <c r="W85">
-        <v>0.1835364950678139</v>
+        <v>0.1837420129836732</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3332311245750743</v>
+        <v>0.3292640873777519</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1830932223090956</v>
+        <v>0.1846432223090956</v>
       </c>
       <c r="C86">
-        <v>-12437.6460858356</v>
+        <v>-12701.5224530628</v>
       </c>
       <c r="D86">
-        <v>5031.385914164404</v>
+        <v>4981.382546937197</v>
       </c>
       <c r="E86">
-        <v>10730.232</v>
+        <v>10944.105</v>
       </c>
       <c r="F86">
-        <v>17965.332</v>
+        <v>18179.205</v>
       </c>
       <c r="G86">
         <v>496.3</v>
@@ -8345,37 +8345,37 @@
         <v>1187.8</v>
       </c>
       <c r="M86">
-        <v>3607.438665600001</v>
+        <v>3650.384364</v>
       </c>
       <c r="N86">
-        <v>-2419.638665600001</v>
+        <v>-2462.584364000001</v>
       </c>
       <c r="O86">
-        <v>-624.2667757248003</v>
+        <v>-635.3467659120003</v>
       </c>
       <c r="P86">
-        <v>-1795.371889875201</v>
+        <v>-1827.237598088001</v>
       </c>
       <c r="Q86">
-        <v>-446.9718898752005</v>
+        <v>-478.8375980880005</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1796870712675632</v>
+        <v>0.1886128760187341</v>
       </c>
       <c r="T86">
-        <v>3.092080167842107</v>
+        <v>3.298218845698248</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.08495013454346002</v>
+        <v>0.08395072119588991</v>
       </c>
       <c r="W86">
-        <v>0.1837420129836732</v>
+        <v>0.1839426951838653</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.329264087377752</v>
+        <v>0.3253903922321314</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1846432223090956</v>
+        <v>0.1861932223090957</v>
       </c>
       <c r="C87">
-        <v>-12701.5224530628</v>
+        <v>-12964.4147048855</v>
       </c>
       <c r="D87">
-        <v>4981.382546937197</v>
+        <v>4932.363295114495</v>
       </c>
       <c r="E87">
-        <v>10944.105</v>
+        <v>11157.978</v>
       </c>
       <c r="F87">
-        <v>18179.205</v>
+        <v>18393.078</v>
       </c>
       <c r="G87">
         <v>496.3</v>
@@ -8427,37 +8427,37 @@
         <v>1187.8</v>
       </c>
       <c r="M87">
-        <v>3650.384364</v>
+        <v>3693.3300624</v>
       </c>
       <c r="N87">
-        <v>-2462.584364000001</v>
+        <v>-2505.530062400001</v>
       </c>
       <c r="O87">
-        <v>-635.3467659120003</v>
+        <v>-646.4267560992001</v>
       </c>
       <c r="P87">
-        <v>-1827.237598088001</v>
+        <v>-1859.1033063008</v>
       </c>
       <c r="Q87">
-        <v>-478.8375980880005</v>
+        <v>-510.7033063008003</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1886128760187341</v>
+        <v>0.198813795734358</v>
       </c>
       <c r="T87">
-        <v>3.298218845698248</v>
+        <v>3.533805906105266</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.08395072119588991</v>
+        <v>0.08297455001919352</v>
       </c>
       <c r="W87">
-        <v>0.1839426951838653</v>
+        <v>0.184138710356146</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3253903922321314</v>
+        <v>0.3216067830201299</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1861932223090957</v>
+        <v>0.1877432223090956</v>
       </c>
       <c r="C88">
-        <v>-12964.4147048855</v>
+        <v>-13226.3516107357</v>
       </c>
       <c r="D88">
-        <v>4932.363295114495</v>
+        <v>4884.299389264298</v>
       </c>
       <c r="E88">
-        <v>11157.978</v>
+        <v>11371.851</v>
       </c>
       <c r="F88">
-        <v>18393.078</v>
+        <v>18606.951</v>
       </c>
       <c r="G88">
         <v>496.3</v>
@@ -8509,37 +8509,37 @@
         <v>1187.8</v>
       </c>
       <c r="M88">
-        <v>3693.3300624</v>
+        <v>3736.2757608</v>
       </c>
       <c r="N88">
-        <v>-2505.530062400001</v>
+        <v>-2548.4757608</v>
       </c>
       <c r="O88">
-        <v>-646.4267560992001</v>
+        <v>-657.5067462864001</v>
       </c>
       <c r="P88">
-        <v>-1859.1033063008</v>
+        <v>-1890.9690145136</v>
       </c>
       <c r="Q88">
-        <v>-510.7033063008003</v>
+        <v>-542.5690145136002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.198813795734358</v>
+        <v>0.210584087713924</v>
       </c>
       <c r="T88">
-        <v>3.533805906105266</v>
+        <v>3.805637129651824</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.08297455001919352</v>
+        <v>0.08202081955920279</v>
       </c>
       <c r="W88">
-        <v>0.184138710356146</v>
+        <v>0.1843302194325121</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3216067830201299</v>
+        <v>0.3179101533302434</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1877432223090956</v>
+        <v>0.1892932223090956</v>
       </c>
       <c r="C89">
-        <v>-13226.3516107357</v>
+        <v>-13487.36082948102</v>
       </c>
       <c r="D89">
-        <v>4884.299389264298</v>
+        <v>4837.163170518986</v>
       </c>
       <c r="E89">
-        <v>11371.851</v>
+        <v>11585.724</v>
       </c>
       <c r="F89">
-        <v>18606.951</v>
+        <v>18820.824</v>
       </c>
       <c r="G89">
         <v>496.3</v>
@@ -8591,37 +8591,37 @@
         <v>1187.8</v>
       </c>
       <c r="M89">
-        <v>3736.2757608</v>
+        <v>3779.221459200001</v>
       </c>
       <c r="N89">
-        <v>-2548.4757608</v>
+        <v>-2591.421459200001</v>
       </c>
       <c r="O89">
-        <v>-657.5067462864001</v>
+        <v>-668.5867364736004</v>
       </c>
       <c r="P89">
-        <v>-1890.9690145136</v>
+        <v>-1922.834722726401</v>
       </c>
       <c r="Q89">
-        <v>-542.5690145136002</v>
+        <v>-574.4347227264007</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.210584087713924</v>
+        <v>0.2243160950234177</v>
       </c>
       <c r="T89">
-        <v>3.805637129651824</v>
+        <v>4.122773557122811</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.08202081955920279</v>
+        <v>0.08108876479148455</v>
       </c>
       <c r="W89">
-        <v>0.1843302194325121</v>
+        <v>0.1845173760298699</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3179101533302434</v>
+        <v>0.3142975379514905</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1892932223090956</v>
+        <v>0.1908432223090956</v>
       </c>
       <c r="C90">
-        <v>-13487.36082948102</v>
+        <v>-13747.4689625003</v>
       </c>
       <c r="D90">
-        <v>4837.163170518986</v>
+        <v>4790.928037499703</v>
       </c>
       <c r="E90">
-        <v>11585.724</v>
+        <v>11799.597</v>
       </c>
       <c r="F90">
-        <v>18820.824</v>
+        <v>19034.697</v>
       </c>
       <c r="G90">
         <v>496.3</v>
@@ -8673,37 +8673,37 @@
         <v>1187.8</v>
       </c>
       <c r="M90">
-        <v>3779.221459200001</v>
+        <v>3822.167157600001</v>
       </c>
       <c r="N90">
-        <v>-2591.421459200001</v>
+        <v>-2634.367157600001</v>
       </c>
       <c r="O90">
-        <v>-668.5867364736004</v>
+        <v>-679.6667266608004</v>
       </c>
       <c r="P90">
-        <v>-1922.834722726401</v>
+        <v>-1954.700430939201</v>
       </c>
       <c r="Q90">
-        <v>-574.4347227264007</v>
+        <v>-606.3004309392006</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2243160950234177</v>
+        <v>0.2405448309346375</v>
       </c>
       <c r="T90">
-        <v>4.122773557122811</v>
+        <v>4.497571153224885</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.08108876479148455</v>
+        <v>0.08017765507472631</v>
       </c>
       <c r="W90">
-        <v>0.1845173760298699</v>
+        <v>0.184700326860995</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3142975379514905</v>
+        <v>0.3107661049407996</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1908432223090956</v>
+        <v>0.1923932223090956</v>
       </c>
       <c r="C91">
-        <v>-13747.4689625003</v>
+        <v>-14006.70160374421</v>
       </c>
       <c r="D91">
-        <v>4790.928037499703</v>
+        <v>4745.568396255795</v>
       </c>
       <c r="E91">
-        <v>11799.597</v>
+        <v>12013.47</v>
       </c>
       <c r="F91">
-        <v>19034.697</v>
+        <v>19248.57</v>
       </c>
       <c r="G91">
         <v>496.3</v>
@@ -8755,37 +8755,37 @@
         <v>1187.8</v>
       </c>
       <c r="M91">
-        <v>3822.167157600001</v>
+        <v>3865.112856000001</v>
       </c>
       <c r="N91">
-        <v>-2634.367157600001</v>
+        <v>-2677.312856000001</v>
       </c>
       <c r="O91">
-        <v>-679.6667266608004</v>
+        <v>-690.7467168480002</v>
       </c>
       <c r="P91">
-        <v>-1954.700430939201</v>
+        <v>-1986.566139152001</v>
       </c>
       <c r="Q91">
-        <v>-606.3004309392006</v>
+        <v>-638.1661391520006</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2405448309346375</v>
+        <v>0.2600193140281012</v>
       </c>
       <c r="T91">
-        <v>4.497571153224885</v>
+        <v>4.947328268547373</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.08017765507472631</v>
+        <v>0.07928679224056269</v>
       </c>
       <c r="W91">
-        <v>0.184700326860995</v>
+        <v>0.184879212118095</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3107661049407996</v>
+        <v>0.3073131482192352</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1923932223090956</v>
+        <v>0.1939432223090956</v>
       </c>
       <c r="C92">
-        <v>-14006.70160374421</v>
+        <v>-14265.08338697865</v>
       </c>
       <c r="D92">
-        <v>4745.568396255795</v>
+        <v>4701.059613021353</v>
       </c>
       <c r="E92">
-        <v>12013.47</v>
+        <v>12227.343</v>
       </c>
       <c r="F92">
-        <v>19248.57</v>
+        <v>19462.443</v>
       </c>
       <c r="G92">
         <v>496.3</v>
@@ -8837,37 +8837,37 @@
         <v>1187.8</v>
       </c>
       <c r="M92">
-        <v>3865.112856000001</v>
+        <v>3908.058554400001</v>
       </c>
       <c r="N92">
-        <v>-2677.312856000001</v>
+        <v>-2720.258554400001</v>
       </c>
       <c r="O92">
-        <v>-690.7467168480002</v>
+        <v>-701.8267070352002</v>
       </c>
       <c r="P92">
-        <v>-1986.566139152001</v>
+        <v>-2018.4318473648</v>
       </c>
       <c r="Q92">
-        <v>-638.1661391520006</v>
+        <v>-670.0318473648003</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2600193140281012</v>
+        <v>0.2838214600312236</v>
       </c>
       <c r="T92">
-        <v>4.947328268547373</v>
+        <v>5.497031409497082</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.07928679224056269</v>
+        <v>0.07841550880934772</v>
       </c>
       <c r="W92">
-        <v>0.184879212118095</v>
+        <v>0.185054165831083</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3073131482192352</v>
+        <v>0.3039360806563864</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1939432223090956</v>
+        <v>0.1954932223090956</v>
       </c>
       <c r="C93">
-        <v>-14265.08338697865</v>
+        <v>-14522.63803039434</v>
       </c>
       <c r="D93">
-        <v>4701.059613021353</v>
+        <v>4657.377969605658</v>
       </c>
       <c r="E93">
-        <v>12227.343</v>
+        <v>12441.216</v>
       </c>
       <c r="F93">
-        <v>19462.443</v>
+        <v>19676.316</v>
       </c>
       <c r="G93">
         <v>496.3</v>
@@ -8919,37 +8919,37 @@
         <v>1187.8</v>
       </c>
       <c r="M93">
-        <v>3908.058554400001</v>
+        <v>3951.004252800001</v>
       </c>
       <c r="N93">
-        <v>-2720.258554400001</v>
+        <v>-2763.204252800001</v>
       </c>
       <c r="O93">
-        <v>-701.8267070352002</v>
+        <v>-712.9066972224003</v>
       </c>
       <c r="P93">
-        <v>-2018.4318473648</v>
+        <v>-2050.297555577601</v>
       </c>
       <c r="Q93">
-        <v>-670.0318473648003</v>
+        <v>-701.8975555776005</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2838214600312236</v>
+        <v>0.3135741425351266</v>
       </c>
       <c r="T93">
-        <v>5.497031409497082</v>
+        <v>6.184160335684219</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.07841550880934772</v>
+        <v>0.07756316632228959</v>
       </c>
       <c r="W93">
-        <v>0.185054165831083</v>
+        <v>0.1852253162024843</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3039360806563864</v>
+        <v>0.3006324276057736</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1954932223090956</v>
+        <v>0.1970432223090956</v>
       </c>
       <c r="C94">
-        <v>-14522.63803039434</v>
+        <v>-14779.38837875226</v>
       </c>
       <c r="D94">
-        <v>4657.377969605658</v>
+        <v>4614.500621247742</v>
       </c>
       <c r="E94">
-        <v>12441.216</v>
+        <v>12655.089</v>
       </c>
       <c r="F94">
-        <v>19676.316</v>
+        <v>19890.189</v>
       </c>
       <c r="G94">
         <v>496.3</v>
@@ -9001,37 +9001,37 @@
         <v>1187.8</v>
       </c>
       <c r="M94">
-        <v>3951.004252800001</v>
+        <v>3993.949951200001</v>
       </c>
       <c r="N94">
-        <v>-2763.204252800001</v>
+        <v>-2806.149951200001</v>
       </c>
       <c r="O94">
-        <v>-712.9066972224003</v>
+        <v>-723.9866874096002</v>
       </c>
       <c r="P94">
-        <v>-2050.297555577601</v>
+        <v>-2082.163263790401</v>
       </c>
       <c r="Q94">
-        <v>-701.8975555776005</v>
+        <v>-733.7632637904007</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3135741425351266</v>
+        <v>0.3518275914687162</v>
       </c>
       <c r="T94">
-        <v>6.184160335684219</v>
+        <v>7.067611812210536</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.07756316632228959</v>
+        <v>0.0767291537811897</v>
       </c>
       <c r="W94">
-        <v>0.1852253162024843</v>
+        <v>0.1853927859207371</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3006324276057736</v>
+        <v>0.2973998208573244</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1970432223090956</v>
+        <v>0.1985932223090957</v>
       </c>
       <c r="C95">
-        <v>-14779.38837875226</v>
+        <v>-15035.35644322225</v>
       </c>
       <c r="D95">
-        <v>4614.500621247742</v>
+        <v>4572.405556777756</v>
       </c>
       <c r="E95">
-        <v>12655.089</v>
+        <v>12868.962</v>
       </c>
       <c r="F95">
-        <v>19890.189</v>
+        <v>20104.06200000001</v>
       </c>
       <c r="G95">
         <v>496.3</v>
@@ -9083,37 +9083,37 @@
         <v>1187.8</v>
       </c>
       <c r="M95">
-        <v>3993.949951200001</v>
+        <v>4036.895649600001</v>
       </c>
       <c r="N95">
-        <v>-2806.149951200001</v>
+        <v>-2849.095649600001</v>
       </c>
       <c r="O95">
-        <v>-723.9866874096002</v>
+        <v>-735.0666775968003</v>
       </c>
       <c r="P95">
-        <v>-2082.163263790401</v>
+        <v>-2114.028972003201</v>
       </c>
       <c r="Q95">
-        <v>-733.7632637904007</v>
+        <v>-765.6289720032009</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3518275914687162</v>
+        <v>0.4028321900468356</v>
       </c>
       <c r="T95">
-        <v>7.067611812210536</v>
+        <v>8.245547114245628</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.0767291537811897</v>
+        <v>0.07591288618777278</v>
       </c>
       <c r="W95">
-        <v>0.1853927859207371</v>
+        <v>0.1855566924534952</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2973998208573244</v>
+        <v>0.2942359929758634</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1985932223090957</v>
+        <v>0.2001432223090956</v>
       </c>
       <c r="C96">
-        <v>-15035.35644322225</v>
+        <v>-15290.56343906084</v>
       </c>
       <c r="D96">
-        <v>4572.405556777756</v>
+        <v>4531.071560939163</v>
       </c>
       <c r="E96">
-        <v>12868.962</v>
+        <v>13082.835</v>
       </c>
       <c r="F96">
-        <v>20104.06200000001</v>
+        <v>20317.935</v>
       </c>
       <c r="G96">
         <v>496.3</v>
@@ -9165,37 +9165,37 @@
         <v>1187.8</v>
       </c>
       <c r="M96">
-        <v>4036.895649600001</v>
+        <v>4079.841348000001</v>
       </c>
       <c r="N96">
-        <v>-2849.095649600001</v>
+        <v>-2892.041348000002</v>
       </c>
       <c r="O96">
-        <v>-735.0666775968003</v>
+        <v>-746.1466677840004</v>
       </c>
       <c r="P96">
-        <v>-2114.028972003201</v>
+        <v>-2145.894680216001</v>
       </c>
       <c r="Q96">
-        <v>-765.6289720032009</v>
+        <v>-797.4946802160011</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4028321900468356</v>
+        <v>0.4742386280562029</v>
       </c>
       <c r="T96">
-        <v>8.245547114245628</v>
+        <v>9.894656537094757</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.07591288618777278</v>
+        <v>0.0751138031752699</v>
       </c>
       <c r="W96">
-        <v>0.1855566924534952</v>
+        <v>0.1857171483224058</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2942359929758634</v>
+        <v>0.2911387719971702</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2001432223090956</v>
+        <v>0.2016932223090957</v>
       </c>
       <c r="C97">
-        <v>-15290.56343906084</v>
+        <v>-15545.02982126379</v>
       </c>
       <c r="D97">
-        <v>4531.071560939163</v>
+        <v>4490.478178736211</v>
       </c>
       <c r="E97">
-        <v>13082.835</v>
+        <v>13296.708</v>
       </c>
       <c r="F97">
-        <v>20317.935</v>
+        <v>20531.808</v>
       </c>
       <c r="G97">
         <v>496.3</v>
@@ -9247,37 +9247,37 @@
         <v>1187.8</v>
       </c>
       <c r="M97">
-        <v>4079.841348000001</v>
+        <v>4122.787046400001</v>
       </c>
       <c r="N97">
-        <v>-2892.041348000002</v>
+        <v>-2934.987046400001</v>
       </c>
       <c r="O97">
-        <v>-746.1466677840004</v>
+        <v>-757.2266579712003</v>
       </c>
       <c r="P97">
-        <v>-2145.894680216001</v>
+        <v>-2177.760388428801</v>
       </c>
       <c r="Q97">
-        <v>-797.4946802160011</v>
+        <v>-829.3603884288004</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4742386280562029</v>
+        <v>0.5813482850702539</v>
       </c>
       <c r="T97">
-        <v>9.894656537094757</v>
+        <v>12.36832067136845</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.0751138031752699</v>
+        <v>0.07433136772552751</v>
       </c>
       <c r="W97">
-        <v>0.1857171483224058</v>
+        <v>0.1858742613607141</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2911387719971702</v>
+        <v>0.288106076455533</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2016932223090956</v>
+        <v>0.2032432223090956</v>
       </c>
       <c r="C98">
-        <v>-15545.02982126379</v>
+        <v>-15798.77531831913</v>
       </c>
       <c r="D98">
-        <v>4490.478178736211</v>
+        <v>4450.605681680868</v>
       </c>
       <c r="E98">
-        <v>13296.708</v>
+        <v>13510.581</v>
       </c>
       <c r="F98">
-        <v>20531.808</v>
+        <v>20745.681</v>
       </c>
       <c r="G98">
         <v>496.3</v>
@@ -9329,37 +9329,37 @@
         <v>1187.8</v>
       </c>
       <c r="M98">
-        <v>4122.787046400001</v>
+        <v>4165.732744800001</v>
       </c>
       <c r="N98">
-        <v>-2934.987046400001</v>
+        <v>-2977.932744800001</v>
       </c>
       <c r="O98">
-        <v>-757.2266579712003</v>
+        <v>-768.3066481584002</v>
       </c>
       <c r="P98">
-        <v>-2177.760388428801</v>
+        <v>-2209.626096641601</v>
       </c>
       <c r="Q98">
-        <v>-829.3603884288004</v>
+        <v>-861.2260966416006</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5813482850702525</v>
+        <v>0.75986438009367</v>
       </c>
       <c r="T98">
-        <v>12.36832067136842</v>
+        <v>16.49109422849123</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.07433136772552751</v>
+        <v>0.07356506496547054</v>
       </c>
       <c r="W98">
-        <v>0.1858742613607141</v>
+        <v>0.1860281349549335</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.288106076455533</v>
+        <v>0.285135910718878</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2032432223090956</v>
+        <v>0.2047932223090956</v>
       </c>
       <c r="C99">
-        <v>-15798.77531831913</v>
+        <v>-16051.81896417787</v>
       </c>
       <c r="D99">
-        <v>4450.605681680868</v>
+        <v>4411.435035822131</v>
       </c>
       <c r="E99">
-        <v>13510.581</v>
+        <v>13724.454</v>
       </c>
       <c r="F99">
-        <v>20745.681</v>
+        <v>20959.554</v>
       </c>
       <c r="G99">
         <v>496.3</v>
@@ -9411,37 +9411,37 @@
         <v>1187.8</v>
       </c>
       <c r="M99">
-        <v>4165.732744800001</v>
+        <v>4208.678443200001</v>
       </c>
       <c r="N99">
-        <v>-2977.932744800001</v>
+        <v>-3020.878443200002</v>
       </c>
       <c r="O99">
-        <v>-768.3066481584002</v>
+        <v>-779.3866383456004</v>
       </c>
       <c r="P99">
-        <v>-2209.626096641601</v>
+        <v>-2241.491804854401</v>
       </c>
       <c r="Q99">
-        <v>-861.2260966416006</v>
+        <v>-893.0918048544013</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.75986438009367</v>
+        <v>1.116896570140505</v>
       </c>
       <c r="T99">
-        <v>16.49109422849123</v>
+        <v>24.73664134273684</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.07356506496547054</v>
+        <v>0.07281440103725144</v>
       </c>
       <c r="W99">
-        <v>0.1860281349549335</v>
+        <v>0.1861788682717199</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.285135910718878</v>
+        <v>0.2822263606095017</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2047932223090956</v>
+        <v>0.2063432223090956</v>
       </c>
       <c r="C100">
-        <v>-16051.81896417787</v>
+        <v>-16304.17912855109</v>
       </c>
       <c r="D100">
-        <v>4411.435035822131</v>
+        <v>4372.94787144891</v>
       </c>
       <c r="E100">
-        <v>13724.454</v>
+        <v>13938.327</v>
       </c>
       <c r="F100">
-        <v>20959.554</v>
+        <v>21173.427</v>
       </c>
       <c r="G100">
         <v>496.3</v>
@@ -9493,37 +9493,37 @@
         <v>1187.8</v>
       </c>
       <c r="M100">
-        <v>4208.678443200001</v>
+        <v>4251.624141600001</v>
       </c>
       <c r="N100">
-        <v>-3020.878443200002</v>
+        <v>-3063.824141600001</v>
       </c>
       <c r="O100">
-        <v>-779.3866383456004</v>
+        <v>-790.4666285328004</v>
       </c>
       <c r="P100">
-        <v>-2241.491804854401</v>
+        <v>-2273.357513067201</v>
       </c>
       <c r="Q100">
-        <v>-893.0918048544013</v>
+        <v>-924.957513067201</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.116896570140505</v>
+        <v>2.18799314028101</v>
       </c>
       <c r="T100">
-        <v>24.73664134273684</v>
+        <v>49.47328268547368</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.07281440103725144</v>
+        <v>0.07207890203687516</v>
       </c>
       <c r="W100">
-        <v>0.1861788682717199</v>
+        <v>0.1863265564709955</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2822263606095017</v>
+        <v>0.2793755892902138</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2063432223090956</v>
-      </c>
-      <c r="C101">
-        <v>-16304.17912855109</v>
-      </c>
-      <c r="D101">
-        <v>4372.94787144891</v>
-      </c>
-      <c r="E101">
-        <v>13938.327</v>
-      </c>
-      <c r="F101">
-        <v>21173.427</v>
-      </c>
-      <c r="G101">
-        <v>496.3</v>
-      </c>
-      <c r="H101">
-        <v>14152.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2536.2</v>
-      </c>
-      <c r="K101">
-        <v>1348.4</v>
-      </c>
-      <c r="L101">
-        <v>1187.8</v>
-      </c>
-      <c r="M101">
-        <v>4251.624141600001</v>
-      </c>
-      <c r="N101">
-        <v>-3063.824141600001</v>
-      </c>
-      <c r="O101">
-        <v>-790.4666285328004</v>
-      </c>
-      <c r="P101">
-        <v>-2273.357513067201</v>
-      </c>
-      <c r="Q101">
-        <v>-924.957513067201</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.18799314028101</v>
-      </c>
-      <c r="T101">
-        <v>49.47328268547368</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.07207890203687516</v>
-      </c>
-      <c r="W101">
-        <v>0.1863265564709955</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2793755892902138</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
